--- a/data/proteomics/rosemary_data_analysis.xlsx
+++ b/data/proteomics/rosemary_data_analysis.xlsx
@@ -1265,16 +1265,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>175.2179951479614</v>
+        <v>175.2179951479615</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3708259819820349</v>
+        <v>0.3708259819820348</v>
       </c>
       <c r="D2" t="n">
         <v>0.2768303852909352</v>
       </c>
       <c r="E2" t="n">
-        <v>3.195561510640328</v>
+        <v>3.195561510640327</v>
       </c>
       <c r="F2" t="n">
         <v>104.4945795180777</v>
@@ -1283,7 +1283,7 @@
         <v>227.0895431527453</v>
       </c>
       <c r="H2" t="n">
-        <v>105.1013304776597</v>
+        <v>105.1013304776598</v>
       </c>
       <c r="I2" t="n">
         <v>29.33172266429985</v>
@@ -1292,16 +1292,16 @@
         <v>7.723574480334038</v>
       </c>
       <c r="K2" t="n">
-        <v>44.88391858779397</v>
+        <v>44.88391858779396</v>
       </c>
       <c r="L2" t="n">
-        <v>12.37121765109382</v>
+        <v>12.37121765109383</v>
       </c>
       <c r="M2" t="n">
-        <v>1.594856480246183</v>
+        <v>1.594856480246182</v>
       </c>
       <c r="N2" t="n">
-        <v>8.834259072602098</v>
+        <v>8.834259072602096</v>
       </c>
       <c r="O2" t="n">
         <v>1.357937390230849</v>
@@ -1313,13 +1313,13 @@
         <v>3.080177624420704</v>
       </c>
       <c r="R2" t="n">
-        <v>2.697049978710425</v>
+        <v>2.697049978710424</v>
       </c>
       <c r="S2" t="n">
-        <v>1.394618081475111</v>
+        <v>1.39461808147511</v>
       </c>
       <c r="T2" t="n">
-        <v>4.335169502189708</v>
+        <v>4.335169502189709</v>
       </c>
       <c r="U2" t="n">
         <v>0.009573886901756628</v>
@@ -1334,16 +1334,16 @@
         <v>0.0970549600016119</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.293725227694881</v>
+        <v>1.293725227694882</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.319501117518226</v>
+        <v>1.319501117518227</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.404548614880595</v>
+        <v>9.4045486148806</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2966098180711587</v>
+        <v>0.2966098180711586</v>
       </c>
       <c r="AC2" t="n">
         <v>14.47655535680351</v>
@@ -1352,25 +1352,25 @@
         <v>0.02335576616544602</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.004322178134305561</v>
+        <v>0.00432217813430556</v>
       </c>
       <c r="AF2" t="n">
-        <v>19.93820832675886</v>
+        <v>19.93820832675885</v>
       </c>
       <c r="AG2" t="n">
-        <v>17.68637931207862</v>
+        <v>17.68637931207861</v>
       </c>
       <c r="AH2" t="n">
         <v>0.6398987966166346</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.4744506766882923</v>
+        <v>0.4744506766882924</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.154579907299943</v>
       </c>
       <c r="AK2" t="n">
-        <v>6.097546813759398</v>
+        <v>6.0975468137594</v>
       </c>
       <c r="AL2" t="n">
         <v>0.3067922242723701</v>
@@ -1379,19 +1379,19 @@
         <v>0.1444252502823726</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.09710812149561765</v>
+        <v>0.09710812149561764</v>
       </c>
       <c r="AO2" t="n">
         <v>0.2221327367623503</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.2548033562810967</v>
+        <v>0.2548033562810968</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.4714266407322931</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.024542231082157</v>
+        <v>3.024542231082155</v>
       </c>
       <c r="AS2" t="n">
         <v>0.06775541010962828</v>
@@ -1409,10 +1409,10 @@
         <v>1.579735841505124</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.08860172431605198</v>
+        <v>0.088601724316052</v>
       </c>
       <c r="AY2" t="n">
-        <v>12.0728918827947</v>
+        <v>12.07289188279469</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.2072592936204653</v>
@@ -1421,25 +1421,25 @@
         <v>0.04237688422225861</v>
       </c>
       <c r="BB2" t="n">
-        <v>20.05955599835347</v>
+        <v>20.05955599835348</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.436010129408096</v>
+        <v>2.436010129408095</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.002219528609343</v>
+        <v>9.002219528609345</v>
       </c>
       <c r="BE2" t="n">
         <v>0.1805047636607367</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.2968479371728842</v>
+        <v>0.296847937172884</v>
       </c>
       <c r="BG2" t="n">
         <v>0.3665211324782944</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.161584142186905</v>
+        <v>4.161584142186904</v>
       </c>
       <c r="BI2" t="n">
         <v>0.1974613923869827</v>
@@ -1448,7 +1448,7 @@
         <v>0.06700902070155082</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.47402575505258</v>
+        <v>7.474025755052581</v>
       </c>
       <c r="BL2" t="n">
         <v>0.02371593080490814</v>
@@ -1463,10 +1463,10 @@
         <v>0.02377993909405592</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.08860435217536047</v>
+        <v>0.08860435217536049</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.1563709549416535</v>
+        <v>0.1563709549416536</v>
       </c>
       <c r="BR2" t="n">
         <v>0.2093369948409277</v>
@@ -1478,7 +1478,7 @@
         <v>1.798067067815747</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.357891277061868</v>
+        <v>1.357891277061867</v>
       </c>
       <c r="BV2" t="n">
         <v>1.302261208263902</v>
@@ -1490,7 +1490,7 @@
         <v>1.018561139278981</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.02665883122237918</v>
+        <v>0.02665883122237917</v>
       </c>
       <c r="BZ2" t="n">
         <v>3.166762259745655</v>
@@ -1502,7 +1502,7 @@
         <v>0.1157185022286448</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.05933909815392528</v>
+        <v>0.05933909815392529</v>
       </c>
       <c r="CD2" t="n">
         <v>0.06714293532456793</v>
@@ -1511,7 +1511,7 @@
         <v>1.393836133437811</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.2770257419772108</v>
+        <v>0.2770257419772107</v>
       </c>
       <c r="CG2" t="n">
         <v>1.135079953708245</v>
@@ -1535,7 +1535,7 @@
         <v>0.01059511087585057</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.08625592042688515</v>
+        <v>0.08625592042688514</v>
       </c>
       <c r="CO2" t="n">
         <v>0.7712787491124983</v>
@@ -1556,22 +1556,22 @@
         <v>0.06531892543288959</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.03924334014375772</v>
+        <v>0.03924334014375773</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.1067341807237031</v>
+        <v>0.1067341807237032</v>
       </c>
       <c r="CW2" t="n">
         <v>0.1758855202626069</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.603832743762589</v>
+        <v>1.60383274376259</v>
       </c>
       <c r="CY2" t="n">
         <v>0.03447032355374471</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.09044645776645845</v>
+        <v>0.09044645776645846</v>
       </c>
       <c r="DA2" t="n">
         <v>0.1027709313058061</v>
@@ -1583,7 +1583,7 @@
         <v>0.05829479483327835</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.5101234225125985</v>
+        <v>0.5101234225125986</v>
       </c>
       <c r="DE2" t="n">
         <v>0.003225085172898607</v>
@@ -1598,7 +1598,7 @@
         <v>0.1723998821097935</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.04491887659854189</v>
+        <v>0.04491887659854188</v>
       </c>
       <c r="DJ2" t="n">
         <v>0.01503112853073343</v>
@@ -1607,7 +1607,7 @@
         <v>0.2882826782378188</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.09242939732681775</v>
+        <v>0.09242939732681776</v>
       </c>
       <c r="DM2" t="n">
         <v>0.04967568699280182</v>
@@ -1616,10 +1616,10 @@
         <v>0.008082196718031924</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.2925431235820297</v>
+        <v>0.2925431235820296</v>
       </c>
       <c r="DP2" t="n">
-        <v>36.39399150982231</v>
+        <v>36.39399150982232</v>
       </c>
       <c r="DQ2" t="n">
         <v>0.004178621764955158</v>
@@ -1631,7 +1631,7 @@
         <v>0.9399657643332729</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.6172335740725086</v>
+        <v>0.6172335740725087</v>
       </c>
       <c r="DU2" t="n">
         <v>1.632089249198855</v>
@@ -1646,7 +1646,7 @@
         <v>0.2723055335375116</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.0814635289844395</v>
+        <v>0.08146352898443948</v>
       </c>
       <c r="DZ2" t="n">
         <v>0.05898244268949321</v>
@@ -1655,7 +1655,7 @@
         <v>0.1310003960225201</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.08626191425146824</v>
+        <v>0.08626191425146823</v>
       </c>
       <c r="EC2" t="n">
         <v>1.030049422002151</v>
@@ -1673,7 +1673,7 @@
         <v>0.02166118843978278</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.01267494239724661</v>
+        <v>0.0126749423972466</v>
       </c>
       <c r="EI2" t="n">
         <v>0.01112961171932348</v>
@@ -1770,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>160.04449738781</v>
+        <v>160.0444973878097</v>
       </c>
       <c r="C3" t="n">
         <v>0.3520361165960142</v>
@@ -1785,13 +1785,13 @@
         <v>95.81337389222566</v>
       </c>
       <c r="G3" t="n">
-        <v>206.7361723285037</v>
+        <v>206.7361723285035</v>
       </c>
       <c r="H3" t="n">
-        <v>92.52612055309251</v>
+        <v>92.52612055309257</v>
       </c>
       <c r="I3" t="n">
-        <v>27.36723455464774</v>
+        <v>27.36723455464773</v>
       </c>
       <c r="J3" t="n">
         <v>6.985257395245154</v>
@@ -1806,19 +1806,19 @@
         <v>1.391237317232775</v>
       </c>
       <c r="N3" t="n">
-        <v>8.706356576039491</v>
+        <v>8.706356576039489</v>
       </c>
       <c r="O3" t="n">
         <v>1.326201247497412</v>
       </c>
       <c r="P3" t="n">
-        <v>1.790477010188329</v>
+        <v>1.79047701018833</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.344927407504834</v>
+        <v>2.344927407504835</v>
       </c>
       <c r="R3" t="n">
-        <v>2.36756958907547</v>
+        <v>2.367569589075473</v>
       </c>
       <c r="S3" t="n">
         <v>1.253350678060727</v>
@@ -1830,10 +1830,10 @@
         <v>0.007685929356725506</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4638494644943265</v>
+        <v>0.4638494644943264</v>
       </c>
       <c r="W3" t="n">
-        <v>18.03371716911289</v>
+        <v>18.03371716911288</v>
       </c>
       <c r="X3" t="n">
         <v>0.1000493163611742</v>
@@ -1845,13 +1845,13 @@
         <v>1.225252673207757</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.081672728719521</v>
+        <v>8.081672728719518</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2735237095728636</v>
+        <v>0.2735237095728638</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.99912192870184</v>
+        <v>13.99912192870183</v>
       </c>
       <c r="AD3" t="n">
         <v>0.02072222810167829</v>
@@ -1866,7 +1866,7 @@
         <v>15.70691743160874</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.5517763762703968</v>
+        <v>0.5517763762703967</v>
       </c>
       <c r="AI3" t="n">
         <v>0.4527354524364828</v>
@@ -1875,10 +1875,10 @@
         <v>1.035954553688365</v>
       </c>
       <c r="AK3" t="n">
-        <v>5.114140316126428</v>
+        <v>5.114140316126429</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.2886299712415188</v>
+        <v>0.2886299712415187</v>
       </c>
       <c r="AM3" t="n">
         <v>0.1421580374637516</v>
@@ -1893,7 +1893,7 @@
         <v>0.1880787036243458</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.4059216546935467</v>
+        <v>0.4059216546935469</v>
       </c>
       <c r="AR3" t="n">
         <v>2.594633508041459</v>
@@ -1914,7 +1914,7 @@
         <v>1.424304970863882</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.07462511893453967</v>
+        <v>0.07462511893453966</v>
       </c>
       <c r="AY3" t="n">
         <v>10.58004088646318</v>
@@ -1929,7 +1929,7 @@
         <v>18.21345737108491</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.110080126989677</v>
+        <v>2.110080126989678</v>
       </c>
       <c r="BD3" t="n">
         <v>8.001800521808399</v>
@@ -1947,13 +1947,13 @@
         <v>3.649819862934674</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.2067498450747352</v>
+        <v>0.2067498450747351</v>
       </c>
       <c r="BJ3" t="n">
         <v>0.004054377887903056</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.359220212472145</v>
+        <v>7.359220212472147</v>
       </c>
       <c r="BL3" t="n">
         <v>0.02119374383137082</v>
@@ -1962,10 +1962,10 @@
         <v>13.38141274543271</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.4811467776143715</v>
+        <v>0.4811467776143714</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.02175221901825344</v>
+        <v>0.02175221901825343</v>
       </c>
       <c r="BP3" t="n">
         <v>0.08338357720705422</v>
@@ -1977,7 +1977,7 @@
         <v>0.214230053281147</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.267283128133085</v>
+        <v>9.267283128133084</v>
       </c>
       <c r="BT3" t="n">
         <v>1.662696460290599</v>
@@ -1986,13 +1986,13 @@
         <v>1.266259381382844</v>
       </c>
       <c r="BV3" t="n">
-        <v>1.212096825122385</v>
+        <v>1.212096825122384</v>
       </c>
       <c r="BW3" t="n">
         <v>0.003160460350449546</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.8945888726264914</v>
+        <v>0.8945888726264916</v>
       </c>
       <c r="BY3" t="n">
         <v>0.02675760155556803</v>
@@ -2001,13 +2001,13 @@
         <v>3.217750426976056</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0347550315373359</v>
+        <v>0.03475503153733589</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0870939116430466</v>
+        <v>0.08709391164304661</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.05744520665500571</v>
+        <v>0.0574452066550057</v>
       </c>
       <c r="CD3" t="n">
         <v>0.0621394541742953</v>
@@ -2022,7 +2022,7 @@
         <v>0.9685246521977757</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.1437978112685631</v>
+        <v>0.1437978112685632</v>
       </c>
       <c r="CI3" t="n">
         <v>0.02087520947440718</v>
@@ -2049,7 +2049,7 @@
         <v>0.4431789994843116</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.4533992482492631</v>
+        <v>0.4533992482492632</v>
       </c>
       <c r="CR3" t="n">
         <v>0.1348887318010449</v>
@@ -2064,25 +2064,25 @@
         <v>0.03380927103038552</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.09507465060253625</v>
+        <v>0.09507465060253627</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1680631214467078</v>
+        <v>0.1680631214467079</v>
       </c>
       <c r="CX3" t="n">
         <v>1.386124320750141</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.03334313565412165</v>
+        <v>0.03334313565412164</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.08713636554628904</v>
+        <v>0.08713636554628902</v>
       </c>
       <c r="DA3" t="n">
         <v>0.09393807738276125</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.1864934488698809</v>
+        <v>0.186493448869881</v>
       </c>
       <c r="DC3" t="n">
         <v>0.04917303096118841</v>
@@ -2109,37 +2109,37 @@
         <v>0.01585215960085824</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.2596177988731837</v>
+        <v>0.2596177988731838</v>
       </c>
       <c r="DL3" t="n">
         <v>0.0830215154054517</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.04448405329343223</v>
+        <v>0.04448405329343224</v>
       </c>
       <c r="DN3" t="n">
         <v>0.007138246939998015</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.2459295862975193</v>
+        <v>0.2459295862975192</v>
       </c>
       <c r="DP3" t="n">
-        <v>31.6852964161284</v>
+        <v>31.68529641612839</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.003816833364138419</v>
+        <v>0.003816833364138418</v>
       </c>
       <c r="DR3" t="n">
         <v>0.03283467127118722</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.8700527698978929</v>
+        <v>0.8700527698978928</v>
       </c>
       <c r="DT3" t="n">
         <v>0.5288835120296254</v>
       </c>
       <c r="DU3" t="n">
-        <v>1.503509674621543</v>
+        <v>1.503509674621542</v>
       </c>
       <c r="DV3" t="n">
         <v>0.0212096346627163</v>
@@ -2181,7 +2181,7 @@
         <v>0.01208350221848329</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.01097461440130991</v>
+        <v>0.01097461440130992</v>
       </c>
       <c r="EJ3" t="n">
         <v>0.01090379259237593</v>
@@ -2275,25 +2275,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>168.5410689658385</v>
+        <v>168.5410689658389</v>
       </c>
       <c r="C4" t="n">
         <v>0.3209661646476563</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2878897626554285</v>
+        <v>0.2878897626554287</v>
       </c>
       <c r="E4" t="n">
-        <v>2.990751305452867</v>
+        <v>2.990751305452866</v>
       </c>
       <c r="F4" t="n">
-        <v>102.9450256576946</v>
+        <v>102.9450256576945</v>
       </c>
       <c r="G4" t="n">
-        <v>213.7851497908098</v>
+        <v>213.7851497908103</v>
       </c>
       <c r="H4" t="n">
-        <v>90.77862659703362</v>
+        <v>90.77862659703366</v>
       </c>
       <c r="I4" t="n">
         <v>24.98386908080797</v>
@@ -2302,7 +2302,7 @@
         <v>7.069936299724761</v>
       </c>
       <c r="K4" t="n">
-        <v>34.16741458109771</v>
+        <v>34.16741458109772</v>
       </c>
       <c r="L4" t="n">
         <v>10.99321760413046</v>
@@ -2317,7 +2317,7 @@
         <v>1.391707305891973</v>
       </c>
       <c r="P4" t="n">
-        <v>1.675540337076726</v>
+        <v>1.675540337076725</v>
       </c>
       <c r="Q4" t="n">
         <v>2.474702807906972</v>
@@ -2329,7 +2329,7 @@
         <v>1.282973572231973</v>
       </c>
       <c r="T4" t="n">
-        <v>4.19777595176689</v>
+        <v>4.197775951766889</v>
       </c>
       <c r="U4" t="n">
         <v>0.006821899707863335</v>
@@ -2338,7 +2338,7 @@
         <v>0.4647205002873783</v>
       </c>
       <c r="W4" t="n">
-        <v>16.19893198143081</v>
+        <v>16.1989319814308</v>
       </c>
       <c r="X4" t="n">
         <v>0.1173116873542076</v>
@@ -2353,7 +2353,7 @@
         <v>8.82600546099248</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3179767014571708</v>
+        <v>0.3179767014571709</v>
       </c>
       <c r="AC4" t="n">
         <v>14.8626514397626</v>
@@ -2365,7 +2365,7 @@
         <v>0.004766503063254892</v>
       </c>
       <c r="AF4" t="n">
-        <v>24.53759922338814</v>
+        <v>24.53759922338813</v>
       </c>
       <c r="AG4" t="n">
         <v>19.60435263495348</v>
@@ -2380,28 +2380,28 @@
         <v>1.060101421488198</v>
       </c>
       <c r="AK4" t="n">
-        <v>5.699036768997353</v>
+        <v>5.699036768997355</v>
       </c>
       <c r="AL4" t="n">
         <v>0.3075289005296661</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.1582238575697931</v>
+        <v>0.1582238575697932</v>
       </c>
       <c r="AN4" t="n">
         <v>0.08033090647511303</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1818800407645293</v>
+        <v>0.1818800407645292</v>
       </c>
       <c r="AP4" t="n">
         <v>0.2052720760341419</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.4442616040029669</v>
+        <v>0.444261604002967</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.411729680617749</v>
+        <v>2.41172968061775</v>
       </c>
       <c r="AS4" t="n">
         <v>0.05867967829297586</v>
@@ -2413,7 +2413,7 @@
         <v>0.1273707029964871</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.464585610619854</v>
+        <v>1.464585610619853</v>
       </c>
       <c r="AW4" t="n">
         <v>1.326429855834397</v>
@@ -2428,7 +2428,7 @@
         <v>0.1873915193676626</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0404799147824051</v>
+        <v>0.04047991478240511</v>
       </c>
       <c r="BB4" t="n">
         <v>18.99311284141382</v>
@@ -2437,16 +2437,16 @@
         <v>2.277600249919772</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.310901666166227</v>
+        <v>8.310901666166226</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.1976847099264052</v>
+        <v>0.1976847099264051</v>
       </c>
       <c r="BF4" t="n">
         <v>0.2793889979108572</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.3323114778158129</v>
+        <v>0.332311477815813</v>
       </c>
       <c r="BH4" t="n">
         <v>4.170236557246419</v>
@@ -2473,7 +2473,7 @@
         <v>0.02091373098466211</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.08065678586299246</v>
+        <v>0.08065678586299248</v>
       </c>
       <c r="BQ4" t="n">
         <v>0.1205506415412189</v>
@@ -2491,7 +2491,7 @@
         <v>1.247334570870389</v>
       </c>
       <c r="BV4" t="n">
-        <v>1.269278501060562</v>
+        <v>1.269278501060561</v>
       </c>
       <c r="BW4" t="n">
         <v>0.00352918485838404</v>
@@ -2506,10 +2506,10 @@
         <v>3.02942983861229</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.03389489950402368</v>
+        <v>0.03389489950402369</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.08973841631731855</v>
+        <v>0.08973841631731856</v>
       </c>
       <c r="CC4" t="n">
         <v>0.05839908678499228</v>
@@ -2521,7 +2521,7 @@
         <v>1.262586489144748</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.2989229648615855</v>
+        <v>0.2989229648615854</v>
       </c>
       <c r="CG4" t="n">
         <v>1.001652329885098</v>
@@ -2530,7 +2530,7 @@
         <v>0.141200837934042</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.02332231646736377</v>
+        <v>0.02332231646736376</v>
       </c>
       <c r="CJ4" t="n">
         <v>2.908891485579277</v>
@@ -2554,7 +2554,7 @@
         <v>0.3954804362670933</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.4946000472131032</v>
+        <v>0.4946000472131033</v>
       </c>
       <c r="CR4" t="n">
         <v>0.1323373448024628</v>
@@ -2581,10 +2581,10 @@
         <v>0.03283430285606561</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.08381819822522085</v>
+        <v>0.08381819822522084</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.08598091816555531</v>
+        <v>0.0859809181655553</v>
       </c>
       <c r="DB4" t="n">
         <v>0.2165407554716994</v>
@@ -2593,7 +2593,7 @@
         <v>0.03823434648983214</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.4783541097144985</v>
+        <v>0.4783541097144987</v>
       </c>
       <c r="DE4" t="n">
         <v>0.003100618076203938</v>
@@ -2608,7 +2608,7 @@
         <v>0.1906595121635297</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.03193271867545316</v>
+        <v>0.03193271867545315</v>
       </c>
       <c r="DJ4" t="n">
         <v>0.01277200986029132</v>
@@ -2620,28 +2620,28 @@
         <v>0.0870420491802058</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.04344081938351102</v>
+        <v>0.04344081938351101</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.006094396892213333</v>
+        <v>0.006094396892213332</v>
       </c>
       <c r="DO4" t="n">
         <v>0.2711962596178854</v>
       </c>
       <c r="DP4" t="n">
-        <v>33.57958085110325</v>
+        <v>33.57958085110323</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.004146630901578283</v>
+        <v>0.004146630901578284</v>
       </c>
       <c r="DR4" t="n">
         <v>0.03143354882417708</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.8946711411131362</v>
+        <v>0.8946711411131363</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.5413122800739332</v>
+        <v>0.5413122800739331</v>
       </c>
       <c r="DU4" t="n">
         <v>1.374822597700631</v>
@@ -2650,7 +2650,7 @@
         <v>0.02000814786674313</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.09986227523868141</v>
+        <v>0.09986227523868142</v>
       </c>
       <c r="DX4" t="n">
         <v>0.2455474380539036</v>
@@ -2671,7 +2671,7 @@
         <v>1.098011482255052</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.00385537885045575</v>
+        <v>0.003855378850455751</v>
       </c>
       <c r="EE4" t="n">
         <v>0.03131183173868463</v>
@@ -2686,7 +2686,7 @@
         <v>0.008234922781882596</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.007180006235608427</v>
+        <v>0.007180006235608428</v>
       </c>
       <c r="EJ4" t="n">
         <v>0.01115794498943608</v>
@@ -2786,19 +2786,19 @@
         <v>0.2823721465399683</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2751683226782105</v>
+        <v>0.2751683226782104</v>
       </c>
       <c r="E5" t="n">
         <v>3.05007442285754</v>
       </c>
       <c r="F5" t="n">
-        <v>80.2771846610231</v>
+        <v>80.27718466102294</v>
       </c>
       <c r="G5" t="n">
         <v>176.2278896016975</v>
       </c>
       <c r="H5" t="n">
-        <v>79.86886913329836</v>
+        <v>79.86886913329829</v>
       </c>
       <c r="I5" t="n">
         <v>21.94003474662141</v>
@@ -2807,10 +2807,10 @@
         <v>7.427702411489458</v>
       </c>
       <c r="K5" t="n">
-        <v>30.43728128847773</v>
+        <v>30.43728128847774</v>
       </c>
       <c r="L5" t="n">
-        <v>10.19134887106635</v>
+        <v>10.19134887106634</v>
       </c>
       <c r="M5" t="n">
         <v>1.483570131170016</v>
@@ -2855,10 +2855,10 @@
         <v>1.273148867528968</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.461035997767331</v>
+        <v>8.461035997767326</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2737142751873577</v>
+        <v>0.2737142751873576</v>
       </c>
       <c r="AC5" t="n">
         <v>11.67889802480416</v>
@@ -2876,16 +2876,16 @@
         <v>16.60027697863732</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.4923282737418818</v>
+        <v>0.4923282737418817</v>
       </c>
       <c r="AI5" t="n">
         <v>0.3947914557885837</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9918783317193488</v>
+        <v>0.9918783317193489</v>
       </c>
       <c r="AK5" t="n">
-        <v>4.884572606433907</v>
+        <v>4.884572606433905</v>
       </c>
       <c r="AL5" t="n">
         <v>0.2541057001269997</v>
@@ -2894,25 +2894,25 @@
         <v>0.128007402293116</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.07192437571553253</v>
+        <v>0.07192437571553252</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.1721878050353203</v>
+        <v>0.1721878050353202</v>
       </c>
       <c r="AP5" t="n">
         <v>0.187438978131869</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.4067174542639536</v>
+        <v>0.4067174542639535</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.391574091326177</v>
+        <v>2.391574091326178</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.05347339224858022</v>
+        <v>0.05347339224858023</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.02384596323141613</v>
+        <v>0.02384596323141612</v>
       </c>
       <c r="AU5" t="n">
         <v>0.1177935257651899</v>
@@ -2924,7 +2924,7 @@
         <v>1.450549665498404</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.06922494332878613</v>
+        <v>0.06922494332878612</v>
       </c>
       <c r="AY5" t="n">
         <v>10.44642706198168</v>
@@ -2963,13 +2963,13 @@
         <v>0.001464764886426153</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.116440797995487</v>
+        <v>5.116440797995488</v>
       </c>
       <c r="BL5" t="n">
         <v>0.02333879309684798</v>
       </c>
       <c r="BM5" t="n">
-        <v>7.327267481926658</v>
+        <v>7.327267481926659</v>
       </c>
       <c r="BN5" t="n">
         <v>0.4553056621614988</v>
@@ -2981,7 +2981,7 @@
         <v>0.07761385131896631</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.1291364735771628</v>
+        <v>0.1291364735771629</v>
       </c>
       <c r="BR5" t="n">
         <v>0.1214491488811778</v>
@@ -2990,7 +2990,7 @@
         <v>7.902609448048588</v>
       </c>
       <c r="BT5" t="n">
-        <v>1.557251233588106</v>
+        <v>1.557251233588107</v>
       </c>
       <c r="BU5" t="n">
         <v>1.124091596050999</v>
@@ -2999,7 +2999,7 @@
         <v>1.034836775534601</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.003097117446052132</v>
+        <v>0.003097117446052133</v>
       </c>
       <c r="BX5" t="n">
         <v>0.8277236937358575</v>
@@ -3011,13 +3011,13 @@
         <v>2.983497083838308</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0300500408654918</v>
+        <v>0.03005004086549179</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.09397478314432434</v>
+        <v>0.09397478314432429</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0424041563918169</v>
+        <v>0.04240415639181689</v>
       </c>
       <c r="CD5" t="n">
         <v>0.06961359750017056</v>
@@ -3026,7 +3026,7 @@
         <v>1.489757808396291</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.2793423110584456</v>
+        <v>0.2793423110584455</v>
       </c>
       <c r="CG5" t="n">
         <v>1.031132347386494</v>
@@ -3053,7 +3053,7 @@
         <v>0.07100647611221503</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.5143752206739164</v>
+        <v>0.5143752206739165</v>
       </c>
       <c r="CP5" t="n">
         <v>0.3101308455065021</v>
@@ -3062,13 +3062,13 @@
         <v>0.3906360062656105</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.1350146240585985</v>
+        <v>0.1350146240585984</v>
       </c>
       <c r="CS5" t="n">
         <v>0.0304712767108469</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0655904605156524</v>
+        <v>0.06559046051565239</v>
       </c>
       <c r="CU5" t="n">
         <v>0.04217129168419489</v>
@@ -3080,19 +3080,19 @@
         <v>0.1270951775764464</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.185620187774638</v>
+        <v>1.185620187774639</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.03293331674025695</v>
+        <v>0.03293331674025694</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.08391294348413214</v>
+        <v>0.08391294348413211</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.08509178210180696</v>
+        <v>0.08509178210180697</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.1744340902489995</v>
+        <v>0.1744340902489996</v>
       </c>
       <c r="DC5" t="n">
         <v>0.05241311712866642</v>
@@ -3122,19 +3122,19 @@
         <v>0.2537061034688015</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0773743162037839</v>
+        <v>0.07737431620378392</v>
       </c>
       <c r="DM5" t="n">
         <v>0.04909478044309922</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.007373636042053184</v>
+        <v>0.007373636042053182</v>
       </c>
       <c r="DO5" t="n">
         <v>0.3117246836364982</v>
       </c>
       <c r="DP5" t="n">
-        <v>31.7892804907736</v>
+        <v>31.78928049077359</v>
       </c>
       <c r="DQ5" t="n">
         <v>0.003141751802932435</v>
@@ -3143,16 +3143,16 @@
         <v>0.03031407201012781</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.747472608020344</v>
+        <v>0.7474726080203441</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.5244515198697509</v>
+        <v>0.524451519869751</v>
       </c>
       <c r="DU5" t="n">
         <v>1.485075125507328</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.02222472790999756</v>
+        <v>0.02222472790999755</v>
       </c>
       <c r="DW5" t="n">
         <v>0.1289563043001198</v>
@@ -3161,13 +3161,13 @@
         <v>0.2323648850570762</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.06161345630372915</v>
+        <v>0.06161345630372916</v>
       </c>
       <c r="DZ5" t="n">
         <v>0.04963612267915252</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.1240649131257953</v>
+        <v>0.1240649131257954</v>
       </c>
       <c r="EB5" t="n">
         <v>0.06981645244968782</v>
@@ -3185,7 +3185,7 @@
         <v>0.001125964166005781</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.03011453156453952</v>
+        <v>0.03011453156453951</v>
       </c>
       <c r="EH5" t="n">
         <v>0.01200460420857307</v>
@@ -3285,25 +3285,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>138.9107551105768</v>
+        <v>138.9107551105769</v>
       </c>
       <c r="C6" t="n">
         <v>0.293400146960464</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2832108840463514</v>
+        <v>0.2832108840463513</v>
       </c>
       <c r="E6" t="n">
         <v>3.140448540665858</v>
       </c>
       <c r="F6" t="n">
-        <v>84.78600455617571</v>
+        <v>84.7860045561757</v>
       </c>
       <c r="G6" t="n">
-        <v>186.3067644873689</v>
+        <v>186.3067644873687</v>
       </c>
       <c r="H6" t="n">
-        <v>82.45308225254726</v>
+        <v>82.45308225254723</v>
       </c>
       <c r="I6" t="n">
         <v>23.26167918693907</v>
@@ -3315,13 +3315,13 @@
         <v>31.0882376660685</v>
       </c>
       <c r="L6" t="n">
-        <v>11.24906435751133</v>
+        <v>11.24906435751132</v>
       </c>
       <c r="M6" t="n">
         <v>1.704424547179815</v>
       </c>
       <c r="N6" t="n">
-        <v>7.55527601623914</v>
+        <v>7.555276016239143</v>
       </c>
       <c r="O6" t="n">
         <v>1.22339618336631</v>
@@ -3333,25 +3333,25 @@
         <v>2.710476785423634</v>
       </c>
       <c r="R6" t="n">
-        <v>2.354784592268258</v>
+        <v>2.354784592268257</v>
       </c>
       <c r="S6" t="n">
         <v>1.298498567442569</v>
       </c>
       <c r="T6" t="n">
-        <v>4.205488963910327</v>
+        <v>4.205488963910328</v>
       </c>
       <c r="U6" t="n">
         <v>0.007242617921602908</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4508700182311753</v>
+        <v>0.4508700182311752</v>
       </c>
       <c r="W6" t="n">
         <v>13.28492633742168</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0969538273474753</v>
+        <v>0.09695382734747529</v>
       </c>
       <c r="Y6" t="n">
         <v>1.182735505186204</v>
@@ -3360,7 +3360,7 @@
         <v>1.272867252759339</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.483129903838186</v>
+        <v>8.483129903838181</v>
       </c>
       <c r="AB6" t="n">
         <v>0.2819010151367157</v>
@@ -3375,16 +3375,16 @@
         <v>0.003588195039972816</v>
       </c>
       <c r="AF6" t="n">
-        <v>17.4686910856083</v>
+        <v>17.46869108560829</v>
       </c>
       <c r="AG6" t="n">
         <v>17.20854420664552</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.524400404450782</v>
+        <v>0.5244004044507818</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.4040374514304065</v>
+        <v>0.4040374514304064</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.005831982981693</v>
@@ -3399,7 +3399,7 @@
         <v>0.1191715095418543</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.07691835437345301</v>
+        <v>0.07691835437345299</v>
       </c>
       <c r="AO6" t="n">
         <v>0.1764086078996173</v>
@@ -3411,7 +3411,7 @@
         <v>0.4522850142606717</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.609562577499625</v>
+        <v>2.609562577499626</v>
       </c>
       <c r="AS6" t="n">
         <v>0.05282702229007273</v>
@@ -3429,7 +3429,7 @@
         <v>1.391482071696705</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.07172424205200939</v>
+        <v>0.07172424205200938</v>
       </c>
       <c r="AY6" t="n">
         <v>10.43091333113151</v>
@@ -3444,22 +3444,22 @@
         <v>15.99289045744803</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.313606941531643</v>
+        <v>2.313606941531642</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.872087524962005</v>
+        <v>9.872087524962</v>
       </c>
       <c r="BE6" t="n">
         <v>0.1671511568142818</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.2872729529123516</v>
+        <v>0.2872729529123517</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.3395348092814298</v>
+        <v>0.3395348092814299</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.493469907462323</v>
+        <v>4.493469907462325</v>
       </c>
       <c r="BI6" t="n">
         <v>0.1611237707939304</v>
@@ -3468,7 +3468,7 @@
         <v>0.06901069494365654</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.33061455553134</v>
+        <v>6.330614555531341</v>
       </c>
       <c r="BL6" t="n">
         <v>0.02638569740257364</v>
@@ -3477,7 +3477,7 @@
         <v>7.903251992633487</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.4975013469952059</v>
+        <v>0.4975013469952058</v>
       </c>
       <c r="BO6" t="n">
         <v>0.02001253943170417</v>
@@ -3492,13 +3492,13 @@
         <v>0.1413930321958507</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.485819198539785</v>
+        <v>8.485819198539783</v>
       </c>
       <c r="BT6" t="n">
         <v>1.529452863138731</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.192844090757994</v>
+        <v>1.192844090757993</v>
       </c>
       <c r="BV6" t="n">
         <v>1.085565508241997</v>
@@ -3513,16 +3513,16 @@
         <v>0.02975289941221304</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.843440586894289</v>
+        <v>3.84344058689429</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.03005228732961068</v>
+        <v>0.03005228732961067</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.09605444856752919</v>
+        <v>0.0960544485675292</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.04513619269068152</v>
+        <v>0.04513619269068151</v>
       </c>
       <c r="CD6" t="n">
         <v>0.07423969407071399</v>
@@ -3555,13 +3555,13 @@
         <v>0.009866529866840737</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0789817644728991</v>
+        <v>0.07898176447289912</v>
       </c>
       <c r="CO6" t="n">
         <v>0.547505922225374</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.3552305710103723</v>
+        <v>0.3552305710103722</v>
       </c>
       <c r="CQ6" t="n">
         <v>0.4343755437320184</v>
@@ -3570,7 +3570,7 @@
         <v>0.1517260826395599</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.03234292294534802</v>
+        <v>0.03234292294534803</v>
       </c>
       <c r="CT6" t="n">
         <v>0.06379327013865763</v>
@@ -3579,7 +3579,7 @@
         <v>0.0440196897631256</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.08873556071103901</v>
+        <v>0.088735560711039</v>
       </c>
       <c r="CW6" t="n">
         <v>0.1486729527400232</v>
@@ -3588,13 +3588,13 @@
         <v>1.222992513548709</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.03026795626806313</v>
+        <v>0.03026795626806312</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.08677815452498971</v>
+        <v>0.0867781545249897</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.08899277775636993</v>
+        <v>0.08899277775636995</v>
       </c>
       <c r="DB6" t="n">
         <v>0.1950489091557717</v>
@@ -3612,7 +3612,7 @@
         <v>0.1365429156878438</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.046169947757326</v>
+        <v>2.046169947757327</v>
       </c>
       <c r="DH6" t="n">
         <v>0.1590557354306156</v>
@@ -3627,7 +3627,7 @@
         <v>0.2649255518145582</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.08321588227671042</v>
+        <v>0.08321588227671044</v>
       </c>
       <c r="DM6" t="n">
         <v>0.03831377203608224</v>
@@ -3639,7 +3639,7 @@
         <v>0.3285180159785941</v>
       </c>
       <c r="DP6" t="n">
-        <v>32.17709875680911</v>
+        <v>32.17709875680912</v>
       </c>
       <c r="DQ6" t="n">
         <v>0.003450053047126204</v>
@@ -3648,10 +3648,10 @@
         <v>0.03149768479291225</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.7737824462692393</v>
+        <v>0.7737824462692394</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.5934844138698825</v>
+        <v>0.5934844138698824</v>
       </c>
       <c r="DU6" t="n">
         <v>1.461966189397994</v>
@@ -3666,7 +3666,7 @@
         <v>0.2507387602561719</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.06199284811417847</v>
+        <v>0.06199284811417845</v>
       </c>
       <c r="DZ6" t="n">
         <v>0.0501850110011607</v>
@@ -3790,7 +3790,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>194.151639272085</v>
+        <v>194.1516392720852</v>
       </c>
       <c r="C7" t="n">
         <v>0.2667038225776687</v>
@@ -3802,52 +3802,52 @@
         <v>3.965933975606093</v>
       </c>
       <c r="F7" t="n">
-        <v>114.8174438999059</v>
+        <v>114.8174438999057</v>
       </c>
       <c r="G7" t="n">
-        <v>256.1877228197561</v>
+        <v>256.1877228197559</v>
       </c>
       <c r="H7" t="n">
         <v>124.7777434740009</v>
       </c>
       <c r="I7" t="n">
-        <v>33.77244137235143</v>
+        <v>33.77244137235142</v>
       </c>
       <c r="J7" t="n">
         <v>8.242559425032638</v>
       </c>
       <c r="K7" t="n">
-        <v>57.4690929654988</v>
+        <v>57.46909296549883</v>
       </c>
       <c r="L7" t="n">
-        <v>10.98161037407189</v>
+        <v>10.9816103740719</v>
       </c>
       <c r="M7" t="n">
         <v>1.306216968593031</v>
       </c>
       <c r="N7" t="n">
-        <v>9.513785607318365</v>
+        <v>9.51378560731837</v>
       </c>
       <c r="O7" t="n">
-        <v>2.546278938749802</v>
+        <v>2.546278938749803</v>
       </c>
       <c r="P7" t="n">
-        <v>1.393755151468505</v>
+        <v>1.393755151468504</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.492957760679431</v>
+        <v>2.49295776067943</v>
       </c>
       <c r="R7" t="n">
-        <v>2.119350125178392</v>
+        <v>2.119350125178393</v>
       </c>
       <c r="S7" t="n">
         <v>1.42281766388067</v>
       </c>
       <c r="T7" t="n">
-        <v>5.342620371404053</v>
+        <v>5.342620371404054</v>
       </c>
       <c r="U7" t="n">
-        <v>0.008029102087370066</v>
+        <v>0.008029102087370064</v>
       </c>
       <c r="V7" t="n">
         <v>0.4570617448494493</v>
@@ -3862,7 +3862,7 @@
         <v>1.718455520972461</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.019367190466019</v>
+        <v>1.019367190466018</v>
       </c>
       <c r="AA7" t="n">
         <v>11.64739412202549</v>
@@ -3874,13 +3874,13 @@
         <v>11.25688282684747</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.02201268354412861</v>
+        <v>0.0220126835441286</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.003848826448934269</v>
+        <v>0.003848826448934268</v>
       </c>
       <c r="AF7" t="n">
-        <v>25.25621865479845</v>
+        <v>25.25621865479846</v>
       </c>
       <c r="AG7" t="n">
         <v>20.63281995978072</v>
@@ -3889,31 +3889,31 @@
         <v>0.6519480739457217</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.6411577324587679</v>
+        <v>0.6411577324587681</v>
       </c>
       <c r="AJ7" t="n">
         <v>0.871287569414619</v>
       </c>
       <c r="AK7" t="n">
-        <v>7.829584069477385</v>
+        <v>7.829584069477383</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.2461904830187607</v>
+        <v>0.2461904830187608</v>
       </c>
       <c r="AM7" t="n">
         <v>0.1221383251849412</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.08964487121806783</v>
+        <v>0.08964487121806781</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.3042331661468078</v>
+        <v>0.3042331661468077</v>
       </c>
       <c r="AP7" t="n">
         <v>0.2617842114919788</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.6343909191249648</v>
+        <v>0.6343909191249647</v>
       </c>
       <c r="AR7" t="n">
         <v>2.677117644914224</v>
@@ -3928,28 +3928,28 @@
         <v>0.1320588053423496</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.43832806298074</v>
+        <v>1.438328062980739</v>
       </c>
       <c r="AW7" t="n">
         <v>1.92071142654928</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.09423983597398895</v>
+        <v>0.09423983597398898</v>
       </c>
       <c r="AY7" t="n">
-        <v>13.97551201437594</v>
+        <v>13.97551201437595</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.2450922242550073</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.03724214220896254</v>
+        <v>0.03724214220896253</v>
       </c>
       <c r="BB7" t="n">
-        <v>17.95847260667808</v>
+        <v>17.95847260667807</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.187641228870548</v>
+        <v>3.187641228870546</v>
       </c>
       <c r="BD7" t="n">
         <v>10.03581358518788</v>
@@ -3964,16 +3964,16 @@
         <v>0.4708188409610112</v>
       </c>
       <c r="BH7" t="n">
-        <v>5.723073238377641</v>
+        <v>5.72307323837764</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.2134939924609449</v>
+        <v>0.213493992460945</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.05376276517055965</v>
       </c>
       <c r="BK7" t="n">
-        <v>7.399709940914341</v>
+        <v>7.399709940914338</v>
       </c>
       <c r="BL7" t="n">
         <v>0.03098704064161814</v>
@@ -3988,7 +3988,7 @@
         <v>0.01846585708739965</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.08908526987208795</v>
+        <v>0.08908526987208798</v>
       </c>
       <c r="BQ7" t="n">
         <v>0.19738497455833</v>
@@ -3997,22 +3997,22 @@
         <v>0.08423041061347662</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.325951313710425</v>
+        <v>9.325951313710423</v>
       </c>
       <c r="BT7" t="n">
         <v>1.692623474689338</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.532561732471719</v>
+        <v>1.532561732471718</v>
       </c>
       <c r="BV7" t="n">
         <v>1.846020041719575</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.004259290025562681</v>
+        <v>0.00425929002556268</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.7210479262269718</v>
+        <v>0.7210479262269717</v>
       </c>
       <c r="BY7" t="n">
         <v>0.02458791186260376</v>
@@ -4030,7 +4030,7 @@
         <v>0.05645308277290648</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0798513887028172</v>
+        <v>0.07985138870281719</v>
       </c>
       <c r="CE7" t="n">
         <v>2.295126493131328</v>
@@ -4060,7 +4060,7 @@
         <v>0.007703465989920754</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0661880222322547</v>
+        <v>0.06618802223225471</v>
       </c>
       <c r="CO7" t="n">
         <v>1.047038876766988</v>
@@ -4069,16 +4069,16 @@
         <v>0.2354046684687308</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.526436357666917</v>
+        <v>0.5264363576669171</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.2222941311482098</v>
+        <v>0.2222941311482099</v>
       </c>
       <c r="CS7" t="n">
         <v>0.02952461267833622</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.07879256798772688</v>
+        <v>0.07879256798772689</v>
       </c>
       <c r="CU7" t="n">
         <v>0.05254094076605902</v>
@@ -4096,10 +4096,10 @@
         <v>0.04171847545225149</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.0719286157344896</v>
+        <v>0.07192861573448958</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.09096147026331741</v>
+        <v>0.0909614702633174</v>
       </c>
       <c r="DB7" t="n">
         <v>0.2118829204142719</v>
@@ -4108,16 +4108,16 @@
         <v>0.07434707124724474</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.5454465916869444</v>
+        <v>0.5454465916869446</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.004251327832597966</v>
+        <v>0.004251327832597968</v>
       </c>
       <c r="DF7" t="n">
         <v>0.127847943131365</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.533085339715601</v>
+        <v>2.5330853397156</v>
       </c>
       <c r="DH7" t="n">
         <v>0.1605354300777937</v>
@@ -4144,7 +4144,7 @@
         <v>0.3152239826089193</v>
       </c>
       <c r="DP7" t="n">
-        <v>46.04880265413406</v>
+        <v>46.04880265413408</v>
       </c>
       <c r="DQ7" t="n">
         <v>0.002952993191651033</v>
@@ -4186,7 +4186,7 @@
         <v>1.245697752333134</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.004853588503155312</v>
+        <v>0.004853588503155313</v>
       </c>
       <c r="EE7" t="n">
         <v>0.02383153798852696</v>
@@ -4204,7 +4204,7 @@
         <v>0.01134515014671978</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.00810186846056858</v>
+        <v>0.008101868460568578</v>
       </c>
       <c r="EK7" t="inlineStr">
         <is>
@@ -4295,19 +4295,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>201.8798627229508</v>
+        <v>201.8798627229507</v>
       </c>
       <c r="C8" t="n">
         <v>0.3708542998708332</v>
       </c>
       <c r="D8" t="n">
-        <v>0.414612277420582</v>
+        <v>0.4146122774205819</v>
       </c>
       <c r="E8" t="n">
         <v>5.111053464292809</v>
       </c>
       <c r="F8" t="n">
-        <v>119.8186726907255</v>
+        <v>119.8186726907256</v>
       </c>
       <c r="G8" t="n">
         <v>272.7578975486281</v>
@@ -4328,34 +4328,34 @@
         <v>16.70952615798391</v>
       </c>
       <c r="M8" t="n">
-        <v>2.609410905571941</v>
+        <v>2.609410905571942</v>
       </c>
       <c r="N8" t="n">
         <v>11.28547886339388</v>
       </c>
       <c r="O8" t="n">
-        <v>2.624838174111786</v>
+        <v>2.624838174111785</v>
       </c>
       <c r="P8" t="n">
-        <v>2.595010764878984</v>
+        <v>2.595010764878985</v>
       </c>
       <c r="Q8" t="n">
         <v>4.345404085764374</v>
       </c>
       <c r="R8" t="n">
-        <v>3.484594297209452</v>
+        <v>3.484594297209453</v>
       </c>
       <c r="S8" t="n">
         <v>2.007546775665482</v>
       </c>
       <c r="T8" t="n">
-        <v>6.275997977658263</v>
+        <v>6.275997977658265</v>
       </c>
       <c r="U8" t="n">
         <v>0.01421632689862126</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6809541129387651</v>
+        <v>0.6809541129387652</v>
       </c>
       <c r="W8" t="n">
         <v>27.94648952835622</v>
@@ -4373,10 +4373,10 @@
         <v>13.82307798420801</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3880931541475546</v>
+        <v>0.3880931541475547</v>
       </c>
       <c r="AC8" t="n">
-        <v>16.07264247295189</v>
+        <v>16.07264247295188</v>
       </c>
       <c r="AD8" t="n">
         <v>0.02475228135865733</v>
@@ -4385,22 +4385,22 @@
         <v>0.004973013323210912</v>
       </c>
       <c r="AF8" t="n">
-        <v>24.93245450968369</v>
+        <v>24.93245450968368</v>
       </c>
       <c r="AG8" t="n">
-        <v>22.82971557122242</v>
+        <v>22.82971557122241</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.9080652564049164</v>
+        <v>0.9080652564049163</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.7572241846316827</v>
+        <v>0.7572241846316826</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.509803313929873</v>
       </c>
       <c r="AK8" t="n">
-        <v>8.877646078700112</v>
+        <v>8.87764607870011</v>
       </c>
       <c r="AL8" t="n">
         <v>0.3625580352376093</v>
@@ -4418,10 +4418,10 @@
         <v>0.2795976787246109</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.748219309996074</v>
+        <v>0.7482193099960742</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.98748497355034</v>
+        <v>3.987484973550339</v>
       </c>
       <c r="AS8" t="n">
         <v>0.08873367081491138</v>
@@ -4433,13 +4433,13 @@
         <v>0.1752237885382232</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.930628058364659</v>
+        <v>1.93062805836466</v>
       </c>
       <c r="AW8" t="n">
         <v>2.869615408585643</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.1141804246804436</v>
+        <v>0.1141804246804437</v>
       </c>
       <c r="AY8" t="n">
         <v>17.96573575479981</v>
@@ -4451,10 +4451,10 @@
         <v>0.04582945961866256</v>
       </c>
       <c r="BB8" t="n">
-        <v>20.96259668949901</v>
+        <v>20.962596689499</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.529625996694258</v>
+        <v>3.529625996694259</v>
       </c>
       <c r="BD8" t="n">
         <v>16.06705389282984</v>
@@ -4478,16 +4478,16 @@
         <v>0.001914501756733634</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.355906746750128</v>
+        <v>7.355906746750127</v>
       </c>
       <c r="BL8" t="n">
         <v>0.03868091963561889</v>
       </c>
       <c r="BM8" t="n">
-        <v>11.95210472771456</v>
+        <v>11.95210472771455</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.8187225122042263</v>
+        <v>0.8187225122042264</v>
       </c>
       <c r="BO8" t="n">
         <v>0.02308263269414841</v>
@@ -4499,13 +4499,13 @@
         <v>0.2467115810174386</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.1252464557861829</v>
+        <v>0.125246455786183</v>
       </c>
       <c r="BS8" t="n">
         <v>12.30330279162969</v>
       </c>
       <c r="BT8" t="n">
-        <v>2.454007711288745</v>
+        <v>2.454007711288746</v>
       </c>
       <c r="BU8" t="n">
         <v>1.845931244623013</v>
@@ -4532,10 +4532,10 @@
         <v>0.172450482390894</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.05996261523613867</v>
+        <v>0.05996261523613866</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.1213628338173828</v>
+        <v>0.1213628338173827</v>
       </c>
       <c r="CE8" t="n">
         <v>2.836273562241487</v>
@@ -4553,7 +4553,7 @@
         <v>0.06405938961350206</v>
       </c>
       <c r="CJ8" t="n">
-        <v>3.858926552936151</v>
+        <v>3.858926552936152</v>
       </c>
       <c r="CK8" t="n">
         <v>0.003273376945760464</v>
@@ -4610,10 +4610,10 @@
         <v>0.2763567556601654</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.07662703355413207</v>
+        <v>0.07662703355413206</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.6746552088366979</v>
+        <v>0.6746552088366982</v>
       </c>
       <c r="DE8" t="n">
         <v>0.004122180173029886</v>
@@ -4622,16 +4622,16 @@
         <v>0.1992849557385708</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.98665230004814</v>
+        <v>2.986652300048139</v>
       </c>
       <c r="DH8" t="n">
         <v>0.2082352219279814</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.04874797363411497</v>
+        <v>0.04874797363411498</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.02220003525830457</v>
+        <v>0.02220003525830456</v>
       </c>
       <c r="DK8" t="n">
         <v>0.4026607505222828</v>
@@ -4640,7 +4640,7 @@
         <v>0.1109691571948775</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.1010451866933928</v>
+        <v>0.1010451866933929</v>
       </c>
       <c r="DN8" t="n">
         <v>0.01214372176951727</v>
@@ -4652,7 +4652,7 @@
         <v>55.72667963150799</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.003706840233057956</v>
+        <v>0.003706840233057957</v>
       </c>
       <c r="DR8" t="n">
         <v>0.03907891452627016</v>
@@ -4661,7 +4661,7 @@
         <v>1.20360330990213</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.7209948920584399</v>
+        <v>0.7209948920584398</v>
       </c>
       <c r="DU8" t="n">
         <v>2.189695759365872</v>
@@ -4703,7 +4703,7 @@
         <v>0.03897989604584059</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.01854040489564004</v>
+        <v>0.01854040489564003</v>
       </c>
       <c r="EI8" t="n">
         <v>0.01689575553735463</v>
@@ -4806,7 +4806,7 @@
         <v>0.3063499146037666</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3471933041993002</v>
+        <v>0.3471933041993003</v>
       </c>
       <c r="E9" t="n">
         <v>4.347833332192387</v>
@@ -4815,10 +4815,10 @@
         <v>105.0651197106895</v>
       </c>
       <c r="G9" t="n">
-        <v>232.3532486181908</v>
+        <v>232.3532486181905</v>
       </c>
       <c r="H9" t="n">
-        <v>107.148589941707</v>
+        <v>107.1485899417069</v>
       </c>
       <c r="I9" t="n">
         <v>27.93061303722451</v>
@@ -4827,10 +4827,10 @@
         <v>10.46176393707282</v>
       </c>
       <c r="K9" t="n">
-        <v>42.47196063001723</v>
+        <v>42.47196063001724</v>
       </c>
       <c r="L9" t="n">
-        <v>14.11412453167333</v>
+        <v>14.11412453167334</v>
       </c>
       <c r="M9" t="n">
         <v>2.100707647950022</v>
@@ -4845,16 +4845,16 @@
         <v>2.070685091602589</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.57369900390397</v>
+        <v>3.573699003903969</v>
       </c>
       <c r="R9" t="n">
-        <v>2.827651824938836</v>
+        <v>2.827651824938837</v>
       </c>
       <c r="S9" t="n">
-        <v>1.75485320519029</v>
+        <v>1.754853205190291</v>
       </c>
       <c r="T9" t="n">
-        <v>5.405688715368904</v>
+        <v>5.405688715368903</v>
       </c>
       <c r="U9" t="n">
         <v>0.01221880300543068</v>
@@ -4875,37 +4875,37 @@
         <v>1.548266336633656</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.70090422757791</v>
+        <v>11.7009042275779</v>
       </c>
       <c r="AB9" t="n">
         <v>0.3325835564324551</v>
       </c>
       <c r="AC9" t="n">
-        <v>13.59756969944152</v>
+        <v>13.59756969944153</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.02296699809063353</v>
+        <v>0.02296699809063352</v>
       </c>
       <c r="AE9" t="n">
         <v>0.004464987007377502</v>
       </c>
       <c r="AF9" t="n">
-        <v>21.48656101137113</v>
+        <v>21.48656101137114</v>
       </c>
       <c r="AG9" t="n">
-        <v>21.43984896650021</v>
+        <v>21.43984896650022</v>
       </c>
       <c r="AH9" t="n">
         <v>0.7702546375485593</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.616061431060507</v>
+        <v>0.6160614310605071</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.309335653968299</v>
       </c>
       <c r="AK9" t="n">
-        <v>7.821808437450234</v>
+        <v>7.821808437450235</v>
       </c>
       <c r="AL9" t="n">
         <v>0.3012688587454552</v>
@@ -4917,13 +4917,13 @@
         <v>0.1068655491495173</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.2227248899821784</v>
+        <v>0.2227248899821783</v>
       </c>
       <c r="AP9" t="n">
         <v>0.2313455560769902</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.5958331305680666</v>
+        <v>0.5958331305680664</v>
       </c>
       <c r="AR9" t="n">
         <v>3.47230724128306</v>
@@ -4941,7 +4941,7 @@
         <v>1.605262706341932</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.386200930552843</v>
+        <v>2.386200930552842</v>
       </c>
       <c r="AX9" t="n">
         <v>0.1007247446415135</v>
@@ -4950,13 +4950,13 @@
         <v>15.27050302327962</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.2838122522826749</v>
+        <v>0.2838122522826748</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.03741265908861737</v>
+        <v>0.03741265908861736</v>
       </c>
       <c r="BB9" t="n">
-        <v>17.07160064407506</v>
+        <v>17.07160064407507</v>
       </c>
       <c r="BC9" t="n">
         <v>3.022402348416372</v>
@@ -4971,13 +4971,13 @@
         <v>0.3114356260656577</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.4742208117594475</v>
+        <v>0.4742208117594476</v>
       </c>
       <c r="BH9" t="n">
         <v>6.780125415666087</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.2289473495324237</v>
+        <v>0.2289473495324238</v>
       </c>
       <c r="BJ9" t="n">
         <v>0.07419645851843938</v>
@@ -4992,7 +4992,7 @@
         <v>10.37326415855205</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.6956189370261473</v>
+        <v>0.6956189370261474</v>
       </c>
       <c r="BO9" t="n">
         <v>0.01936245314165293</v>
@@ -5025,7 +5025,7 @@
         <v>1.112894457142302</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0435268604477771</v>
+        <v>0.04352686044777709</v>
       </c>
       <c r="BZ9" t="n">
         <v>2.722560404665681</v>
@@ -5037,16 +5037,16 @@
         <v>0.1495194092891474</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.05164878148660471</v>
+        <v>0.05164878148660472</v>
       </c>
       <c r="CD9" t="n">
         <v>0.09843462988138479</v>
       </c>
       <c r="CE9" t="n">
-        <v>2.417174992534312</v>
+        <v>2.417174992534311</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.4822571045037669</v>
+        <v>0.4822571045037668</v>
       </c>
       <c r="CG9" t="n">
         <v>1.523997908334917</v>
@@ -5058,7 +5058,7 @@
         <v>0.04268201319381001</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.841505409250779</v>
+        <v>2.841505409250778</v>
       </c>
       <c r="CK9" t="n">
         <v>0.002922508202888128</v>
@@ -5067,7 +5067,7 @@
         <v>0.1982915449839802</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.009981556220991629</v>
+        <v>0.009981556220991632</v>
       </c>
       <c r="CN9" t="n">
         <v>0.09697468775771055</v>
@@ -5082,13 +5082,13 @@
         <v>0.4937780148965236</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.2342655673948318</v>
+        <v>0.2342655673948319</v>
       </c>
       <c r="CS9" t="n">
         <v>0.04176296972431984</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.08387857574106961</v>
+        <v>0.08387857574106962</v>
       </c>
       <c r="CU9" t="n">
         <v>0.06733240946347598</v>
@@ -5106,16 +5106,16 @@
         <v>0.04176760800081346</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.09895297046330494</v>
+        <v>0.09895297046330495</v>
       </c>
       <c r="DA9" t="n">
         <v>0.1206008450221609</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.2348720174067936</v>
+        <v>0.2348720174067935</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.07030848800768889</v>
+        <v>0.07030848800768888</v>
       </c>
       <c r="DD9" t="n">
         <v>0.5943378617017551</v>
@@ -5127,7 +5127,7 @@
         <v>0.1644904701363574</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.493604682163041</v>
+        <v>2.493604682163042</v>
       </c>
       <c r="DH9" t="n">
         <v>0.2008420096765616</v>
@@ -5145,7 +5145,7 @@
         <v>0.09223783201410281</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.07422423305444273</v>
+        <v>0.07422423305444274</v>
       </c>
       <c r="DN9" t="n">
         <v>0.01091425179289844</v>
@@ -5184,7 +5184,7 @@
         <v>0.09341260844929498</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.06669857174586101</v>
+        <v>0.066698571745861</v>
       </c>
       <c r="EA9" t="n">
         <v>0.1623325715634387</v>
@@ -5305,7 +5305,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>176.5021655182093</v>
+        <v>176.5021655182092</v>
       </c>
       <c r="C10" t="n">
         <v>0.3400807864308382</v>
@@ -5335,13 +5335,13 @@
         <v>43.1574878017832</v>
       </c>
       <c r="L10" t="n">
-        <v>15.01617979942496</v>
+        <v>15.01617979942495</v>
       </c>
       <c r="M10" t="n">
         <v>2.368011853405704</v>
       </c>
       <c r="N10" t="n">
-        <v>9.33233755707219</v>
+        <v>9.332337557072192</v>
       </c>
       <c r="O10" t="n">
         <v>2.061607512407088</v>
@@ -5350,7 +5350,7 @@
         <v>2.301921450679949</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.825545655808234</v>
+        <v>2.825545655808233</v>
       </c>
       <c r="R10" t="n">
         <v>3.247249273668731</v>
@@ -5359,13 +5359,13 @@
         <v>1.750947455166642</v>
       </c>
       <c r="T10" t="n">
-        <v>5.517800802999914</v>
+        <v>5.517800802999912</v>
       </c>
       <c r="U10" t="n">
         <v>0.01234384443198804</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6081992116069271</v>
+        <v>0.608199211606927</v>
       </c>
       <c r="W10" t="n">
         <v>21.71390926757909</v>
@@ -5374,7 +5374,7 @@
         <v>0.1492579475560332</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.558999231146298</v>
+        <v>1.558999231146299</v>
       </c>
       <c r="Z10" t="n">
         <v>1.777768147733415</v>
@@ -5401,16 +5401,16 @@
         <v>19.98986465302142</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.772884028590574</v>
+        <v>0.7728840285905739</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.6343336691637605</v>
+        <v>0.6343336691637602</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.323740422266948</v>
       </c>
       <c r="AK10" t="n">
-        <v>8.01017499815722</v>
+        <v>8.010174998157218</v>
       </c>
       <c r="AL10" t="n">
         <v>0.3067471673055576</v>
@@ -5425,13 +5425,13 @@
         <v>0.2281883559689881</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.2370927516089912</v>
+        <v>0.2370927516089911</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.6785166683249233</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.583910071131088</v>
+        <v>3.583910071131089</v>
       </c>
       <c r="AS10" t="n">
         <v>0.08492990995005055</v>
@@ -5446,46 +5446,46 @@
         <v>1.900433259945865</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.29076323595778</v>
+        <v>2.290763235957779</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0977172567010372</v>
+        <v>0.09771725670103719</v>
       </c>
       <c r="AY10" t="n">
-        <v>15.04962773666825</v>
+        <v>15.04962773666824</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.2892103106972123</v>
+        <v>0.2892103106972124</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.03967442793739956</v>
+        <v>0.03967442793739957</v>
       </c>
       <c r="BB10" t="n">
         <v>17.05811283337796</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.114295236810142</v>
+        <v>3.114295236810141</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.54418936305817</v>
+        <v>14.54418936305818</v>
       </c>
       <c r="BE10" t="n">
         <v>0.1961996114879743</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.3236855746377045</v>
+        <v>0.3236855746377046</v>
       </c>
       <c r="BG10" t="n">
         <v>0.4308885404772455</v>
       </c>
       <c r="BH10" t="n">
-        <v>6.767072585146675</v>
+        <v>6.767072585146674</v>
       </c>
       <c r="BI10" t="n">
         <v>0.203477773626796</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.005398043655014137</v>
+        <v>0.005398043655014138</v>
       </c>
       <c r="BK10" t="n">
         <v>6.585760931303153</v>
@@ -5506,7 +5506,7 @@
         <v>0.1140930164639797</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.202760139104235</v>
+        <v>0.2027601391042351</v>
       </c>
       <c r="BR10" t="n">
         <v>0.1145132670706833</v>
@@ -5527,7 +5527,7 @@
         <v>0.003714001496067616</v>
       </c>
       <c r="BX10" t="n">
-        <v>1.144149575341082</v>
+        <v>1.144149575341083</v>
       </c>
       <c r="BY10" t="n">
         <v>0.04438819765351257</v>
@@ -5536,10 +5536,10 @@
         <v>3.381800307865367</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.03891491276865705</v>
+        <v>0.03891491276865704</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.1368358099157079</v>
+        <v>0.1368358099157078</v>
       </c>
       <c r="CC10" t="n">
         <v>0.05421839837363157</v>
@@ -5551,13 +5551,13 @@
         <v>2.42674827254095</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.4533326189723014</v>
+        <v>0.4533326189723015</v>
       </c>
       <c r="CG10" t="n">
         <v>1.712259097160009</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.1846386056041956</v>
+        <v>0.1846386056041955</v>
       </c>
       <c r="CI10" t="n">
         <v>0.05535813023685163</v>
@@ -5572,19 +5572,19 @@
         <v>0.1844169951137988</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.01051261112679135</v>
+        <v>0.01051261112679136</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.1009982068395509</v>
+        <v>0.100998206839551</v>
       </c>
       <c r="CO10" t="n">
         <v>0.7292431431132188</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.3998182305580217</v>
+        <v>0.3998182305580216</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.5207285228083588</v>
+        <v>0.5207285228083589</v>
       </c>
       <c r="CR10" t="n">
         <v>0.2364135732087782</v>
@@ -5593,10 +5593,10 @@
         <v>0.04237198931489834</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.08982486574616702</v>
+        <v>0.08982486574616701</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.06364515952936124</v>
+        <v>0.06364515952936126</v>
       </c>
       <c r="CV10" t="n">
         <v>0.1170801533123453</v>
@@ -5608,7 +5608,7 @@
         <v>1.728692986257528</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.04215617076575474</v>
+        <v>0.04215617076575475</v>
       </c>
       <c r="CZ10" t="n">
         <v>0.1038573560059444</v>
@@ -5623,7 +5623,7 @@
         <v>0.06896695079849764</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.6000502950882362</v>
+        <v>0.6000502950882363</v>
       </c>
       <c r="DE10" t="n">
         <v>0.003616053275144071</v>
@@ -5632,7 +5632,7 @@
         <v>0.173817803058287</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.608279296657933</v>
+        <v>2.608279296657932</v>
       </c>
       <c r="DH10" t="n">
         <v>0.1877492120083748</v>
@@ -5644,13 +5644,13 @@
         <v>0.02051908463940784</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.3580528216494313</v>
+        <v>0.3580528216494314</v>
       </c>
       <c r="DL10" t="n">
         <v>0.09876486462459264</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.08741121325958066</v>
+        <v>0.08741121325958065</v>
       </c>
       <c r="DN10" t="n">
         <v>0.009588173482431657</v>
@@ -5665,16 +5665,16 @@
         <v>0.003262975951645978</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.03915343791191977</v>
+        <v>0.03915343791191978</v>
       </c>
       <c r="DS10" t="n">
         <v>1.065343571167971</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.7190629827271918</v>
+        <v>0.7190629827271917</v>
       </c>
       <c r="DU10" t="n">
-        <v>1.997007496237452</v>
+        <v>1.997007496237453</v>
       </c>
       <c r="DV10" t="n">
         <v>0.02921254809571045</v>
@@ -5695,13 +5695,13 @@
         <v>0.1674564070302692</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.09868430853697012</v>
+        <v>0.09868430853697009</v>
       </c>
       <c r="EC10" t="n">
         <v>1.704248274815274</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.003039443326098781</v>
+        <v>0.00303944332609878</v>
       </c>
       <c r="EE10" t="n">
         <v>0.0286921302474362</v>
@@ -5822,10 +5822,10 @@
         <v>5.348680764520734</v>
       </c>
       <c r="F11" t="n">
-        <v>107.1511386458313</v>
+        <v>107.1511386458312</v>
       </c>
       <c r="G11" t="n">
-        <v>277.1407638493974</v>
+        <v>277.1407638493976</v>
       </c>
       <c r="H11" t="n">
         <v>104.1523720523613</v>
@@ -5840,10 +5840,10 @@
         <v>37.93758004013361</v>
       </c>
       <c r="L11" t="n">
-        <v>17.19123215896572</v>
+        <v>17.19123215896571</v>
       </c>
       <c r="M11" t="n">
-        <v>2.733202960559169</v>
+        <v>2.733202960559168</v>
       </c>
       <c r="N11" t="n">
         <v>10.29327721599667</v>
@@ -5852,19 +5852,19 @@
         <v>2.165748760732103</v>
       </c>
       <c r="P11" t="n">
-        <v>2.732038197793637</v>
+        <v>2.732038197793636</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.32100745527604</v>
+        <v>4.321007455276041</v>
       </c>
       <c r="R11" t="n">
         <v>3.585612856636332</v>
       </c>
       <c r="S11" t="n">
-        <v>2.033171827422394</v>
+        <v>2.033171827422393</v>
       </c>
       <c r="T11" t="n">
-        <v>6.779577136475652</v>
+        <v>6.779577136475654</v>
       </c>
       <c r="U11" t="n">
         <v>0.0141786890133055</v>
@@ -5891,34 +5891,34 @@
         <v>0.3818549328205632</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.56965801981578</v>
+        <v>16.56965801981577</v>
       </c>
       <c r="AD11" t="n">
         <v>0.02220517251655242</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.005079442183379284</v>
+        <v>0.005079442183379286</v>
       </c>
       <c r="AF11" t="n">
-        <v>26.13462266820759</v>
+        <v>26.1346226682076</v>
       </c>
       <c r="AG11" t="n">
-        <v>18.40901245093401</v>
+        <v>18.409012450934</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.8898760548571359</v>
+        <v>0.8898760548571358</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.706108520593674</v>
+        <v>0.7061085205936739</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.498336159672435</v>
+        <v>1.498336159672434</v>
       </c>
       <c r="AK11" t="n">
-        <v>9.004934032311969</v>
+        <v>9.004934032311967</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.3671450306366577</v>
+        <v>0.3671450306366576</v>
       </c>
       <c r="AM11" t="n">
         <v>0.1763758135510166</v>
@@ -5933,19 +5933,19 @@
         <v>0.3337879722522906</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.7753307415839777</v>
+        <v>0.775330741583978</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.18555492402009</v>
+        <v>4.185554924020091</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.09633633359715216</v>
+        <v>0.09633633359715214</v>
       </c>
       <c r="AT11" t="n">
         <v>0.0364376929739617</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1677984888185559</v>
+        <v>0.167798488818556</v>
       </c>
       <c r="AV11" t="n">
         <v>1.959481859451967</v>
@@ -5966,10 +5966,10 @@
         <v>0.04477268194484697</v>
       </c>
       <c r="BB11" t="n">
-        <v>18.58251270403408</v>
+        <v>18.58251270403407</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.3002678333294</v>
+        <v>3.300267833329399</v>
       </c>
       <c r="BD11" t="n">
         <v>17.56714647826358</v>
@@ -5978,13 +5978,13 @@
         <v>0.2206493916154403</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.3804854728963058</v>
+        <v>0.3804854728963059</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.5075893048054007</v>
+        <v>0.5075893048054004</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.603990588882167</v>
+        <v>7.603990588882166</v>
       </c>
       <c r="BI11" t="n">
         <v>0.246010848986166</v>
@@ -6002,7 +6002,7 @@
         <v>12.56411846965583</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.7551802154687057</v>
+        <v>0.7551802154687061</v>
       </c>
       <c r="BO11" t="n">
         <v>0.02271194402430413</v>
@@ -6035,7 +6035,7 @@
         <v>1.28495243082631</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.05411597128455276</v>
+        <v>0.05411597128455277</v>
       </c>
       <c r="BZ11" t="n">
         <v>3.55020619353806</v>
@@ -6044,16 +6044,16 @@
         <v>0.04371732745194583</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.1608264319618945</v>
+        <v>0.1608264319618944</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0597099427937756</v>
+        <v>0.05970994279377561</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.1637941294357921</v>
+        <v>0.1637941294357922</v>
       </c>
       <c r="CE11" t="n">
-        <v>3.133742684470829</v>
+        <v>3.13374268447083</v>
       </c>
       <c r="CF11" t="n">
         <v>0.5749132562661738</v>
@@ -6083,16 +6083,16 @@
         <v>0.1249070614196443</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.796153752061831</v>
+        <v>0.7961537520618309</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.4546009389174042</v>
+        <v>0.4546009389174043</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.5638320377990617</v>
+        <v>0.5638320377990615</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.2771967778569333</v>
+        <v>0.2771967778569332</v>
       </c>
       <c r="CS11" t="n">
         <v>0.05996663682789351</v>
@@ -6101,7 +6101,7 @@
         <v>0.1141302357486455</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.07579122685742144</v>
+        <v>0.07579122685742143</v>
       </c>
       <c r="CV11" t="n">
         <v>0.1369291433858244</v>
@@ -6113,7 +6113,7 @@
         <v>1.907117167195867</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.04849379615433272</v>
+        <v>0.04849379615433273</v>
       </c>
       <c r="CZ11" t="n">
         <v>0.1190732019778976</v>
@@ -6128,7 +6128,7 @@
         <v>0.06449414900494278</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.6682684462619434</v>
+        <v>0.6682684462619436</v>
       </c>
       <c r="DE11" t="n">
         <v>0.004378530889456951</v>
@@ -6137,10 +6137,10 @@
         <v>0.1962401695831143</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.885856698444892</v>
+        <v>2.885856698444893</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.2106602483431021</v>
+        <v>0.2106602483431022</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04963104701768073</v>
@@ -6155,19 +6155,19 @@
         <v>0.1049099458252576</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.09519134926709451</v>
+        <v>0.09519134926709452</v>
       </c>
       <c r="DN11" t="n">
         <v>0.01187108661801902</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.5918819885997834</v>
+        <v>0.5918819885997835</v>
       </c>
       <c r="DP11" t="n">
         <v>66.86606208878894</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.003740307738466385</v>
+        <v>0.003740307738466386</v>
       </c>
       <c r="DR11" t="n">
         <v>0.04065615904214659</v>
@@ -6182,7 +6182,7 @@
         <v>2.241979550608346</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.03621011087554069</v>
+        <v>0.03621011087554068</v>
       </c>
       <c r="DW11" t="n">
         <v>0.2403934985128031</v>
@@ -6206,13 +6206,13 @@
         <v>2.237791824592469</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.004562543078647832</v>
+        <v>0.004562543078647831</v>
       </c>
       <c r="EE11" t="n">
         <v>0.03822168866691002</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.001682134683973039</v>
+        <v>0.001682134683973038</v>
       </c>
       <c r="EG11" t="n">
         <v>0.04605061460469453</v>
@@ -6318,7 +6318,7 @@
         <v>187.3070433279954</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3555703574112494</v>
+        <v>0.3555703574112495</v>
       </c>
       <c r="D12" t="n">
         <v>0.4151547571207965</v>
@@ -6327,10 +6327,10 @@
         <v>5.292774770321793</v>
       </c>
       <c r="F12" t="n">
-        <v>108.7628022245242</v>
+        <v>108.7628022245244</v>
       </c>
       <c r="G12" t="n">
-        <v>268.7329213330881</v>
+        <v>268.7329213330884</v>
       </c>
       <c r="H12" t="n">
         <v>106.3532786148636</v>
@@ -6342,7 +6342,7 @@
         <v>11.30777484244006</v>
       </c>
       <c r="K12" t="n">
-        <v>39.80559791450519</v>
+        <v>39.8055979145052</v>
       </c>
       <c r="L12" t="n">
         <v>15.9791180294715</v>
@@ -6351,31 +6351,31 @@
         <v>2.394400220074553</v>
       </c>
       <c r="N12" t="n">
-        <v>9.736310523820679</v>
+        <v>9.736310523820672</v>
       </c>
       <c r="O12" t="n">
-        <v>1.990417712685601</v>
+        <v>1.990417712685602</v>
       </c>
       <c r="P12" t="n">
-        <v>2.626509281078437</v>
+        <v>2.626509281078438</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.886444447192753</v>
+        <v>3.886444447192756</v>
       </c>
       <c r="R12" t="n">
-        <v>3.431604030995713</v>
+        <v>3.431604030995714</v>
       </c>
       <c r="S12" t="n">
         <v>1.965292494422673</v>
       </c>
       <c r="T12" t="n">
-        <v>6.822938493470525</v>
+        <v>6.822938493470521</v>
       </c>
       <c r="U12" t="n">
         <v>0.01479850812310418</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6831327355708823</v>
+        <v>0.6831327355708822</v>
       </c>
       <c r="W12" t="n">
         <v>21.91786035124965</v>
@@ -6390,10 +6390,10 @@
         <v>1.904726755139886</v>
       </c>
       <c r="AA12" t="n">
-        <v>15.17355782477129</v>
+        <v>15.1735578247713</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.3916087622637227</v>
+        <v>0.3916087622637228</v>
       </c>
       <c r="AC12" t="n">
         <v>15.58310716611139</v>
@@ -6405,13 +6405,13 @@
         <v>0.005088180246803167</v>
       </c>
       <c r="AF12" t="n">
-        <v>26.36321867281374</v>
+        <v>26.36321867281375</v>
       </c>
       <c r="AG12" t="n">
-        <v>19.19765185377347</v>
+        <v>19.19765185377348</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.8485600622825983</v>
+        <v>0.8485600622825979</v>
       </c>
       <c r="AI12" t="n">
         <v>0.67793136788177</v>
@@ -6423,13 +6423,13 @@
         <v>8.733332666759518</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.35216344321095</v>
+        <v>0.3521634432109499</v>
       </c>
       <c r="AM12" t="n">
         <v>0.1681905673975861</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.1154911914492234</v>
+        <v>0.1154911914492233</v>
       </c>
       <c r="AO12" t="n">
         <v>0.2619777059145987</v>
@@ -6438,25 +6438,25 @@
         <v>0.2661535577246337</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.7358421863239857</v>
+        <v>0.7358421863239855</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.925163487466424</v>
+        <v>3.925163487466426</v>
       </c>
       <c r="AS12" t="n">
         <v>0.08268256667200101</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.0353136937263423</v>
+        <v>0.03531369372634229</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1618113915623241</v>
+        <v>0.161811391562324</v>
       </c>
       <c r="AV12" t="n">
         <v>1.972958482392654</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.59035893763127</v>
+        <v>2.590358937631269</v>
       </c>
       <c r="AX12" t="n">
         <v>0.127132903867545</v>
@@ -6465,13 +6465,13 @@
         <v>20.41376999275762</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.3265435606084485</v>
+        <v>0.3265435606084486</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.04494895685484367</v>
+        <v>0.04494895685484368</v>
       </c>
       <c r="BB12" t="n">
-        <v>19.07413149796637</v>
+        <v>19.07413149796638</v>
       </c>
       <c r="BC12" t="n">
         <v>3.242387635362422</v>
@@ -6489,13 +6489,13 @@
         <v>0.510434753019819</v>
       </c>
       <c r="BH12" t="n">
-        <v>7.347889275251528</v>
+        <v>7.347889275251529</v>
       </c>
       <c r="BI12" t="n">
         <v>0.2383280794542198</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.06141771527524519</v>
+        <v>0.06141771527524521</v>
       </c>
       <c r="BK12" t="n">
         <v>6.168226399682598</v>
@@ -6507,7 +6507,7 @@
         <v>12.02445064709249</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.763226385100119</v>
+        <v>0.7632263851001189</v>
       </c>
       <c r="BO12" t="n">
         <v>0.02091447885943392</v>
@@ -6519,7 +6519,7 @@
         <v>0.2307714604298093</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.09998712615172535</v>
+        <v>0.09998712615172534</v>
       </c>
       <c r="BS12" t="n">
         <v>10.84190769677739</v>
@@ -6594,7 +6594,7 @@
         <v>0.3934110076782731</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.5334785492231423</v>
+        <v>0.5334785492231422</v>
       </c>
       <c r="CR12" t="n">
         <v>0.2688384950185213</v>
@@ -6645,7 +6645,7 @@
         <v>2.743713024582892</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.2223755308085499</v>
+        <v>0.2223755308085498</v>
       </c>
       <c r="DI12" t="n">
         <v>0.0466906448458017</v>
@@ -6654,13 +6654,13 @@
         <v>0.02525575224460969</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.4429762482509984</v>
+        <v>0.4429762482509985</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.1050776726829564</v>
+        <v>0.1050776726829563</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.0897456257891253</v>
+        <v>0.08974562578912532</v>
       </c>
       <c r="DN12" t="n">
         <v>0.01249759963997908</v>
@@ -6669,19 +6669,19 @@
         <v>0.5435166559557555</v>
       </c>
       <c r="DP12" t="n">
-        <v>64.62088792362661</v>
+        <v>64.62088792362664</v>
       </c>
       <c r="DQ12" t="n">
         <v>0.003583911960086808</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.03649438428811823</v>
+        <v>0.03649438428811822</v>
       </c>
       <c r="DS12" t="n">
         <v>1.136924020648441</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.7949750095406467</v>
+        <v>0.7949750095406468</v>
       </c>
       <c r="DU12" t="n">
         <v>2.025434114054333</v>
@@ -6720,7 +6720,7 @@
         <v>0.00171616624890284</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.04725596108656757</v>
+        <v>0.04725596108656758</v>
       </c>
       <c r="EH12" t="n">
         <v>0.01172807695543431</v>
@@ -6820,13 +6820,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>191.0380320703821</v>
+        <v>191.0380320703822</v>
       </c>
       <c r="C13" t="n">
         <v>0.3924982775995451</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4111555903524837</v>
+        <v>0.4111555903524835</v>
       </c>
       <c r="E13" t="n">
         <v>5.213778626452774</v>
@@ -6835,10 +6835,10 @@
         <v>110.3052217624947</v>
       </c>
       <c r="G13" t="n">
-        <v>264.3676705543983</v>
+        <v>264.3676705543982</v>
       </c>
       <c r="H13" t="n">
-        <v>104.6966534357503</v>
+        <v>104.6966534357504</v>
       </c>
       <c r="I13" t="n">
         <v>22.34533065527027</v>
@@ -6847,7 +6847,7 @@
         <v>12.47287293970283</v>
       </c>
       <c r="K13" t="n">
-        <v>34.32068342049713</v>
+        <v>34.32068342049714</v>
       </c>
       <c r="L13" t="n">
         <v>17.09755670687182</v>
@@ -6856,16 +6856,16 @@
         <v>2.737326259186796</v>
       </c>
       <c r="N13" t="n">
-        <v>10.64477255047418</v>
+        <v>10.64477255047419</v>
       </c>
       <c r="O13" t="n">
-        <v>2.219151633555638</v>
+        <v>2.219151633555639</v>
       </c>
       <c r="P13" t="n">
-        <v>2.793978906999193</v>
+        <v>2.793978906999192</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.277978724909395</v>
+        <v>4.277978724909394</v>
       </c>
       <c r="R13" t="n">
         <v>3.538331749640751</v>
@@ -6874,28 +6874,28 @@
         <v>2.0331648319044</v>
       </c>
       <c r="T13" t="n">
-        <v>6.110590743398346</v>
+        <v>6.110590743398348</v>
       </c>
       <c r="U13" t="n">
         <v>0.01386448343769085</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7426155281044443</v>
+        <v>0.7426155281044446</v>
       </c>
       <c r="W13" t="n">
-        <v>19.95199690421992</v>
+        <v>19.95199690421991</v>
       </c>
       <c r="X13" t="n">
         <v>0.1718320453756577</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.780468192537126</v>
+        <v>1.780468192537125</v>
       </c>
       <c r="Z13" t="n">
         <v>2.004021483978576</v>
       </c>
       <c r="AA13" t="n">
-        <v>15.35778525360576</v>
+        <v>15.35778525360575</v>
       </c>
       <c r="AB13" t="n">
         <v>0.3851934035328792</v>
@@ -6907,28 +6907,28 @@
         <v>0.02413512281717073</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.005577482936193969</v>
+        <v>0.005577482936193968</v>
       </c>
       <c r="AF13" t="n">
         <v>24.73088385068638</v>
       </c>
       <c r="AG13" t="n">
-        <v>22.81341672059988</v>
+        <v>22.81341672059989</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.8368804554497219</v>
+        <v>0.8368804554497222</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.6602776033856694</v>
+        <v>0.6602776033856695</v>
       </c>
       <c r="AJ13" t="n">
         <v>1.477686988087022</v>
       </c>
       <c r="AK13" t="n">
-        <v>8.676850139866703</v>
+        <v>8.676850139866698</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.3672161387547305</v>
+        <v>0.3672161387547306</v>
       </c>
       <c r="AM13" t="n">
         <v>0.1786003732741557</v>
@@ -6943,10 +6943,10 @@
         <v>0.291072014145302</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.7576220320898085</v>
+        <v>0.7576220320898086</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.042892391814343</v>
+        <v>4.042892391814345</v>
       </c>
       <c r="AS13" t="n">
         <v>0.08467083455298798</v>
@@ -6958,7 +6958,7 @@
         <v>0.1739873745788708</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.989040608340257</v>
+        <v>1.989040608340256</v>
       </c>
       <c r="AW13" t="n">
         <v>2.931767319528783</v>
@@ -6970,10 +6970,10 @@
         <v>19.13479435591571</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.3465252200970449</v>
+        <v>0.3465252200970448</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.04700792014354089</v>
+        <v>0.0470079201435409</v>
       </c>
       <c r="BB13" t="n">
         <v>19.87843876472925</v>
@@ -6988,13 +6988,13 @@
         <v>0.2263504382617427</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.3984779450632039</v>
+        <v>0.3984779450632038</v>
       </c>
       <c r="BG13" t="n">
         <v>0.4907193142019843</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.062993280187833</v>
+        <v>8.062993280187831</v>
       </c>
       <c r="BI13" t="n">
         <v>0.2430093264782666</v>
@@ -7003,7 +7003,7 @@
         <v>0.08612387844326093</v>
       </c>
       <c r="BK13" t="n">
-        <v>7.023879547269578</v>
+        <v>7.023879547269579</v>
       </c>
       <c r="BL13" t="n">
         <v>0.04246970638124706</v>
@@ -7012,7 +7012,7 @@
         <v>12.28035276699541</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.7570082705146346</v>
+        <v>0.7570082705146344</v>
       </c>
       <c r="BO13" t="n">
         <v>0.02344663692084176</v>
@@ -7039,25 +7039,25 @@
         <v>1.759391306409165</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.004476151060149608</v>
+        <v>0.004476151060149609</v>
       </c>
       <c r="BX13" t="n">
         <v>1.256437534535655</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.05116264471375146</v>
+        <v>0.05116264471375147</v>
       </c>
       <c r="BZ13" t="n">
         <v>3.845395550790482</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.04691687729155184</v>
+        <v>0.04691687729155183</v>
       </c>
       <c r="CB13" t="n">
         <v>0.1564915082664003</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.06510591134099561</v>
+        <v>0.06510591134099562</v>
       </c>
       <c r="CD13" t="n">
         <v>0.1406300368012715</v>
@@ -7066,7 +7066,7 @@
         <v>2.944105917051</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.5583936066807865</v>
+        <v>0.5583936066807866</v>
       </c>
       <c r="CG13" t="n">
         <v>2.003314533415022</v>
@@ -7075,7 +7075,7 @@
         <v>0.226086820747178</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.03331167636755809</v>
+        <v>0.03331167636755808</v>
       </c>
       <c r="CJ13" t="n">
         <v>3.885575731420615</v>
@@ -7096,10 +7096,10 @@
         <v>0.8344932147221735</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.4517372060521734</v>
+        <v>0.4517372060521735</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.5569789107032855</v>
+        <v>0.5569789107032853</v>
       </c>
       <c r="CR13" t="n">
         <v>0.2828601122862184</v>
@@ -7135,7 +7135,7 @@
         <v>0.2794040744160127</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0678873037541696</v>
+        <v>0.06788730375416958</v>
       </c>
       <c r="DD13" t="n">
         <v>0.7035790012512176</v>
@@ -7144,13 +7144,13 @@
         <v>0.004865689545017192</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.193250088745261</v>
+        <v>0.1932500887452609</v>
       </c>
       <c r="DG13" t="n">
         <v>2.783543866216574</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.2170466243168653</v>
+        <v>0.2170466243168654</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05298630328692746</v>
@@ -7159,7 +7159,7 @@
         <v>0.02037772726023158</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.4226519572721289</v>
+        <v>0.4226519572721288</v>
       </c>
       <c r="DL13" t="n">
         <v>0.1131739929662637</v>
@@ -7171,22 +7171,22 @@
         <v>0.01306765503662449</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.6030104600436826</v>
+        <v>0.6030104600436827</v>
       </c>
       <c r="DP13" t="n">
-        <v>59.94315758148489</v>
+        <v>59.94315758148487</v>
       </c>
       <c r="DQ13" t="n">
         <v>0.003739565747016878</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.04588618740527184</v>
+        <v>0.04588618740527185</v>
       </c>
       <c r="DS13" t="n">
         <v>1.246810489652782</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.8005035758992186</v>
+        <v>0.8005035758992184</v>
       </c>
       <c r="DU13" t="n">
         <v>2.215937061203404</v>
@@ -7225,13 +7225,13 @@
         <v>0.001692103126007447</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.04508094035460075</v>
+        <v>0.04508094035460074</v>
       </c>
       <c r="EH13" t="n">
         <v>0.01751248503811286</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.01660601240470809</v>
+        <v>0.0166060124047081</v>
       </c>
       <c r="EJ13" t="n">
         <v>0.01436476716826299</v>
@@ -7325,25 +7325,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>338.4823015571531</v>
+        <v>338.4823015571529</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5003321480743242</v>
+        <v>0.5003321480743244</v>
       </c>
       <c r="D14" t="n">
         <v>0.6506676470786706</v>
       </c>
       <c r="E14" t="n">
-        <v>9.058890207885748</v>
+        <v>9.058890207885746</v>
       </c>
       <c r="F14" t="n">
-        <v>197.5002617175618</v>
+        <v>197.5002617175616</v>
       </c>
       <c r="G14" t="n">
-        <v>550.9705103015148</v>
+        <v>550.9705103015147</v>
       </c>
       <c r="H14" t="n">
-        <v>202.7461011100773</v>
+        <v>202.7461011100775</v>
       </c>
       <c r="I14" t="n">
         <v>51.92845623094195</v>
@@ -7352,13 +7352,13 @@
         <v>16.81970054946068</v>
       </c>
       <c r="K14" t="n">
-        <v>78.82347839509924</v>
+        <v>78.82347839509923</v>
       </c>
       <c r="L14" t="n">
-        <v>26.60739153097733</v>
+        <v>26.60739153097735</v>
       </c>
       <c r="M14" t="n">
-        <v>3.725108609580324</v>
+        <v>3.725108609580325</v>
       </c>
       <c r="N14" t="n">
         <v>14.5691849331249</v>
@@ -7367,19 +7367,19 @@
         <v>3.294903038112016</v>
       </c>
       <c r="P14" t="n">
-        <v>3.906260789134766</v>
+        <v>3.906260789134768</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.842754123659385</v>
+        <v>3.842754123659387</v>
       </c>
       <c r="R14" t="n">
-        <v>5.88260745659845</v>
+        <v>5.882607456598449</v>
       </c>
       <c r="S14" t="n">
-        <v>3.169463582482698</v>
+        <v>3.169463582482697</v>
       </c>
       <c r="T14" t="n">
-        <v>13.27941177386086</v>
+        <v>13.27941177386085</v>
       </c>
       <c r="U14" t="n">
         <v>0.02296348693052435</v>
@@ -7394,19 +7394,19 @@
         <v>0.3246791236204478</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.103087807084306</v>
+        <v>3.103087807084308</v>
       </c>
       <c r="Z14" t="n">
         <v>2.872239639466172</v>
       </c>
       <c r="AA14" t="n">
-        <v>36.04669631674182</v>
+        <v>36.04669631674181</v>
       </c>
       <c r="AB14" t="n">
         <v>0.6566030779648063</v>
       </c>
       <c r="AC14" t="n">
-        <v>24.2587360783589</v>
+        <v>24.25873607835889</v>
       </c>
       <c r="AD14" t="n">
         <v>0.03954050305358028</v>
@@ -7418,7 +7418,7 @@
         <v>53.2915976146195</v>
       </c>
       <c r="AG14" t="n">
-        <v>34.2841966099906</v>
+        <v>34.28419660999059</v>
       </c>
       <c r="AH14" t="n">
         <v>1.573818366340089</v>
@@ -7433,7 +7433,7 @@
         <v>13.35027819563612</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.5560605283839813</v>
+        <v>0.5560605283839815</v>
       </c>
       <c r="AM14" t="n">
         <v>0.2559435892229798</v>
@@ -7442,7 +7442,7 @@
         <v>0.1925881156272423</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.4269529431590516</v>
+        <v>0.4269529431590515</v>
       </c>
       <c r="AP14" t="n">
         <v>0.3777150994936763</v>
@@ -7466,13 +7466,13 @@
         <v>3.569180612299943</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.670492835038579</v>
+        <v>4.67049283503858</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.2378016392687132</v>
+        <v>0.2378016392687133</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.21069115862192</v>
+        <v>50.21069115862191</v>
       </c>
       <c r="AZ14" t="n">
         <v>0.5383586329485343</v>
@@ -7481,25 +7481,25 @@
         <v>0.06515883312020487</v>
       </c>
       <c r="BB14" t="n">
-        <v>46.85941209386321</v>
+        <v>46.85941209386324</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.323467152298637</v>
+        <v>5.323467152298638</v>
       </c>
       <c r="BD14" t="n">
         <v>28.09770099886684</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.3739193495611518</v>
+        <v>0.3739193495611519</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.5733265193252319</v>
+        <v>0.5733265193252318</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.7753968259582846</v>
+        <v>0.7753968259582847</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.2335474348251</v>
+        <v>11.23354743482509</v>
       </c>
       <c r="BI14" t="n">
         <v>0.3691221454281291</v>
@@ -7508,13 +7508,13 @@
         <v>0.005737491980239817</v>
       </c>
       <c r="BK14" t="n">
-        <v>7.576125406056335</v>
+        <v>7.576125406056336</v>
       </c>
       <c r="BL14" t="n">
         <v>0.09660918369795228</v>
       </c>
       <c r="BM14" t="n">
-        <v>21.96548053126049</v>
+        <v>21.96548053126048</v>
       </c>
       <c r="BN14" t="n">
         <v>1.334536763315314</v>
@@ -7535,13 +7535,13 @@
         <v>15.07977235414507</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.147166574557633</v>
+        <v>5.147166574557632</v>
       </c>
       <c r="BU14" t="n">
         <v>2.703419228222107</v>
       </c>
       <c r="BV14" t="n">
-        <v>2.981202413708605</v>
+        <v>2.981202413708604</v>
       </c>
       <c r="BW14" t="n">
         <v>0.005243158880678737</v>
@@ -7556,7 +7556,7 @@
         <v>4.012654404122346</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.06758305287676422</v>
+        <v>0.06758305287676421</v>
       </c>
       <c r="CB14" t="n">
         <v>0.2565236722730194</v>
@@ -7565,16 +7565,16 @@
         <v>0.09395388926363958</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.262493242466177</v>
+        <v>0.2624932424661769</v>
       </c>
       <c r="CE14" t="n">
-        <v>5.75971813586441</v>
+        <v>5.759718135864409</v>
       </c>
       <c r="CF14" t="n">
         <v>1.244031089143612</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.395896523025483</v>
+        <v>2.395896523025484</v>
       </c>
       <c r="CH14" t="n">
         <v>0.3224537586271389</v>
@@ -7592,7 +7592,7 @@
         <v>0.3511870505842729</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.01870451431533713</v>
+        <v>0.01870451431533712</v>
       </c>
       <c r="CN14" t="n">
         <v>0.221111651308962</v>
@@ -7601,10 +7601,10 @@
         <v>1.253943234206859</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.6649306411617703</v>
+        <v>0.6649306411617704</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.6782095792201263</v>
+        <v>0.6782095792201264</v>
       </c>
       <c r="CR14" t="n">
         <v>0.5207305060998288</v>
@@ -7637,37 +7637,37 @@
         <v>0.1981927999260763</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.3978751665435197</v>
+        <v>0.3978751665435196</v>
       </c>
       <c r="DC14" t="n">
         <v>0.1339083718702938</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.048874403837277</v>
+        <v>1.048874403837278</v>
       </c>
       <c r="DE14" t="n">
         <v>0.007017540010765875</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.3133784444673173</v>
+        <v>0.3133784444673172</v>
       </c>
       <c r="DG14" t="n">
-        <v>4.423906837336294</v>
+        <v>4.423906837336295</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.3581196260909453</v>
+        <v>0.3581196260909452</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.08287078400642735</v>
+        <v>0.08287078400642736</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.03957516619987031</v>
+        <v>0.03957516619987032</v>
       </c>
       <c r="DK14" t="n">
         <v>0.755089749759567</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.1643653690071009</v>
+        <v>0.1643653690071008</v>
       </c>
       <c r="DM14" t="n">
         <v>0.184134835247514</v>
@@ -7685,7 +7685,7 @@
         <v>0.005325984725393929</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.05268373050962067</v>
+        <v>0.05268373050962066</v>
       </c>
       <c r="DS14" t="n">
         <v>2.083760022232143</v>
@@ -7703,16 +7703,16 @@
         <v>0.4301833303193309</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.4769793031682761</v>
+        <v>0.4769793031682762</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.1773578181153355</v>
+        <v>0.1773578181153356</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.142358980203267</v>
+        <v>0.1423589802032671</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.3364997309286673</v>
+        <v>0.3364997309286672</v>
       </c>
       <c r="EB14" t="n">
         <v>0.1784285836989163</v>
@@ -7721,13 +7721,13 @@
         <v>4.972578129277611</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.004000648607851964</v>
+        <v>0.004000648607851965</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.07073018304569614</v>
+        <v>0.07073018304569616</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.001710488634244893</v>
+        <v>0.001710488634244892</v>
       </c>
       <c r="EG14" t="n">
         <v>0.06116672976681157</v>
@@ -7830,37 +7830,37 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>339.9679037431537</v>
+        <v>339.9679037431539</v>
       </c>
       <c r="C15" t="n">
         <v>0.5162502252648964</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6913160163047212</v>
+        <v>0.6913160163047214</v>
       </c>
       <c r="E15" t="n">
-        <v>9.472006026950428</v>
+        <v>9.472006026950426</v>
       </c>
       <c r="F15" t="n">
-        <v>199.9282717881695</v>
+        <v>199.9282717881693</v>
       </c>
       <c r="G15" t="n">
-        <v>550.8143144862207</v>
+        <v>550.8143144862206</v>
       </c>
       <c r="H15" t="n">
         <v>201.4705166773789</v>
       </c>
       <c r="I15" t="n">
-        <v>49.64308423613162</v>
+        <v>49.64308423613164</v>
       </c>
       <c r="J15" t="n">
         <v>16.64573910606476</v>
       </c>
       <c r="K15" t="n">
-        <v>79.32295137278487</v>
+        <v>79.32295137278484</v>
       </c>
       <c r="L15" t="n">
-        <v>27.18642336678112</v>
+        <v>27.18642336678111</v>
       </c>
       <c r="M15" t="n">
         <v>3.445901137445752</v>
@@ -7869,16 +7869,16 @@
         <v>14.97814149223479</v>
       </c>
       <c r="O15" t="n">
-        <v>3.877453199129755</v>
+        <v>3.877453199129756</v>
       </c>
       <c r="P15" t="n">
-        <v>3.834332002907979</v>
+        <v>3.83433200290798</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.023177172559855</v>
+        <v>6.023177172559853</v>
       </c>
       <c r="R15" t="n">
-        <v>5.949131763719678</v>
+        <v>5.949131763719676</v>
       </c>
       <c r="S15" t="n">
         <v>3.224974770365973</v>
@@ -7893,25 +7893,25 @@
         <v>1.162095979254191</v>
       </c>
       <c r="W15" t="n">
-        <v>43.51516009209706</v>
+        <v>43.51516009209707</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3210695322001896</v>
+        <v>0.3210695322001895</v>
       </c>
       <c r="Y15" t="n">
         <v>3.087807269100277</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.766895871208599</v>
+        <v>2.7668958712086</v>
       </c>
       <c r="AA15" t="n">
-        <v>38.36051604651185</v>
+        <v>38.36051604651183</v>
       </c>
       <c r="AB15" t="n">
         <v>0.618488506865019</v>
       </c>
       <c r="AC15" t="n">
-        <v>24.71870188120023</v>
+        <v>24.71870188120024</v>
       </c>
       <c r="AD15" t="n">
         <v>0.04147805068852546</v>
@@ -7920,7 +7920,7 @@
         <v>0.008270629897851415</v>
       </c>
       <c r="AF15" t="n">
-        <v>50.55783057115723</v>
+        <v>50.55783057115721</v>
       </c>
       <c r="AG15" t="n">
         <v>35.76583284950183</v>
@@ -7938,7 +7938,7 @@
         <v>13.90177800769293</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.5979598904923212</v>
+        <v>0.5979598904923213</v>
       </c>
       <c r="AM15" t="n">
         <v>0.2783264139697931</v>
@@ -7953,10 +7953,10 @@
         <v>0.3996174953893472</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.394145542172852</v>
+        <v>1.394145542172853</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.806862964356109</v>
+        <v>7.806862964356108</v>
       </c>
       <c r="AS15" t="n">
         <v>0.1660504141021948</v>
@@ -7968,7 +7968,7 @@
         <v>0.239473226394323</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.777795179031263</v>
+        <v>3.777795179031264</v>
       </c>
       <c r="AW15" t="n">
         <v>5.685296609868967</v>
@@ -7980,16 +7980,16 @@
         <v>50.22166455892092</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.5375528631004316</v>
+        <v>0.5375528631004318</v>
       </c>
       <c r="BA15" t="n">
         <v>0.0706783984784168</v>
       </c>
       <c r="BB15" t="n">
-        <v>42.2203452231828</v>
+        <v>42.22034522318279</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.164562010286513</v>
+        <v>5.164562010286512</v>
       </c>
       <c r="BD15" t="n">
         <v>27.061580558701</v>
@@ -8001,22 +8001,22 @@
         <v>0.5640821584039857</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.8229122625220627</v>
+        <v>0.822912262522063</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.97800730298768</v>
+        <v>10.97800730298769</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.4106936260497088</v>
+        <v>0.4106936260497087</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.06751459582641882</v>
+        <v>0.06751459582641883</v>
       </c>
       <c r="BK15" t="n">
         <v>7.583220679254564</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.09725104860782102</v>
+        <v>0.09725104860782101</v>
       </c>
       <c r="BM15" t="n">
         <v>22.28538870430981</v>
@@ -8025,10 +8025,10 @@
         <v>1.280089657097345</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.03244527416312855</v>
+        <v>0.03244527416312854</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.2030245335134442</v>
+        <v>0.2030245335134443</v>
       </c>
       <c r="BQ15" t="n">
         <v>0.4547050420758502</v>
@@ -8040,13 +8040,13 @@
         <v>14.66952582916914</v>
       </c>
       <c r="BT15" t="n">
-        <v>5.377060657092477</v>
+        <v>5.377060657092476</v>
       </c>
       <c r="BU15" t="n">
-        <v>2.910520281185771</v>
+        <v>2.91052028118577</v>
       </c>
       <c r="BV15" t="n">
-        <v>2.990116388617168</v>
+        <v>2.990116388617169</v>
       </c>
       <c r="BW15" t="n">
         <v>0.005320022576707077</v>
@@ -8067,7 +8067,7 @@
         <v>0.3131226425413716</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.09981060038399726</v>
+        <v>0.09981060038399732</v>
       </c>
       <c r="CD15" t="n">
         <v>0.2965181102235944</v>
@@ -8088,7 +8088,7 @@
         <v>0.1202264550615719</v>
       </c>
       <c r="CJ15" t="n">
-        <v>4.685707881822316</v>
+        <v>4.685707881822317</v>
       </c>
       <c r="CK15" t="n">
         <v>0.00627177523991902</v>
@@ -8106,7 +8106,7 @@
         <v>1.116509428003112</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.6484568813828582</v>
+        <v>0.6484568813828581</v>
       </c>
       <c r="CQ15" t="n">
         <v>0.7640684764955331</v>
@@ -8133,10 +8133,10 @@
         <v>3.28135128746548</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.07287907595229684</v>
+        <v>0.07287907595229685</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.1805709191206046</v>
+        <v>0.1805709191206047</v>
       </c>
       <c r="DA15" t="n">
         <v>0.2218884171008656</v>
@@ -8151,7 +8151,7 @@
         <v>1.121128913677394</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.006791461285416965</v>
+        <v>0.006791461285416964</v>
       </c>
       <c r="DF15" t="n">
         <v>0.3451279815988144</v>
@@ -8160,16 +8160,16 @@
         <v>4.353706378088149</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.3300902996819181</v>
+        <v>0.330090299681918</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.08996835551590758</v>
+        <v>0.08996835551590757</v>
       </c>
       <c r="DJ15" t="n">
         <v>0.0452821189075249</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.7370437127873851</v>
+        <v>0.7370437127873852</v>
       </c>
       <c r="DL15" t="n">
         <v>0.1650313945374654</v>
@@ -8181,7 +8181,7 @@
         <v>0.02273034247456948</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.9358240422108776</v>
+        <v>0.9358240422108777</v>
       </c>
       <c r="DP15" t="n">
         <v>159.2556506418967</v>
@@ -8190,7 +8190,7 @@
         <v>0.004645682075760891</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.05704856430363185</v>
+        <v>0.05704856430363184</v>
       </c>
       <c r="DS15" t="n">
         <v>2.151554306896785</v>
@@ -8205,16 +8205,16 @@
         <v>0.04213054718216701</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.4379004654374033</v>
+        <v>0.4379004654374032</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.451270467491299</v>
+        <v>0.4512704674912991</v>
       </c>
       <c r="DY15" t="n">
         <v>0.1765583218793542</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.1447150677966461</v>
+        <v>0.144715067796646</v>
       </c>
       <c r="EA15" t="n">
         <v>0.3315956427584689</v>
@@ -8229,13 +8229,13 @@
         <v>0.00588903872533335</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.07489858299237576</v>
+        <v>0.07489858299237577</v>
       </c>
       <c r="EF15" t="n">
         <v>0.001729720928940454</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.06283371290740408</v>
+        <v>0.0628337129074041</v>
       </c>
       <c r="EH15" t="n">
         <v>0.01840053132977065</v>
@@ -8335,25 +8335,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>316.4651507008163</v>
+        <v>316.4651507008169</v>
       </c>
       <c r="C16" t="n">
         <v>0.4992434495697613</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6883910427175277</v>
+        <v>0.6883910427175276</v>
       </c>
       <c r="E16" t="n">
         <v>8.454021668257226</v>
       </c>
       <c r="F16" t="n">
-        <v>190.4890067392384</v>
+        <v>190.4890067392386</v>
       </c>
       <c r="G16" t="n">
-        <v>531.8284565095474</v>
+        <v>531.8284565095476</v>
       </c>
       <c r="H16" t="n">
-        <v>197.1847244190117</v>
+        <v>197.1847244190116</v>
       </c>
       <c r="I16" t="n">
         <v>55.17449330541861</v>
@@ -8362,10 +8362,10 @@
         <v>17.05904384213317</v>
       </c>
       <c r="K16" t="n">
-        <v>79.7483698107697</v>
+        <v>79.74836981076972</v>
       </c>
       <c r="L16" t="n">
-        <v>26.08149031429907</v>
+        <v>26.08149031429908</v>
       </c>
       <c r="M16" t="n">
         <v>3.65493199032628</v>
@@ -8374,13 +8374,13 @@
         <v>13.04493835903978</v>
       </c>
       <c r="O16" t="n">
-        <v>3.020817851880674</v>
+        <v>3.020817851880673</v>
       </c>
       <c r="P16" t="n">
         <v>3.761919792796915</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.554566851162718</v>
+        <v>5.554566851162716</v>
       </c>
       <c r="R16" t="n">
         <v>5.5952396878183</v>
@@ -8398,25 +8398,25 @@
         <v>1.053665962554217</v>
       </c>
       <c r="W16" t="n">
-        <v>40.85438593492319</v>
+        <v>40.85438593492318</v>
       </c>
       <c r="X16" t="n">
         <v>0.3242406935439865</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.817306935382983</v>
+        <v>2.817306935382982</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.763653088680079</v>
+        <v>2.76365308868008</v>
       </c>
       <c r="AA16" t="n">
-        <v>35.55832547782605</v>
+        <v>35.55832547782603</v>
       </c>
       <c r="AB16" t="n">
         <v>0.6013531913225519</v>
       </c>
       <c r="AC16" t="n">
-        <v>23.55321816763552</v>
+        <v>23.55321816763551</v>
       </c>
       <c r="AD16" t="n">
         <v>0.03549163257831871</v>
@@ -8428,7 +8428,7 @@
         <v>51.02369697691538</v>
       </c>
       <c r="AG16" t="n">
-        <v>30.9405044214045</v>
+        <v>30.94050442140451</v>
       </c>
       <c r="AH16" t="n">
         <v>1.369355104171192</v>
@@ -8443,13 +8443,13 @@
         <v>12.34934950018937</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.5950990026010462</v>
+        <v>0.5950990026010461</v>
       </c>
       <c r="AM16" t="n">
         <v>0.2706569995989109</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.2080942140041125</v>
+        <v>0.2080942140041126</v>
       </c>
       <c r="AO16" t="n">
         <v>0.3981511220443803</v>
@@ -8461,7 +8461,7 @@
         <v>1.441774165774629</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.558398617417603</v>
+        <v>7.558398617417602</v>
       </c>
       <c r="AS16" t="n">
         <v>0.1710382159973853</v>
@@ -8470,7 +8470,7 @@
         <v>0.04305162054661447</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.2383106961359085</v>
+        <v>0.2383106961359086</v>
       </c>
       <c r="AV16" t="n">
         <v>3.240435673082851</v>
@@ -8482,16 +8482,16 @@
         <v>0.2475292447110699</v>
       </c>
       <c r="AY16" t="n">
-        <v>50.13837317396758</v>
+        <v>50.13837317396759</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.4778548293983886</v>
+        <v>0.4778548293983885</v>
       </c>
       <c r="BA16" t="n">
         <v>0.06363342134431832</v>
       </c>
       <c r="BB16" t="n">
-        <v>41.99579983189019</v>
+        <v>41.99579983189017</v>
       </c>
       <c r="BC16" t="n">
         <v>5.00495213308536</v>
@@ -8500,10 +8500,10 @@
         <v>24.16732439168008</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.3871143697981332</v>
+        <v>0.3871143697981334</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.584300141410396</v>
+        <v>0.5843001414103957</v>
       </c>
       <c r="BG16" t="n">
         <v>0.7637496637475516</v>
@@ -8512,19 +8512,19 @@
         <v>11.52429887559248</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.4121127517241337</v>
+        <v>0.4121127517241336</v>
       </c>
       <c r="BJ16" t="n">
         <v>0.001975814628289631</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.525872006185974</v>
+        <v>6.525872006185973</v>
       </c>
       <c r="BL16" t="n">
         <v>0.07683679912447719</v>
       </c>
       <c r="BM16" t="n">
-        <v>19.04418992930889</v>
+        <v>19.0441899293089</v>
       </c>
       <c r="BN16" t="n">
         <v>1.319142144997545</v>
@@ -8542,7 +8542,7 @@
         <v>0.1053617787462058</v>
       </c>
       <c r="BS16" t="n">
-        <v>14.61431866093424</v>
+        <v>14.61431866093425</v>
       </c>
       <c r="BT16" t="n">
         <v>4.473685519038743</v>
@@ -8566,7 +8566,7 @@
         <v>4.225381236245749</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.06520952053710403</v>
+        <v>0.06520952053710402</v>
       </c>
       <c r="CB16" t="n">
         <v>0.325462257089227</v>
@@ -8581,10 +8581,10 @@
         <v>5.259860609033285</v>
       </c>
       <c r="CF16" t="n">
-        <v>1.067176372910877</v>
+        <v>1.067176372910878</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.289162291748105</v>
+        <v>2.289162291748106</v>
       </c>
       <c r="CH16" t="n">
         <v>0.3196776778397661</v>
@@ -8602,10 +8602,10 @@
         <v>0.3626541629384397</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.01834703480267893</v>
+        <v>0.01834703480267892</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.2020668916630236</v>
+        <v>0.2020668916630237</v>
       </c>
       <c r="CO16" t="n">
         <v>0.5997736627781288</v>
@@ -8626,7 +8626,7 @@
         <v>0.1906983546248199</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.1265788327576677</v>
+        <v>0.1265788327576678</v>
       </c>
       <c r="CV16" t="n">
         <v>0.2140383884757204</v>
@@ -8638,7 +8638,7 @@
         <v>2.438774334043478</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.07541772980031558</v>
+        <v>0.07541772980031555</v>
       </c>
       <c r="CZ16" t="n">
         <v>0.1705255841763265</v>
@@ -8662,16 +8662,16 @@
         <v>0.2382420737160807</v>
       </c>
       <c r="DG16" t="n">
-        <v>4.20643113311178</v>
+        <v>4.206431133111779</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.3695391844189432</v>
+        <v>0.3695391844189431</v>
       </c>
       <c r="DI16" t="n">
         <v>0.0898961334915731</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.04274963930216526</v>
+        <v>0.04274963930216525</v>
       </c>
       <c r="DK16" t="n">
         <v>0.754051893186615</v>
@@ -8686,7 +8686,7 @@
         <v>0.02248887581906394</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.8067208686977895</v>
+        <v>0.8067208686977893</v>
       </c>
       <c r="DP16" t="n">
         <v>148.0693184042884</v>
@@ -8695,10 +8695,10 @@
         <v>0.00408496055828206</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.04092794229738319</v>
+        <v>0.04092794229738318</v>
       </c>
       <c r="DS16" t="n">
-        <v>2.38668707196074</v>
+        <v>2.386687071960739</v>
       </c>
       <c r="DT16" t="n">
         <v>1.00826734993306</v>
@@ -8734,13 +8734,13 @@
         <v>0.004415197859653697</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.07529819277237362</v>
+        <v>0.07529819277237361</v>
       </c>
       <c r="EF16" t="n">
         <v>0.001537795517978547</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.05145825336683773</v>
+        <v>0.05145825336683772</v>
       </c>
       <c r="EH16" t="n">
         <v>0.03086554379758411</v>
@@ -8846,22 +8846,22 @@
         <v>0.578346559989949</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8026681630801574</v>
+        <v>0.8026681630801572</v>
       </c>
       <c r="E17" t="n">
         <v>10.25139762752197</v>
       </c>
       <c r="F17" t="n">
-        <v>263.1742931654668</v>
+        <v>263.174293165467</v>
       </c>
       <c r="G17" t="n">
-        <v>759.0744330364073</v>
+        <v>759.074433036407</v>
       </c>
       <c r="H17" t="n">
-        <v>277.9700000718025</v>
+        <v>277.9700000718029</v>
       </c>
       <c r="I17" t="n">
-        <v>78.52670899027699</v>
+        <v>78.52670899027697</v>
       </c>
       <c r="J17" t="n">
         <v>19.78277436779359</v>
@@ -8870,13 +8870,13 @@
         <v>113.7499439550954</v>
       </c>
       <c r="L17" t="n">
-        <v>30.92416302141377</v>
+        <v>30.92416302141376</v>
       </c>
       <c r="M17" t="n">
-        <v>3.315162242105956</v>
+        <v>3.315162242105957</v>
       </c>
       <c r="N17" t="n">
-        <v>15.62250490095466</v>
+        <v>15.62250490095467</v>
       </c>
       <c r="O17" t="n">
         <v>3.97830927028128</v>
@@ -8885,13 +8885,13 @@
         <v>4.253952706653429</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.169677931648653</v>
+        <v>6.169677931648652</v>
       </c>
       <c r="R17" t="n">
         <v>7.203289999042919</v>
       </c>
       <c r="S17" t="n">
-        <v>4.038574819956989</v>
+        <v>4.038574819956987</v>
       </c>
       <c r="T17" t="n">
         <v>16.10289527677356</v>
@@ -8900,7 +8900,7 @@
         <v>0.03157373753011766</v>
       </c>
       <c r="V17" t="n">
-        <v>1.370383244301235</v>
+        <v>1.370383244301234</v>
       </c>
       <c r="W17" t="n">
         <v>57.45436274853692</v>
@@ -8909,7 +8909,7 @@
         <v>0.3621489062048468</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.470960661583677</v>
+        <v>3.470960661583678</v>
       </c>
       <c r="Z17" t="n">
         <v>3.238436963249196</v>
@@ -8921,19 +8921,19 @@
         <v>0.7095695368170816</v>
       </c>
       <c r="AC17" t="n">
-        <v>27.30672319240507</v>
+        <v>27.30672319240505</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.05375065546140827</v>
+        <v>0.05375065546140828</v>
       </c>
       <c r="AE17" t="n">
         <v>0.009114815042309427</v>
       </c>
       <c r="AF17" t="n">
-        <v>75.07397051738791</v>
+        <v>75.07397051738786</v>
       </c>
       <c r="AG17" t="n">
-        <v>37.77008413281229</v>
+        <v>37.77008413281228</v>
       </c>
       <c r="AH17" t="n">
         <v>2.093817064582382</v>
@@ -8942,7 +8942,7 @@
         <v>1.419414465684149</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.05403101196083</v>
+        <v>3.054031011960829</v>
       </c>
       <c r="AK17" t="n">
         <v>15.07712930581885</v>
@@ -8954,10 +8954,10 @@
         <v>0.322706471715766</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.2625387612799136</v>
+        <v>0.2625387612799135</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.51907373160486</v>
+        <v>0.5190737316048599</v>
       </c>
       <c r="AP17" t="n">
         <v>0.4685313158556249</v>
@@ -8966,7 +8966,7 @@
         <v>1.504180574800631</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.757436153017903</v>
+        <v>8.75743615301791</v>
       </c>
       <c r="AS17" t="n">
         <v>0.2056600914382004</v>
@@ -8978,28 +8978,28 @@
         <v>0.2607051141114113</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.38706166391511</v>
+        <v>4.387061663915111</v>
       </c>
       <c r="AW17" t="n">
         <v>5.653048057956342</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.3056180042771322</v>
+        <v>0.3056180042771321</v>
       </c>
       <c r="AY17" t="n">
-        <v>77.26122772373186</v>
+        <v>77.26122772373189</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.5592223663275284</v>
+        <v>0.5592223663275285</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.07107560786585661</v>
+        <v>0.07107560786585659</v>
       </c>
       <c r="BB17" t="n">
-        <v>62.33204504933174</v>
+        <v>62.33204504933176</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.287370154692156</v>
+        <v>6.287370154692155</v>
       </c>
       <c r="BD17" t="n">
         <v>27.90142995101545</v>
@@ -9017,13 +9017,13 @@
         <v>13.66599580628666</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.5310232600619323</v>
+        <v>0.5310232600619322</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.08580228255947946</v>
+        <v>0.08580228255947943</v>
       </c>
       <c r="BK17" t="n">
-        <v>8.758523229211008</v>
+        <v>8.758523229211004</v>
       </c>
       <c r="BL17" t="n">
         <v>0.105621725757033</v>
@@ -9041,22 +9041,22 @@
         <v>0.2277342449158929</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.6100145977516065</v>
+        <v>0.6100145977516064</v>
       </c>
       <c r="BR17" t="n">
         <v>0.08856993352889866</v>
       </c>
       <c r="BS17" t="n">
-        <v>17.11880592520788</v>
+        <v>17.11880592520789</v>
       </c>
       <c r="BT17" t="n">
         <v>6.379974186720847</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.159059213605379</v>
+        <v>3.159059213605378</v>
       </c>
       <c r="BV17" t="n">
-        <v>3.430566588778874</v>
+        <v>3.430566588778875</v>
       </c>
       <c r="BW17" t="n">
         <v>0.005622881439779774</v>
@@ -9068,7 +9068,7 @@
         <v>0.1293216650144353</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.028397708228864</v>
+        <v>4.028397708228863</v>
       </c>
       <c r="CA17" t="n">
         <v>0.07648818052484195</v>
@@ -9098,7 +9098,7 @@
         <v>0.1637870101412136</v>
       </c>
       <c r="CJ17" t="n">
-        <v>4.065838664408862</v>
+        <v>4.065838664408863</v>
       </c>
       <c r="CK17" t="n">
         <v>0.007607140877065268</v>
@@ -9119,16 +9119,16 @@
         <v>0.7322264340903724</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.7455975000702634</v>
+        <v>0.7455975000702633</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.5965024187343204</v>
+        <v>0.5965024187343203</v>
       </c>
       <c r="CS17" t="n">
         <v>0.1283721371705351</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.2374188615686211</v>
+        <v>0.2374188615686212</v>
       </c>
       <c r="CU17" t="n">
         <v>0.1629636241676406</v>
@@ -9146,13 +9146,13 @@
         <v>0.09691409456915476</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.1910374347783411</v>
+        <v>0.1910374347783412</v>
       </c>
       <c r="DA17" t="n">
         <v>0.2550371984085896</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.4092292769400333</v>
+        <v>0.4092292769400332</v>
       </c>
       <c r="DC17" t="n">
         <v>0.1700319651189248</v>
@@ -9164,13 +9164,13 @@
         <v>0.007869573468016479</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.3829800780147803</v>
+        <v>0.3829800780147804</v>
       </c>
       <c r="DG17" t="n">
-        <v>4.926163053362603</v>
+        <v>4.926163053362602</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.3921391808218672</v>
+        <v>0.3921391808218673</v>
       </c>
       <c r="DI17" t="n">
         <v>0.1093438533910073</v>
@@ -9179,7 +9179,7 @@
         <v>0.054784359252892</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.9585364727435161</v>
+        <v>0.9585364727435164</v>
       </c>
       <c r="DL17" t="n">
         <v>0.1729668912227956</v>
@@ -9236,7 +9236,7 @@
         <v>6.918524389962566</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.005707098546805793</v>
+        <v>0.005707098546805792</v>
       </c>
       <c r="EE17" t="n">
         <v>0.09120238656550907</v>
@@ -9245,7 +9245,7 @@
         <v>0.001797543201915725</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.05927287749060196</v>
+        <v>0.05927287749060194</v>
       </c>
       <c r="EH17" t="n">
         <v>0.01941204782325846</v>
@@ -9254,7 +9254,7 @@
         <v>0.01936684133885338</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.02300159717581599</v>
+        <v>0.02300159717581598</v>
       </c>
       <c r="EK17" t="inlineStr">
         <is>
@@ -9345,13 +9345,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>452.7732087518456</v>
+        <v>452.7732087518454</v>
       </c>
       <c r="C18" t="n">
         <v>0.6028096168457832</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9624695034230458</v>
+        <v>0.9624695034230455</v>
       </c>
       <c r="E18" t="n">
         <v>10.70725105523885</v>
@@ -9360,13 +9360,13 @@
         <v>283.6896214537359</v>
       </c>
       <c r="G18" t="n">
-        <v>797.3983425768847</v>
+        <v>797.3983425768859</v>
       </c>
       <c r="H18" t="n">
-        <v>308.7744288208418</v>
+        <v>308.7744288208417</v>
       </c>
       <c r="I18" t="n">
-        <v>86.58033040432602</v>
+        <v>86.58033040432601</v>
       </c>
       <c r="J18" t="n">
         <v>19.27333480777068</v>
@@ -9375,49 +9375,49 @@
         <v>139.808191732281</v>
       </c>
       <c r="L18" t="n">
-        <v>33.67093013591801</v>
+        <v>33.67093013591804</v>
       </c>
       <c r="M18" t="n">
         <v>3.635938154208346</v>
       </c>
       <c r="N18" t="n">
-        <v>16.78014764680844</v>
+        <v>16.78014764680845</v>
       </c>
       <c r="O18" t="n">
-        <v>4.155985265138865</v>
+        <v>4.155985265138864</v>
       </c>
       <c r="P18" t="n">
-        <v>4.352405875048258</v>
+        <v>4.352405875048257</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.272894064982357</v>
+        <v>6.272894064982358</v>
       </c>
       <c r="R18" t="n">
-        <v>8.735446391515648</v>
+        <v>8.735446391515644</v>
       </c>
       <c r="S18" t="n">
-        <v>4.206550290138672</v>
+        <v>4.206550290138673</v>
       </c>
       <c r="T18" t="n">
-        <v>14.95038329562326</v>
+        <v>14.95038329562327</v>
       </c>
       <c r="U18" t="n">
         <v>0.03303951752592633</v>
       </c>
       <c r="V18" t="n">
-        <v>1.378030835205639</v>
+        <v>1.378030835205638</v>
       </c>
       <c r="W18" t="n">
-        <v>74.60968757876506</v>
+        <v>74.60968757876508</v>
       </c>
       <c r="X18" t="n">
         <v>0.4067919635099077</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.571209022316341</v>
+        <v>3.571209022316342</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.451649865653488</v>
+        <v>3.451649865653489</v>
       </c>
       <c r="AA18" t="n">
         <v>59.24178136349355</v>
@@ -9435,7 +9435,7 @@
         <v>0.007919862486787305</v>
       </c>
       <c r="AF18" t="n">
-        <v>78.12636319637697</v>
+        <v>78.126363196377</v>
       </c>
       <c r="AG18" t="n">
         <v>37.83058400153883</v>
@@ -9453,7 +9453,7 @@
         <v>13.83875879936987</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.7025020583363112</v>
+        <v>0.7025020583363109</v>
       </c>
       <c r="AM18" t="n">
         <v>0.2989639581600973</v>
@@ -9462,7 +9462,7 @@
         <v>0.2564671268979504</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.4926698176538301</v>
+        <v>0.49266981765383</v>
       </c>
       <c r="AP18" t="n">
         <v>0.4689794849502715</v>
@@ -9471,7 +9471,7 @@
         <v>1.750946287373406</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.836762725264927</v>
+        <v>9.836762725264924</v>
       </c>
       <c r="AS18" t="n">
         <v>0.2485624767400129</v>
@@ -9483,7 +9483,7 @@
         <v>0.296278098906221</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.625264225328276</v>
+        <v>5.625264225328277</v>
       </c>
       <c r="AW18" t="n">
         <v>5.348696248413469</v>
@@ -9492,13 +9492,13 @@
         <v>0.3356938204301642</v>
       </c>
       <c r="AY18" t="n">
-        <v>83.51987220662356</v>
+        <v>83.51987220662355</v>
       </c>
       <c r="AZ18" t="n">
         <v>0.5651631022033325</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.0727845745336286</v>
+        <v>0.07278457453362859</v>
       </c>
       <c r="BB18" t="n">
         <v>68.0818331262815</v>
@@ -9513,28 +9513,28 @@
         <v>0.4854848696430998</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.6905510298714843</v>
+        <v>0.6905510298714844</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.8358940932905661</v>
+        <v>0.8358940932905663</v>
       </c>
       <c r="BH18" t="n">
-        <v>13.9706521433974</v>
+        <v>13.97065214339741</v>
       </c>
       <c r="BI18" t="n">
         <v>0.5761061180904167</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.002297086572761169</v>
+        <v>0.00229708657276117</v>
       </c>
       <c r="BK18" t="n">
-        <v>8.831576217316703</v>
+        <v>8.831576217316705</v>
       </c>
       <c r="BL18" t="n">
         <v>0.1258254157547768</v>
       </c>
       <c r="BM18" t="n">
-        <v>24.82385990061706</v>
+        <v>24.82385990061704</v>
       </c>
       <c r="BN18" t="n">
         <v>1.558043731696295</v>
@@ -9552,13 +9552,13 @@
         <v>0.1111202260536448</v>
       </c>
       <c r="BS18" t="n">
-        <v>17.93867995912189</v>
+        <v>17.9386799591219</v>
       </c>
       <c r="BT18" t="n">
-        <v>5.431101620617825</v>
+        <v>5.431101620617826</v>
       </c>
       <c r="BU18" t="n">
-        <v>3.140371146369913</v>
+        <v>3.140371146369914</v>
       </c>
       <c r="BV18" t="n">
         <v>3.263613274909258</v>
@@ -9576,7 +9576,7 @@
         <v>2.853065271852293</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.07569175457430553</v>
+        <v>0.07569175457430552</v>
       </c>
       <c r="CB18" t="n">
         <v>0.4643978015188598</v>
@@ -9597,13 +9597,13 @@
         <v>1.941317000982244</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.4207049694510193</v>
+        <v>0.4207049694510192</v>
       </c>
       <c r="CI18" t="n">
         <v>0.2227027841446452</v>
       </c>
       <c r="CJ18" t="n">
-        <v>3.739191187375784</v>
+        <v>3.739191187375785</v>
       </c>
       <c r="CK18" t="n">
         <v>0.006326157532838396</v>
@@ -9621,10 +9621,10 @@
         <v>2.548811120263291</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.6217817696471721</v>
+        <v>0.621781769647172</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.6336853379094591</v>
+        <v>0.633685337909459</v>
       </c>
       <c r="CR18" t="n">
         <v>0.6045335162258804</v>
@@ -9672,19 +9672,19 @@
         <v>0.5029585851291909</v>
       </c>
       <c r="DG18" t="n">
-        <v>5.348155786784832</v>
+        <v>5.34815578678483</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.4663618835657086</v>
+        <v>0.4663618835657087</v>
       </c>
       <c r="DI18" t="n">
         <v>0.1247185211256902</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.04887452673400482</v>
+        <v>0.04887452673400481</v>
       </c>
       <c r="DK18" t="n">
-        <v>0.9809816707575172</v>
+        <v>0.980981670757517</v>
       </c>
       <c r="DL18" t="n">
         <v>0.1760549860689678</v>
@@ -9696,7 +9696,7 @@
         <v>0.02873029736743081</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.010340618104769</v>
+        <v>1.01034061810477</v>
       </c>
       <c r="DP18" t="n">
         <v>253.2538501704686</v>
@@ -9720,7 +9720,7 @@
         <v>0.0791418077117118</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.6171494618153189</v>
+        <v>0.617149461815319</v>
       </c>
       <c r="DX18" t="n">
         <v>0.5880162834958484</v>
@@ -9744,13 +9744,13 @@
         <v>0.004711373892475688</v>
       </c>
       <c r="EE18" t="n">
-        <v>0.09123032222020939</v>
+        <v>0.09123032222020941</v>
       </c>
       <c r="EF18" t="n">
-        <v>0.001641131796296526</v>
+        <v>0.001641131796296527</v>
       </c>
       <c r="EG18" t="n">
-        <v>0.05595093132880289</v>
+        <v>0.05595093132880288</v>
       </c>
       <c r="EH18" t="n">
         <v>0.0345843758289333</v>
@@ -9850,28 +9850,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>448.8247288819241</v>
+        <v>448.8247288819235</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5580478351504096</v>
+        <v>0.5580478351504095</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9224246385322584</v>
+        <v>0.9224246385322585</v>
       </c>
       <c r="E19" t="n">
         <v>10.74934796496974</v>
       </c>
       <c r="F19" t="n">
-        <v>269.2484509264086</v>
+        <v>269.2484509264083</v>
       </c>
       <c r="G19" t="n">
-        <v>785.7650879781927</v>
+        <v>785.765087978192</v>
       </c>
       <c r="H19" t="n">
         <v>286.234307123676</v>
       </c>
       <c r="I19" t="n">
-        <v>77.01204798802522</v>
+        <v>77.0120479880252</v>
       </c>
       <c r="J19" t="n">
         <v>21.25938443433023</v>
@@ -9880,13 +9880,13 @@
         <v>117.9812102547329</v>
       </c>
       <c r="L19" t="n">
-        <v>34.87168598776997</v>
+        <v>34.87168598776994</v>
       </c>
       <c r="M19" t="n">
         <v>3.986433630032791</v>
       </c>
       <c r="N19" t="n">
-        <v>17.08224206893463</v>
+        <v>17.08224206893462</v>
       </c>
       <c r="O19" t="n">
         <v>4.254430363801599</v>
@@ -9895,16 +9895,16 @@
         <v>5.006679935035801</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.704989322128011</v>
+        <v>6.704989322128009</v>
       </c>
       <c r="R19" t="n">
-        <v>9.028734150007701</v>
+        <v>9.028734150007697</v>
       </c>
       <c r="S19" t="n">
         <v>4.182635611530205</v>
       </c>
       <c r="T19" t="n">
-        <v>17.12089756026326</v>
+        <v>17.12089756026327</v>
       </c>
       <c r="U19" t="n">
         <v>0.02893467159938666</v>
@@ -9913,25 +9913,25 @@
         <v>1.445287994098645</v>
       </c>
       <c r="W19" t="n">
-        <v>61.97072864975441</v>
+        <v>61.97072864975439</v>
       </c>
       <c r="X19" t="n">
-        <v>0.4057598674094484</v>
+        <v>0.4057598674094485</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.937660405606107</v>
+        <v>3.937660405606108</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.984225577084572</v>
+        <v>3.984225577084573</v>
       </c>
       <c r="AA19" t="n">
-        <v>57.57534920434807</v>
+        <v>57.57534920434809</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.7692599133981048</v>
+        <v>0.7692599133981047</v>
       </c>
       <c r="AC19" t="n">
-        <v>30.87203135452537</v>
+        <v>30.87203135452538</v>
       </c>
       <c r="AD19" t="n">
         <v>0.03762621860516217</v>
@@ -9940,16 +9940,16 @@
         <v>0.009678379455482436</v>
       </c>
       <c r="AF19" t="n">
-        <v>74.25901315828331</v>
+        <v>74.25901315828332</v>
       </c>
       <c r="AG19" t="n">
-        <v>39.01559282927752</v>
+        <v>39.01559282927751</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.086229208040844</v>
+        <v>2.086229208040842</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.667507511373176</v>
+        <v>1.667507511373175</v>
       </c>
       <c r="AJ19" t="n">
         <v>3.490201020686051</v>
@@ -9958,7 +9958,7 @@
         <v>16.09873236260819</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.7224778093726276</v>
+        <v>0.7224778093726278</v>
       </c>
       <c r="AM19" t="n">
         <v>0.3385117436309611</v>
@@ -9967,13 +9967,13 @@
         <v>0.2597562821048839</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.5045882975581968</v>
+        <v>0.5045882975581967</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.4612020433625663</v>
+        <v>0.4612020433625662</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.871157889002288</v>
+        <v>1.871157889002289</v>
       </c>
       <c r="AR19" t="n">
         <v>10.21186387658839</v>
@@ -9988,7 +9988,7 @@
         <v>0.2941269442488873</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.468889665806282</v>
+        <v>5.46888966580628</v>
       </c>
       <c r="AW19" t="n">
         <v>6.067849628342474</v>
@@ -9997,34 +9997,34 @@
         <v>0.3253991120492345</v>
       </c>
       <c r="AY19" t="n">
-        <v>79.43649960610362</v>
+        <v>79.43649960610364</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.6393289829530446</v>
+        <v>0.6393289829530447</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.08027789510327019</v>
+        <v>0.0802778951032702</v>
       </c>
       <c r="BB19" t="n">
-        <v>67.54040679039807</v>
+        <v>67.54040679039808</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.586134288915918</v>
+        <v>6.586134288915915</v>
       </c>
       <c r="BD19" t="n">
-        <v>33.68994732335536</v>
+        <v>33.68994732335538</v>
       </c>
       <c r="BE19" t="n">
         <v>0.5083179191588839</v>
       </c>
       <c r="BF19" t="n">
-        <v>0.6905632149585154</v>
+        <v>0.6905632149585152</v>
       </c>
       <c r="BG19" t="n">
         <v>0.9534817720727392</v>
       </c>
       <c r="BH19" t="n">
-        <v>14.59932269287498</v>
+        <v>14.59932269287497</v>
       </c>
       <c r="BI19" t="n">
         <v>0.5208319884479181</v>
@@ -10039,10 +10039,10 @@
         <v>0.1212508408923788</v>
       </c>
       <c r="BM19" t="n">
-        <v>27.11831060220082</v>
+        <v>27.11831060220081</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.491737739410398</v>
+        <v>1.491737739410399</v>
       </c>
       <c r="BO19" t="n">
         <v>0.03374899302145457</v>
@@ -10060,19 +10060,19 @@
         <v>18.34885510296303</v>
       </c>
       <c r="BT19" t="n">
-        <v>6.941913179724764</v>
+        <v>6.941913179724765</v>
       </c>
       <c r="BU19" t="n">
-        <v>3.199083838448153</v>
+        <v>3.199083838448154</v>
       </c>
       <c r="BV19" t="n">
-        <v>3.633930412665087</v>
+        <v>3.633930412665086</v>
       </c>
       <c r="BW19" t="n">
-        <v>0.007991089357987535</v>
+        <v>0.007991089357987537</v>
       </c>
       <c r="BX19" t="n">
-        <v>2.905019319809834</v>
+        <v>2.905019319809835</v>
       </c>
       <c r="BY19" t="n">
         <v>0.1281563934325669</v>
@@ -10090,7 +10090,7 @@
         <v>0.1131544706672763</v>
       </c>
       <c r="CD19" t="n">
-        <v>0.2899206521774501</v>
+        <v>0.2899206521774502</v>
       </c>
       <c r="CE19" t="n">
         <v>7.089961413254848</v>
@@ -10114,7 +10114,7 @@
         <v>0.00635996377835817</v>
       </c>
       <c r="CL19" t="n">
-        <v>0.4798162831858709</v>
+        <v>0.479816283185871</v>
       </c>
       <c r="CM19" t="n">
         <v>0.02099124758965534</v>
@@ -10126,19 +10126,19 @@
         <v>1.884495547139693</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.6860214198591613</v>
+        <v>0.6860214198591614</v>
       </c>
       <c r="CQ19" t="n">
-        <v>0.672750971014471</v>
+        <v>0.6727509710144711</v>
       </c>
       <c r="CR19" t="n">
-        <v>0.5858840725609685</v>
+        <v>0.5858840725609684</v>
       </c>
       <c r="CS19" t="n">
         <v>0.1371763294525771</v>
       </c>
       <c r="CT19" t="n">
-        <v>0.2400608097112797</v>
+        <v>0.2400608097112796</v>
       </c>
       <c r="CU19" t="n">
         <v>0.154169627035524</v>
@@ -10150,7 +10150,7 @@
         <v>0.4796167721842459</v>
       </c>
       <c r="CX19" t="n">
-        <v>4.323559000243051</v>
+        <v>4.32355900024305</v>
       </c>
       <c r="CY19" t="n">
         <v>0.08549185195936546</v>
@@ -10168,7 +10168,7 @@
         <v>0.1974329715431272</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.271951823513563</v>
+        <v>1.271951823513564</v>
       </c>
       <c r="DE19" t="n">
         <v>0.007869031590050566</v>
@@ -10177,10 +10177,10 @@
         <v>0.3953490814184847</v>
       </c>
       <c r="DG19" t="n">
-        <v>5.34308373933038</v>
+        <v>5.343083739330379</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.4871132460500389</v>
+        <v>0.487113246050039</v>
       </c>
       <c r="DI19" t="n">
         <v>0.1095440100711572</v>
@@ -10210,7 +10210,7 @@
         <v>0.00626703978837724</v>
       </c>
       <c r="DR19" t="n">
-        <v>0.05580483740390496</v>
+        <v>0.05580483740390497</v>
       </c>
       <c r="DS19" t="n">
         <v>2.958252027001548</v>
@@ -10243,13 +10243,13 @@
         <v>0.2276105817607756</v>
       </c>
       <c r="EC19" t="n">
-        <v>6.995052901601812</v>
+        <v>6.995052901601811</v>
       </c>
       <c r="ED19" t="n">
-        <v>0.006278111539059244</v>
+        <v>0.006278111539059245</v>
       </c>
       <c r="EE19" t="n">
-        <v>0.09785536894197601</v>
+        <v>0.09785536894197602</v>
       </c>
       <c r="EF19" t="n">
         <v>0.001777674644798384</v>

--- a/data/proteomics/rosemary_data_analysis.xlsx
+++ b/data/proteomics/rosemary_data_analysis.xlsx
@@ -1265,10 +1265,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>175.2179951479615</v>
+        <v>175.2179951479617</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3708259819820348</v>
+        <v>0.3708259819820346</v>
       </c>
       <c r="D2" t="n">
         <v>0.2768303852909352</v>
@@ -1277,10 +1277,10 @@
         <v>3.195561510640327</v>
       </c>
       <c r="F2" t="n">
-        <v>104.4945795180777</v>
+        <v>104.4945795180778</v>
       </c>
       <c r="G2" t="n">
-        <v>227.0895431527453</v>
+        <v>227.0895431527457</v>
       </c>
       <c r="H2" t="n">
         <v>105.1013304776598</v>
@@ -1292,16 +1292,16 @@
         <v>7.723574480334038</v>
       </c>
       <c r="K2" t="n">
-        <v>44.88391858779396</v>
+        <v>44.88391858779397</v>
       </c>
       <c r="L2" t="n">
-        <v>12.37121765109383</v>
+        <v>12.3712176510938</v>
       </c>
       <c r="M2" t="n">
         <v>1.594856480246182</v>
       </c>
       <c r="N2" t="n">
-        <v>8.834259072602096</v>
+        <v>8.834259072602103</v>
       </c>
       <c r="O2" t="n">
         <v>1.357937390230849</v>
@@ -1313,13 +1313,13 @@
         <v>3.080177624420704</v>
       </c>
       <c r="R2" t="n">
-        <v>2.697049978710424</v>
+        <v>2.697049978710423</v>
       </c>
       <c r="S2" t="n">
-        <v>1.39461808147511</v>
+        <v>1.394618081475111</v>
       </c>
       <c r="T2" t="n">
-        <v>4.335169502189709</v>
+        <v>4.335169502189708</v>
       </c>
       <c r="U2" t="n">
         <v>0.009573886901756628</v>
@@ -1337,16 +1337,16 @@
         <v>1.293725227694882</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.319501117518227</v>
+        <v>1.319501117518226</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.4045486148806</v>
+        <v>9.404548614880595</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2966098180711586</v>
+        <v>0.2966098180711587</v>
       </c>
       <c r="AC2" t="n">
-        <v>14.47655535680351</v>
+        <v>14.4765553568035</v>
       </c>
       <c r="AD2" t="n">
         <v>0.02335576616544602</v>
@@ -1355,13 +1355,13 @@
         <v>0.00432217813430556</v>
       </c>
       <c r="AF2" t="n">
-        <v>19.93820832675885</v>
+        <v>19.93820832675886</v>
       </c>
       <c r="AG2" t="n">
-        <v>17.68637931207861</v>
+        <v>17.68637931207862</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.6398987966166346</v>
+        <v>0.6398987966166347</v>
       </c>
       <c r="AI2" t="n">
         <v>0.4744506766882924</v>
@@ -1370,7 +1370,7 @@
         <v>1.154579907299943</v>
       </c>
       <c r="AK2" t="n">
-        <v>6.0975468137594</v>
+        <v>6.097546813759397</v>
       </c>
       <c r="AL2" t="n">
         <v>0.3067922242723701</v>
@@ -1409,13 +1409,13 @@
         <v>1.579735841505124</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.088601724316052</v>
+        <v>0.08860172431605201</v>
       </c>
       <c r="AY2" t="n">
         <v>12.07289188279469</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.2072592936204653</v>
+        <v>0.2072592936204654</v>
       </c>
       <c r="BA2" t="n">
         <v>0.04237688422225861</v>
@@ -1424,7 +1424,7 @@
         <v>20.05955599835348</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.436010129408095</v>
+        <v>2.436010129408096</v>
       </c>
       <c r="BD2" t="n">
         <v>9.002219528609345</v>
@@ -1436,10 +1436,10 @@
         <v>0.296847937172884</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.3665211324782944</v>
+        <v>0.3665211324782945</v>
       </c>
       <c r="BH2" t="n">
-        <v>4.161584142186904</v>
+        <v>4.161584142186905</v>
       </c>
       <c r="BI2" t="n">
         <v>0.1974613923869827</v>
@@ -1457,7 +1457,7 @@
         <v>14.00103691004356</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.5521138996539522</v>
+        <v>0.5521138996539524</v>
       </c>
       <c r="BO2" t="n">
         <v>0.02377993909405592</v>
@@ -1478,7 +1478,7 @@
         <v>1.798067067815747</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.357891277061867</v>
+        <v>1.357891277061868</v>
       </c>
       <c r="BV2" t="n">
         <v>1.302261208263902</v>
@@ -1517,7 +1517,7 @@
         <v>1.135079953708245</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.15282476319892</v>
+        <v>0.1528247631989199</v>
       </c>
       <c r="CI2" t="n">
         <v>0.02319838407489109</v>
@@ -1553,10 +1553,10 @@
         <v>0.0313110643391484</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.06531892543288959</v>
+        <v>0.06531892543288957</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.03924334014375773</v>
+        <v>0.03924334014375772</v>
       </c>
       <c r="CV2" t="n">
         <v>0.1067341807237032</v>
@@ -1571,7 +1571,7 @@
         <v>0.03447032355374471</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.09044645776645846</v>
+        <v>0.09044645776645845</v>
       </c>
       <c r="DA2" t="n">
         <v>0.1027709313058061</v>
@@ -1583,7 +1583,7 @@
         <v>0.05829479483327835</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.5101234225125986</v>
+        <v>0.5101234225125983</v>
       </c>
       <c r="DE2" t="n">
         <v>0.003225085172898607</v>
@@ -1613,13 +1613,13 @@
         <v>0.04967568699280182</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.008082196718031924</v>
+        <v>0.008082196718031922</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.2925431235820296</v>
+        <v>0.2925431235820297</v>
       </c>
       <c r="DP2" t="n">
-        <v>36.39399150982232</v>
+        <v>36.39399150982231</v>
       </c>
       <c r="DQ2" t="n">
         <v>0.004178621764955158</v>
@@ -1631,7 +1631,7 @@
         <v>0.9399657643332729</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.6172335740725087</v>
+        <v>0.6172335740725086</v>
       </c>
       <c r="DU2" t="n">
         <v>1.632089249198855</v>
@@ -1646,7 +1646,7 @@
         <v>0.2723055335375116</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.08146352898443948</v>
+        <v>0.0814635289844395</v>
       </c>
       <c r="DZ2" t="n">
         <v>0.05898244268949321</v>
@@ -1664,7 +1664,7 @@
         <v>0.003631984596370452</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.03548847653947745</v>
+        <v>0.03548847653947744</v>
       </c>
       <c r="EF2" t="n">
         <v>0.001121373595968469</v>
@@ -1673,7 +1673,7 @@
         <v>0.02166118843978278</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.0126749423972466</v>
+        <v>0.01267494239724661</v>
       </c>
       <c r="EI2" t="n">
         <v>0.01112961171932348</v>
@@ -1770,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>160.0444973878097</v>
+        <v>160.04449738781</v>
       </c>
       <c r="C3" t="n">
         <v>0.3520361165960142</v>
@@ -1782,16 +1782,16 @@
         <v>2.95094109772652</v>
       </c>
       <c r="F3" t="n">
-        <v>95.81337389222566</v>
+        <v>95.81337389222553</v>
       </c>
       <c r="G3" t="n">
-        <v>206.7361723285035</v>
+        <v>206.7361723285037</v>
       </c>
       <c r="H3" t="n">
-        <v>92.52612055309257</v>
+        <v>92.52612055309245</v>
       </c>
       <c r="I3" t="n">
-        <v>27.36723455464773</v>
+        <v>27.36723455464774</v>
       </c>
       <c r="J3" t="n">
         <v>6.985257395245154</v>
@@ -1806,34 +1806,34 @@
         <v>1.391237317232775</v>
       </c>
       <c r="N3" t="n">
-        <v>8.706356576039489</v>
+        <v>8.706356576039491</v>
       </c>
       <c r="O3" t="n">
         <v>1.326201247497412</v>
       </c>
       <c r="P3" t="n">
-        <v>1.79047701018833</v>
+        <v>1.790477010188329</v>
       </c>
       <c r="Q3" t="n">
         <v>2.344927407504835</v>
       </c>
       <c r="R3" t="n">
-        <v>2.367569589075473</v>
+        <v>2.367569589075471</v>
       </c>
       <c r="S3" t="n">
         <v>1.253350678060727</v>
       </c>
       <c r="T3" t="n">
-        <v>3.77073536509215</v>
+        <v>3.770735365092149</v>
       </c>
       <c r="U3" t="n">
         <v>0.007685929356725506</v>
       </c>
       <c r="V3" t="n">
-        <v>0.4638494644943264</v>
+        <v>0.4638494644943265</v>
       </c>
       <c r="W3" t="n">
-        <v>18.03371716911288</v>
+        <v>18.03371716911289</v>
       </c>
       <c r="X3" t="n">
         <v>0.1000493163611742</v>
@@ -1845,13 +1845,13 @@
         <v>1.225252673207757</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.081672728719518</v>
+        <v>8.081672728719516</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2735237095728638</v>
+        <v>0.2735237095728636</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.99912192870183</v>
+        <v>13.99912192870184</v>
       </c>
       <c r="AD3" t="n">
         <v>0.02072222810167829</v>
@@ -1875,10 +1875,10 @@
         <v>1.035954553688365</v>
       </c>
       <c r="AK3" t="n">
-        <v>5.114140316126429</v>
+        <v>5.114140316126428</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.2886299712415187</v>
+        <v>0.2886299712415188</v>
       </c>
       <c r="AM3" t="n">
         <v>0.1421580374637516</v>
@@ -1893,10 +1893,10 @@
         <v>0.1880787036243458</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.4059216546935469</v>
+        <v>0.4059216546935468</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.594633508041459</v>
+        <v>2.59463350804146</v>
       </c>
       <c r="AS3" t="n">
         <v>0.05768933578430236</v>
@@ -1914,7 +1914,7 @@
         <v>1.424304970863882</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.07462511893453966</v>
+        <v>0.07462511893453967</v>
       </c>
       <c r="AY3" t="n">
         <v>10.58004088646318</v>
@@ -1923,22 +1923,22 @@
         <v>0.1889226046138226</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0410082721530399</v>
+        <v>0.04100827215303991</v>
       </c>
       <c r="BB3" t="n">
-        <v>18.21345737108491</v>
+        <v>18.21345737108492</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.110080126989678</v>
+        <v>2.110080126989677</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.001800521808399</v>
+        <v>8.001800521808397</v>
       </c>
       <c r="BE3" t="n">
         <v>0.1588400189496464</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.2761931299905347</v>
+        <v>0.2761931299905348</v>
       </c>
       <c r="BG3" t="n">
         <v>0.2616070552258732</v>
@@ -1947,13 +1947,13 @@
         <v>3.649819862934674</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.2067498450747351</v>
+        <v>0.2067498450747352</v>
       </c>
       <c r="BJ3" t="n">
         <v>0.004054377887903056</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.359220212472147</v>
+        <v>7.359220212472145</v>
       </c>
       <c r="BL3" t="n">
         <v>0.02119374383137082</v>
@@ -1962,7 +1962,7 @@
         <v>13.38141274543271</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.4811467776143714</v>
+        <v>0.4811467776143715</v>
       </c>
       <c r="BO3" t="n">
         <v>0.02175221901825343</v>
@@ -1977,7 +1977,7 @@
         <v>0.214230053281147</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.267283128133084</v>
+        <v>9.267283128133087</v>
       </c>
       <c r="BT3" t="n">
         <v>1.662696460290599</v>
@@ -1986,7 +1986,7 @@
         <v>1.266259381382844</v>
       </c>
       <c r="BV3" t="n">
-        <v>1.212096825122384</v>
+        <v>1.212096825122385</v>
       </c>
       <c r="BW3" t="n">
         <v>0.003160460350449546</v>
@@ -1995,13 +1995,13 @@
         <v>0.8945888726264916</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.02675760155556803</v>
+        <v>0.02675760155556802</v>
       </c>
       <c r="BZ3" t="n">
         <v>3.217750426976056</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.03475503153733589</v>
+        <v>0.0347550315373359</v>
       </c>
       <c r="CB3" t="n">
         <v>0.08709391164304661</v>
@@ -2052,7 +2052,7 @@
         <v>0.4533992482492632</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1348887318010449</v>
+        <v>0.1348887318010448</v>
       </c>
       <c r="CS3" t="n">
         <v>0.03290787691352896</v>
@@ -2067,7 +2067,7 @@
         <v>0.09507465060253627</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1680631214467079</v>
+        <v>0.1680631214467078</v>
       </c>
       <c r="CX3" t="n">
         <v>1.386124320750141</v>
@@ -2088,7 +2088,7 @@
         <v>0.04917303096118841</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.4630616644207624</v>
+        <v>0.4630616644207625</v>
       </c>
       <c r="DE3" t="n">
         <v>0.002714044211247651</v>
@@ -2097,7 +2097,7 @@
         <v>0.1330655795682035</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.216055675415121</v>
+        <v>2.21605567541512</v>
       </c>
       <c r="DH3" t="n">
         <v>0.1506828198713857</v>
@@ -2109,37 +2109,37 @@
         <v>0.01585215960085824</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.2596177988731838</v>
+        <v>0.2596177988731837</v>
       </c>
       <c r="DL3" t="n">
         <v>0.0830215154054517</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.04448405329343224</v>
+        <v>0.04448405329343223</v>
       </c>
       <c r="DN3" t="n">
         <v>0.007138246939998015</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.2459295862975192</v>
+        <v>0.2459295862975193</v>
       </c>
       <c r="DP3" t="n">
-        <v>31.68529641612839</v>
+        <v>31.6852964161284</v>
       </c>
       <c r="DQ3" t="n">
         <v>0.003816833364138418</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.03283467127118722</v>
+        <v>0.03283467127118721</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.8700527698978928</v>
+        <v>0.870052769897893</v>
       </c>
       <c r="DT3" t="n">
         <v>0.5288835120296254</v>
       </c>
       <c r="DU3" t="n">
-        <v>1.503509674621542</v>
+        <v>1.503509674621543</v>
       </c>
       <c r="DV3" t="n">
         <v>0.0212096346627163</v>
@@ -2181,7 +2181,7 @@
         <v>0.01208350221848329</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.01097461440130992</v>
+        <v>0.01097461440130991</v>
       </c>
       <c r="EJ3" t="n">
         <v>0.01090379259237593</v>
@@ -2275,22 +2275,22 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>168.5410689658389</v>
+        <v>168.5410689658385</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3209661646476563</v>
+        <v>0.3209661646476562</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2878897626554287</v>
+        <v>0.2878897626554286</v>
       </c>
       <c r="E4" t="n">
         <v>2.990751305452866</v>
       </c>
       <c r="F4" t="n">
-        <v>102.9450256576945</v>
+        <v>102.9450256576946</v>
       </c>
       <c r="G4" t="n">
-        <v>213.7851497908103</v>
+        <v>213.7851497908105</v>
       </c>
       <c r="H4" t="n">
         <v>90.77862659703366</v>
@@ -2302,13 +2302,13 @@
         <v>7.069936299724761</v>
       </c>
       <c r="K4" t="n">
-        <v>34.16741458109772</v>
+        <v>34.16741458109771</v>
       </c>
       <c r="L4" t="n">
         <v>10.99321760413046</v>
       </c>
       <c r="M4" t="n">
-        <v>1.432905886592719</v>
+        <v>1.432905886592718</v>
       </c>
       <c r="N4" t="n">
         <v>10.01133393430948</v>
@@ -2317,19 +2317,19 @@
         <v>1.391707305891973</v>
       </c>
       <c r="P4" t="n">
-        <v>1.675540337076725</v>
+        <v>1.675540337076726</v>
       </c>
       <c r="Q4" t="n">
         <v>2.474702807906972</v>
       </c>
       <c r="R4" t="n">
-        <v>2.251324005595607</v>
+        <v>2.251324005595604</v>
       </c>
       <c r="S4" t="n">
         <v>1.282973572231973</v>
       </c>
       <c r="T4" t="n">
-        <v>4.197775951766889</v>
+        <v>4.19777595176689</v>
       </c>
       <c r="U4" t="n">
         <v>0.006821899707863335</v>
@@ -2350,7 +2350,7 @@
         <v>1.157232547934686</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.82600546099248</v>
+        <v>8.826005460992482</v>
       </c>
       <c r="AB4" t="n">
         <v>0.3179767014571709</v>
@@ -2368,10 +2368,10 @@
         <v>24.53759922338813</v>
       </c>
       <c r="AG4" t="n">
-        <v>19.60435263495348</v>
+        <v>19.60435263495347</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.5582690650600813</v>
+        <v>0.5582690650600812</v>
       </c>
       <c r="AI4" t="n">
         <v>0.4276884542506333</v>
@@ -2380,7 +2380,7 @@
         <v>1.060101421488198</v>
       </c>
       <c r="AK4" t="n">
-        <v>5.699036768997355</v>
+        <v>5.699036768997353</v>
       </c>
       <c r="AL4" t="n">
         <v>0.3075289005296661</v>
@@ -2389,10 +2389,10 @@
         <v>0.1582238575697932</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.08033090647511303</v>
+        <v>0.08033090647511304</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1818800407645292</v>
+        <v>0.1818800407645293</v>
       </c>
       <c r="AP4" t="n">
         <v>0.2052720760341419</v>
@@ -2401,7 +2401,7 @@
         <v>0.444261604002967</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.41172968061775</v>
+        <v>2.411729680617749</v>
       </c>
       <c r="AS4" t="n">
         <v>0.05867967829297586</v>
@@ -2413,13 +2413,13 @@
         <v>0.1273707029964871</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.464585610619853</v>
+        <v>1.464585610619854</v>
       </c>
       <c r="AW4" t="n">
         <v>1.326429855834397</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.08198445385099677</v>
+        <v>0.0819844538509968</v>
       </c>
       <c r="AY4" t="n">
         <v>10.53355234849261</v>
@@ -2434,10 +2434,10 @@
         <v>18.99311284141382</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.277600249919772</v>
+        <v>2.277600249919771</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.310901666166226</v>
+        <v>8.310901666166227</v>
       </c>
       <c r="BE4" t="n">
         <v>0.1976847099264051</v>
@@ -2446,7 +2446,7 @@
         <v>0.2793889979108572</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.332311477815813</v>
+        <v>0.3323114778158129</v>
       </c>
       <c r="BH4" t="n">
         <v>4.170236557246419</v>
@@ -2473,7 +2473,7 @@
         <v>0.02091373098466211</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.08065678586299248</v>
+        <v>0.08065678586299246</v>
       </c>
       <c r="BQ4" t="n">
         <v>0.1205506415412189</v>
@@ -2488,10 +2488,10 @@
         <v>1.675966094995908</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.247334570870389</v>
+        <v>1.24733457087039</v>
       </c>
       <c r="BV4" t="n">
-        <v>1.269278501060561</v>
+        <v>1.269278501060562</v>
       </c>
       <c r="BW4" t="n">
         <v>0.00352918485838404</v>
@@ -2506,10 +2506,10 @@
         <v>3.02942983861229</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.03389489950402369</v>
+        <v>0.03389489950402368</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.08973841631731856</v>
+        <v>0.08973841631731855</v>
       </c>
       <c r="CC4" t="n">
         <v>0.05839908678499228</v>
@@ -2581,19 +2581,19 @@
         <v>0.03283430285606561</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.08381819822522084</v>
+        <v>0.08381819822522082</v>
       </c>
       <c r="DA4" t="n">
         <v>0.0859809181655553</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.2165407554716994</v>
+        <v>0.2165407554716995</v>
       </c>
       <c r="DC4" t="n">
         <v>0.03823434648983214</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.4783541097144987</v>
+        <v>0.4783541097144988</v>
       </c>
       <c r="DE4" t="n">
         <v>0.003100618076203938</v>
@@ -2617,16 +2617,16 @@
         <v>0.2643634038236027</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0870420491802058</v>
+        <v>0.08704204918020579</v>
       </c>
       <c r="DM4" t="n">
         <v>0.04344081938351101</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.006094396892213332</v>
+        <v>0.006094396892213333</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.2711962596178854</v>
+        <v>0.2711962596178853</v>
       </c>
       <c r="DP4" t="n">
         <v>33.57958085110323</v>
@@ -2638,7 +2638,7 @@
         <v>0.03143354882417708</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.8946711411131363</v>
+        <v>0.8946711411131362</v>
       </c>
       <c r="DT4" t="n">
         <v>0.5413122800739331</v>
@@ -2650,7 +2650,7 @@
         <v>0.02000814786674313</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.09986227523868142</v>
+        <v>0.09986227523868141</v>
       </c>
       <c r="DX4" t="n">
         <v>0.2455474380539036</v>
@@ -2686,7 +2686,7 @@
         <v>0.008234922781882596</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.007180006235608428</v>
+        <v>0.007180006235608427</v>
       </c>
       <c r="EJ4" t="n">
         <v>0.01115794498943608</v>
@@ -2780,10 +2780,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>132.4694784504293</v>
+        <v>132.4694784504292</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2823721465399683</v>
+        <v>0.2823721465399684</v>
       </c>
       <c r="D5" t="n">
         <v>0.2751683226782104</v>
@@ -2792,31 +2792,31 @@
         <v>3.05007442285754</v>
       </c>
       <c r="F5" t="n">
-        <v>80.27718466102294</v>
+        <v>80.27718466102299</v>
       </c>
       <c r="G5" t="n">
-        <v>176.2278896016975</v>
+        <v>176.2278896016973</v>
       </c>
       <c r="H5" t="n">
-        <v>79.86886913329829</v>
+        <v>79.86886913329825</v>
       </c>
       <c r="I5" t="n">
-        <v>21.94003474662141</v>
+        <v>21.9400347466214</v>
       </c>
       <c r="J5" t="n">
         <v>7.427702411489458</v>
       </c>
       <c r="K5" t="n">
-        <v>30.43728128847774</v>
+        <v>30.43728128847775</v>
       </c>
       <c r="L5" t="n">
-        <v>10.19134887106634</v>
+        <v>10.19134887106635</v>
       </c>
       <c r="M5" t="n">
         <v>1.483570131170016</v>
       </c>
       <c r="N5" t="n">
-        <v>6.530599188264407</v>
+        <v>6.530599188264409</v>
       </c>
       <c r="O5" t="n">
         <v>1.116094841154244</v>
@@ -2828,10 +2828,10 @@
         <v>2.342396619992761</v>
       </c>
       <c r="R5" t="n">
-        <v>2.131324671124972</v>
+        <v>2.131324671124971</v>
       </c>
       <c r="S5" t="n">
-        <v>1.248900046263693</v>
+        <v>1.248900046263694</v>
       </c>
       <c r="T5" t="n">
         <v>3.880091227827486</v>
@@ -2855,10 +2855,10 @@
         <v>1.273148867528968</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.461035997767326</v>
+        <v>8.461035997767327</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.2737142751873576</v>
+        <v>0.2737142751873577</v>
       </c>
       <c r="AC5" t="n">
         <v>11.67889802480416</v>
@@ -2870,13 +2870,13 @@
         <v>0.003732364605354748</v>
       </c>
       <c r="AF5" t="n">
-        <v>16.48422927123905</v>
+        <v>16.48422927123904</v>
       </c>
       <c r="AG5" t="n">
         <v>16.60027697863732</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.4923282737418817</v>
+        <v>0.4923282737418818</v>
       </c>
       <c r="AI5" t="n">
         <v>0.3947914557885837</v>
@@ -2903,10 +2903,10 @@
         <v>0.187438978131869</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.4067174542639535</v>
+        <v>0.4067174542639536</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.391574091326178</v>
+        <v>2.391574091326179</v>
       </c>
       <c r="AS5" t="n">
         <v>0.05347339224858023</v>
@@ -2924,7 +2924,7 @@
         <v>1.450549665498404</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.06922494332878612</v>
+        <v>0.06922494332878613</v>
       </c>
       <c r="AY5" t="n">
         <v>10.44642706198168</v>
@@ -2933,7 +2933,7 @@
         <v>0.1871588238984855</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.03380066366290122</v>
+        <v>0.03380066366290121</v>
       </c>
       <c r="BB5" t="n">
         <v>13.6523022805223</v>
@@ -2954,7 +2954,7 @@
         <v>0.2480803905613383</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.649035203937602</v>
+        <v>4.649035203937604</v>
       </c>
       <c r="BI5" t="n">
         <v>0.1597263109206815</v>
@@ -2963,7 +2963,7 @@
         <v>0.001464764886426153</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.116440797995488</v>
+        <v>5.116440797995489</v>
       </c>
       <c r="BL5" t="n">
         <v>0.02333879309684798</v>
@@ -2972,7 +2972,7 @@
         <v>7.327267481926659</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.4553056621614988</v>
+        <v>0.4553056621614989</v>
       </c>
       <c r="BO5" t="n">
         <v>0.01867519038105681</v>
@@ -2990,7 +2990,7 @@
         <v>7.902609448048588</v>
       </c>
       <c r="BT5" t="n">
-        <v>1.557251233588107</v>
+        <v>1.557251233588106</v>
       </c>
       <c r="BU5" t="n">
         <v>1.124091596050999</v>
@@ -3002,7 +3002,7 @@
         <v>0.003097117446052133</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.8277236937358575</v>
+        <v>0.8277236937358576</v>
       </c>
       <c r="BY5" t="n">
         <v>0.02790055359240734</v>
@@ -3014,13 +3014,13 @@
         <v>0.03005004086549179</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.09397478314432429</v>
+        <v>0.09397478314432431</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.04240415639181689</v>
+        <v>0.0424041563918169</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.06961359750017056</v>
+        <v>0.06961359750017054</v>
       </c>
       <c r="CE5" t="n">
         <v>1.489757808396291</v>
@@ -3050,10 +3050,10 @@
         <v>0.008640558749067722</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.07100647611221503</v>
+        <v>0.07100647611221501</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.5143752206739165</v>
+        <v>0.5143752206739164</v>
       </c>
       <c r="CP5" t="n">
         <v>0.3101308455065021</v>
@@ -3062,7 +3062,7 @@
         <v>0.3906360062656105</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.1350146240585984</v>
+        <v>0.1350146240585985</v>
       </c>
       <c r="CS5" t="n">
         <v>0.0304712767108469</v>
@@ -3074,22 +3074,22 @@
         <v>0.04217129168419489</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.08995811277860048</v>
+        <v>0.0899581127786005</v>
       </c>
       <c r="CW5" t="n">
         <v>0.1270951775764464</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.185620187774639</v>
+        <v>1.185620187774638</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.03293331674025694</v>
+        <v>0.03293331674025695</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.08391294348413211</v>
+        <v>0.08391294348413214</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.08509178210180697</v>
+        <v>0.08509178210180696</v>
       </c>
       <c r="DB5" t="n">
         <v>0.1744340902489996</v>
@@ -3107,7 +3107,7 @@
         <v>0.1171107950438264</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.909036602409349</v>
+        <v>1.90903660240935</v>
       </c>
       <c r="DH5" t="n">
         <v>0.1495596709793175</v>
@@ -3122,7 +3122,7 @@
         <v>0.2537061034688015</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.07737431620378392</v>
+        <v>0.07737431620378393</v>
       </c>
       <c r="DM5" t="n">
         <v>0.04909478044309922</v>
@@ -3134,7 +3134,7 @@
         <v>0.3117246836364982</v>
       </c>
       <c r="DP5" t="n">
-        <v>31.78928049077359</v>
+        <v>31.78928049077357</v>
       </c>
       <c r="DQ5" t="n">
         <v>0.003141751802932435</v>
@@ -3143,10 +3143,10 @@
         <v>0.03031407201012781</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.7474726080203441</v>
+        <v>0.7474726080203442</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.524451519869751</v>
+        <v>0.5244515198697509</v>
       </c>
       <c r="DU5" t="n">
         <v>1.485075125507328</v>
@@ -3161,7 +3161,7 @@
         <v>0.2323648850570762</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.06161345630372916</v>
+        <v>0.06161345630372915</v>
       </c>
       <c r="DZ5" t="n">
         <v>0.04963612267915252</v>
@@ -3170,13 +3170,13 @@
         <v>0.1240649131257954</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.06981645244968782</v>
+        <v>0.06981645244968783</v>
       </c>
       <c r="EC5" t="n">
         <v>1.19648764895406</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.003265007207208154</v>
+        <v>0.003265007207208155</v>
       </c>
       <c r="EE5" t="n">
         <v>0.02164012952338443</v>
@@ -3188,7 +3188,7 @@
         <v>0.03011453156453951</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.01200460420857307</v>
+        <v>0.01200460420857306</v>
       </c>
       <c r="EI5" t="n">
         <v>0.01057830314920887</v>
@@ -3285,25 +3285,25 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>138.9107551105769</v>
+        <v>138.910755110577</v>
       </c>
       <c r="C6" t="n">
-        <v>0.293400146960464</v>
+        <v>0.2934001469604641</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2832108840463513</v>
+        <v>0.2832108840463514</v>
       </c>
       <c r="E6" t="n">
         <v>3.140448540665858</v>
       </c>
       <c r="F6" t="n">
-        <v>84.7860045561757</v>
+        <v>84.78600455617577</v>
       </c>
       <c r="G6" t="n">
-        <v>186.3067644873687</v>
+        <v>186.3067644873686</v>
       </c>
       <c r="H6" t="n">
-        <v>82.45308225254723</v>
+        <v>82.4530822525473</v>
       </c>
       <c r="I6" t="n">
         <v>23.26167918693907</v>
@@ -3315,13 +3315,13 @@
         <v>31.0882376660685</v>
       </c>
       <c r="L6" t="n">
-        <v>11.24906435751132</v>
+        <v>11.24906435751133</v>
       </c>
       <c r="M6" t="n">
         <v>1.704424547179815</v>
       </c>
       <c r="N6" t="n">
-        <v>7.555276016239143</v>
+        <v>7.555276016239142</v>
       </c>
       <c r="O6" t="n">
         <v>1.22339618336631</v>
@@ -3345,7 +3345,7 @@
         <v>0.007242617921602908</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4508700182311752</v>
+        <v>0.4508700182311753</v>
       </c>
       <c r="W6" t="n">
         <v>13.28492633742168</v>
@@ -3375,13 +3375,13 @@
         <v>0.003588195039972816</v>
       </c>
       <c r="AF6" t="n">
-        <v>17.46869108560829</v>
+        <v>17.4686910856083</v>
       </c>
       <c r="AG6" t="n">
         <v>17.20854420664552</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.5244004044507818</v>
+        <v>0.524400404450782</v>
       </c>
       <c r="AI6" t="n">
         <v>0.4040374514304064</v>
@@ -3390,7 +3390,7 @@
         <v>1.005831982981693</v>
       </c>
       <c r="AK6" t="n">
-        <v>5.202316019783635</v>
+        <v>5.202316019783636</v>
       </c>
       <c r="AL6" t="n">
         <v>0.2556200834535385</v>
@@ -3408,7 +3408,7 @@
         <v>0.1982811554629436</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.4522850142606717</v>
+        <v>0.4522850142606718</v>
       </c>
       <c r="AR6" t="n">
         <v>2.609562577499626</v>
@@ -3432,7 +3432,7 @@
         <v>0.07172424205200938</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.43091333113151</v>
+        <v>10.43091333113152</v>
       </c>
       <c r="AZ6" t="n">
         <v>0.1992711523650431</v>
@@ -3456,10 +3456,10 @@
         <v>0.2872729529123517</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.3395348092814299</v>
+        <v>0.3395348092814298</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.493469907462325</v>
+        <v>4.493469907462324</v>
       </c>
       <c r="BI6" t="n">
         <v>0.1611237707939304</v>
@@ -3498,7 +3498,7 @@
         <v>1.529452863138731</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.192844090757993</v>
+        <v>1.192844090757994</v>
       </c>
       <c r="BV6" t="n">
         <v>1.085565508241997</v>
@@ -3522,10 +3522,10 @@
         <v>0.0960544485675292</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.04513619269068151</v>
+        <v>0.04513619269068152</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.07423969407071399</v>
+        <v>0.07423969407071397</v>
       </c>
       <c r="CE6" t="n">
         <v>1.525422700373917</v>
@@ -3561,7 +3561,7 @@
         <v>0.547505922225374</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.3552305710103722</v>
+        <v>0.3552305710103723</v>
       </c>
       <c r="CQ6" t="n">
         <v>0.4343755437320184</v>
@@ -3570,16 +3570,16 @@
         <v>0.1517260826395599</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.03234292294534803</v>
+        <v>0.03234292294534802</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.06379327013865763</v>
+        <v>0.06379327013865761</v>
       </c>
       <c r="CU6" t="n">
         <v>0.0440196897631256</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.088735560711039</v>
+        <v>0.08873556071103901</v>
       </c>
       <c r="CW6" t="n">
         <v>0.1486729527400232</v>
@@ -3588,13 +3588,13 @@
         <v>1.222992513548709</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.03026795626806312</v>
+        <v>0.03026795626806313</v>
       </c>
       <c r="CZ6" t="n">
         <v>0.0867781545249897</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.08899277775636995</v>
+        <v>0.08899277775636993</v>
       </c>
       <c r="DB6" t="n">
         <v>0.1950489091557717</v>
@@ -3603,7 +3603,7 @@
         <v>0.0587228945569753</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.4655193486598915</v>
+        <v>0.4655193486598914</v>
       </c>
       <c r="DE6" t="n">
         <v>0.003018707723193235</v>
@@ -3612,7 +3612,7 @@
         <v>0.1365429156878438</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.046169947757327</v>
+        <v>2.046169947757326</v>
       </c>
       <c r="DH6" t="n">
         <v>0.1590557354306156</v>
@@ -3627,7 +3627,7 @@
         <v>0.2649255518145582</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.08321588227671044</v>
+        <v>0.08321588227671042</v>
       </c>
       <c r="DM6" t="n">
         <v>0.03831377203608224</v>
@@ -3639,7 +3639,7 @@
         <v>0.3285180159785941</v>
       </c>
       <c r="DP6" t="n">
-        <v>32.17709875680912</v>
+        <v>32.17709875680911</v>
       </c>
       <c r="DQ6" t="n">
         <v>0.003450053047126204</v>
@@ -3669,13 +3669,13 @@
         <v>0.06199284811417845</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0501850110011607</v>
+        <v>0.05018501100116069</v>
       </c>
       <c r="EA6" t="n">
         <v>0.1307136115909444</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.07213817805808047</v>
+        <v>0.07213817805808045</v>
       </c>
       <c r="EC6" t="n">
         <v>1.297780669102657</v>
@@ -3790,70 +3790,70 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>194.1516392720852</v>
+        <v>194.1516392720853</v>
       </c>
       <c r="C7" t="n">
         <v>0.2667038225776687</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2900750027999563</v>
+        <v>0.2900750027999564</v>
       </c>
       <c r="E7" t="n">
         <v>3.965933975606093</v>
       </c>
       <c r="F7" t="n">
-        <v>114.8174438999057</v>
+        <v>114.8174438999059</v>
       </c>
       <c r="G7" t="n">
-        <v>256.1877228197559</v>
+        <v>256.1877228197558</v>
       </c>
       <c r="H7" t="n">
         <v>124.7777434740009</v>
       </c>
       <c r="I7" t="n">
-        <v>33.77244137235142</v>
+        <v>33.77244137235143</v>
       </c>
       <c r="J7" t="n">
         <v>8.242559425032638</v>
       </c>
       <c r="K7" t="n">
-        <v>57.46909296549883</v>
+        <v>57.4690929654988</v>
       </c>
       <c r="L7" t="n">
-        <v>10.9816103740719</v>
+        <v>10.98161037407191</v>
       </c>
       <c r="M7" t="n">
         <v>1.306216968593031</v>
       </c>
       <c r="N7" t="n">
-        <v>9.51378560731837</v>
+        <v>9.513785607318368</v>
       </c>
       <c r="O7" t="n">
         <v>2.546278938749803</v>
       </c>
       <c r="P7" t="n">
-        <v>1.393755151468504</v>
+        <v>1.393755151468505</v>
       </c>
       <c r="Q7" t="n">
         <v>2.49295776067943</v>
       </c>
       <c r="R7" t="n">
-        <v>2.119350125178393</v>
+        <v>2.119350125178392</v>
       </c>
       <c r="S7" t="n">
         <v>1.42281766388067</v>
       </c>
       <c r="T7" t="n">
-        <v>5.342620371404054</v>
+        <v>5.342620371404053</v>
       </c>
       <c r="U7" t="n">
         <v>0.008029102087370064</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4570617448494493</v>
+        <v>0.4570617448494494</v>
       </c>
       <c r="W7" t="n">
-        <v>34.89380449301557</v>
+        <v>34.89380449301556</v>
       </c>
       <c r="X7" t="n">
         <v>0.1350705664009528</v>
@@ -3865,7 +3865,7 @@
         <v>1.019367190466018</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.64739412202549</v>
+        <v>11.64739412202548</v>
       </c>
       <c r="AB7" t="n">
         <v>0.2847564985576653</v>
@@ -3874,7 +3874,7 @@
         <v>11.25688282684747</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0220126835441286</v>
+        <v>0.02201268354412861</v>
       </c>
       <c r="AE7" t="n">
         <v>0.003848826448934268</v>
@@ -3886,37 +3886,37 @@
         <v>20.63281995978072</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.6519480739457217</v>
+        <v>0.6519480739457219</v>
       </c>
       <c r="AI7" t="n">
         <v>0.6411577324587681</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.871287569414619</v>
+        <v>0.8712875694146189</v>
       </c>
       <c r="AK7" t="n">
-        <v>7.829584069477383</v>
+        <v>7.829584069477385</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.2461904830187608</v>
+        <v>0.2461904830187607</v>
       </c>
       <c r="AM7" t="n">
         <v>0.1221383251849412</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.08964487121806781</v>
+        <v>0.08964487121806783</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.3042331661468077</v>
+        <v>0.3042331661468078</v>
       </c>
       <c r="AP7" t="n">
         <v>0.2617842114919788</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.6343909191249647</v>
+        <v>0.6343909191249648</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.677117644914224</v>
+        <v>2.677117644914223</v>
       </c>
       <c r="AS7" t="n">
         <v>0.0538089178580423</v>
@@ -3928,31 +3928,31 @@
         <v>0.1320588053423496</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.438328062980739</v>
+        <v>1.43832806298074</v>
       </c>
       <c r="AW7" t="n">
         <v>1.92071142654928</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.09423983597398898</v>
+        <v>0.09423983597398895</v>
       </c>
       <c r="AY7" t="n">
         <v>13.97551201437595</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.2450922242550073</v>
+        <v>0.2450922242550072</v>
       </c>
       <c r="BA7" t="n">
         <v>0.03724214220896253</v>
       </c>
       <c r="BB7" t="n">
-        <v>17.95847260667807</v>
+        <v>17.95847260667808</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.187641228870546</v>
+        <v>3.187641228870548</v>
       </c>
       <c r="BD7" t="n">
-        <v>10.03581358518788</v>
+        <v>10.03581358518787</v>
       </c>
       <c r="BE7" t="n">
         <v>0.1658806295648923</v>
@@ -3964,10 +3964,10 @@
         <v>0.4708188409610112</v>
       </c>
       <c r="BH7" t="n">
-        <v>5.72307323837764</v>
+        <v>5.723073238377641</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.213493992460945</v>
+        <v>0.2134939924609449</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.05376276517055965</v>
@@ -3988,7 +3988,7 @@
         <v>0.01846585708739965</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.08908526987208798</v>
+        <v>0.08908526987208797</v>
       </c>
       <c r="BQ7" t="n">
         <v>0.19738497455833</v>
@@ -3997,7 +3997,7 @@
         <v>0.08423041061347662</v>
       </c>
       <c r="BS7" t="n">
-        <v>9.325951313710423</v>
+        <v>9.325951313710425</v>
       </c>
       <c r="BT7" t="n">
         <v>1.692623474689338</v>
@@ -4006,7 +4006,7 @@
         <v>1.532561732471718</v>
       </c>
       <c r="BV7" t="n">
-        <v>1.846020041719575</v>
+        <v>1.846020041719576</v>
       </c>
       <c r="BW7" t="n">
         <v>0.00425929002556268</v>
@@ -4036,10 +4036,10 @@
         <v>2.295126493131328</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.5183574239175386</v>
+        <v>0.5183574239175387</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.8977009922761627</v>
+        <v>0.8977009922761626</v>
       </c>
       <c r="CH7" t="n">
         <v>0.1575231655655225</v>
@@ -4069,7 +4069,7 @@
         <v>0.2354046684687308</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.5264363576669171</v>
+        <v>0.526436357666917</v>
       </c>
       <c r="CR7" t="n">
         <v>0.2222941311482099</v>
@@ -4078,10 +4078,10 @@
         <v>0.02952461267833622</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.07879256798772689</v>
+        <v>0.07879256798772688</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.05254094076605902</v>
+        <v>0.05254094076605903</v>
       </c>
       <c r="CV7" t="n">
         <v>0.1104927059114956</v>
@@ -4093,13 +4093,13 @@
         <v>1.626012443149114</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.04171847545225149</v>
+        <v>0.0417184754522515</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.07192861573448958</v>
+        <v>0.07192861573448961</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0909614702633174</v>
+        <v>0.09096147026331741</v>
       </c>
       <c r="DB7" t="n">
         <v>0.2118829204142719</v>
@@ -4126,7 +4126,7 @@
         <v>0.05051499283806828</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.02317985066823313</v>
+        <v>0.02317985066823312</v>
       </c>
       <c r="DK7" t="n">
         <v>0.287938071682147</v>
@@ -4138,13 +4138,13 @@
         <v>0.05801065755781137</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.006937971521298142</v>
+        <v>0.006937971521298141</v>
       </c>
       <c r="DO7" t="n">
         <v>0.3152239826089193</v>
       </c>
       <c r="DP7" t="n">
-        <v>46.04880265413408</v>
+        <v>46.04880265413407</v>
       </c>
       <c r="DQ7" t="n">
         <v>0.002952993191651033</v>
@@ -4153,7 +4153,7 @@
         <v>0.02087589037561699</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.9047812536436597</v>
+        <v>0.9047812536436596</v>
       </c>
       <c r="DT7" t="n">
         <v>0.524715641976671</v>
@@ -4301,16 +4301,16 @@
         <v>0.3708542998708332</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4146122774205819</v>
+        <v>0.4146122774205821</v>
       </c>
       <c r="E8" t="n">
         <v>5.111053464292809</v>
       </c>
       <c r="F8" t="n">
-        <v>119.8186726907256</v>
+        <v>119.8186726907255</v>
       </c>
       <c r="G8" t="n">
-        <v>272.7578975486281</v>
+        <v>272.7578975486279</v>
       </c>
       <c r="H8" t="n">
         <v>122.9903899924766</v>
@@ -4325,10 +4325,10 @@
         <v>49.48987799306352</v>
       </c>
       <c r="L8" t="n">
-        <v>16.70952615798391</v>
+        <v>16.70952615798392</v>
       </c>
       <c r="M8" t="n">
-        <v>2.609410905571942</v>
+        <v>2.609410905571941</v>
       </c>
       <c r="N8" t="n">
         <v>11.28547886339388</v>
@@ -4337,25 +4337,25 @@
         <v>2.624838174111785</v>
       </c>
       <c r="P8" t="n">
-        <v>2.595010764878985</v>
+        <v>2.595010764878983</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.345404085764374</v>
+        <v>4.345404085764371</v>
       </c>
       <c r="R8" t="n">
-        <v>3.484594297209453</v>
+        <v>3.484594297209451</v>
       </c>
       <c r="S8" t="n">
         <v>2.007546775665482</v>
       </c>
       <c r="T8" t="n">
-        <v>6.275997977658265</v>
+        <v>6.275997977658263</v>
       </c>
       <c r="U8" t="n">
         <v>0.01421632689862126</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6809541129387652</v>
+        <v>0.6809541129387653</v>
       </c>
       <c r="W8" t="n">
         <v>27.94648952835622</v>
@@ -4373,37 +4373,37 @@
         <v>13.82307798420801</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3880931541475547</v>
+        <v>0.3880931541475546</v>
       </c>
       <c r="AC8" t="n">
-        <v>16.07264247295188</v>
+        <v>16.07264247295189</v>
       </c>
       <c r="AD8" t="n">
         <v>0.02475228135865733</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.004973013323210912</v>
+        <v>0.004973013323210913</v>
       </c>
       <c r="AF8" t="n">
         <v>24.93245450968368</v>
       </c>
       <c r="AG8" t="n">
-        <v>22.82971557122241</v>
+        <v>22.82971557122242</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.9080652564049163</v>
+        <v>0.9080652564049165</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.7572241846316826</v>
+        <v>0.7572241846316827</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.509803313929873</v>
       </c>
       <c r="AK8" t="n">
-        <v>8.87764607870011</v>
+        <v>8.877646078700112</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.3625580352376093</v>
+        <v>0.3625580352376091</v>
       </c>
       <c r="AM8" t="n">
         <v>0.175274511831099</v>
@@ -4412,16 +4412,16 @@
         <v>0.1227979759771488</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.2624707868585384</v>
+        <v>0.2624707868585383</v>
       </c>
       <c r="AP8" t="n">
         <v>0.2795976787246109</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.7482193099960742</v>
+        <v>0.7482193099960741</v>
       </c>
       <c r="AR8" t="n">
-        <v>3.987484973550339</v>
+        <v>3.987484973550338</v>
       </c>
       <c r="AS8" t="n">
         <v>0.08873367081491138</v>
@@ -4433,7 +4433,7 @@
         <v>0.1752237885382232</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.93062805836466</v>
+        <v>1.930628058364659</v>
       </c>
       <c r="AW8" t="n">
         <v>2.869615408585643</v>
@@ -4442,7 +4442,7 @@
         <v>0.1141804246804437</v>
       </c>
       <c r="AY8" t="n">
-        <v>17.96573575479981</v>
+        <v>17.9657357547998</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.3301955192627085</v>
@@ -4451,7 +4451,7 @@
         <v>0.04582945961866256</v>
       </c>
       <c r="BB8" t="n">
-        <v>20.962596689499</v>
+        <v>20.96259668949901</v>
       </c>
       <c r="BC8" t="n">
         <v>3.529625996694259</v>
@@ -4460,13 +4460,13 @@
         <v>16.06705389282984</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.2177711638196846</v>
+        <v>0.2177711638196845</v>
       </c>
       <c r="BF8" t="n">
         <v>0.3730450479624072</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.494194412178551</v>
+        <v>0.4941944121785509</v>
       </c>
       <c r="BH8" t="n">
         <v>7.696409682496403</v>
@@ -4484,16 +4484,16 @@
         <v>0.03868091963561889</v>
       </c>
       <c r="BM8" t="n">
-        <v>11.95210472771455</v>
+        <v>11.95210472771456</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.8187225122042264</v>
+        <v>0.8187225122042263</v>
       </c>
       <c r="BO8" t="n">
         <v>0.02308263269414841</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.1271922780285745</v>
+        <v>0.1271922780285746</v>
       </c>
       <c r="BQ8" t="n">
         <v>0.2467115810174386</v>
@@ -4526,7 +4526,7 @@
         <v>2.989032498265958</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.04190916760972434</v>
+        <v>0.04190916760972435</v>
       </c>
       <c r="CB8" t="n">
         <v>0.172450482390894</v>
@@ -4586,7 +4586,7 @@
         <v>0.1045954781126142</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0747091262953315</v>
+        <v>0.07470912629533148</v>
       </c>
       <c r="CV8" t="n">
         <v>0.1391802220905064</v>
@@ -4613,7 +4613,7 @@
         <v>0.07662703355413206</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.6746552088366982</v>
+        <v>0.6746552088366981</v>
       </c>
       <c r="DE8" t="n">
         <v>0.004122180173029886</v>
@@ -4622,10 +4622,10 @@
         <v>0.1992849557385708</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.986652300048139</v>
+        <v>2.98665230004814</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.2082352219279814</v>
+        <v>0.2082352219279813</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04874797363411498</v>
@@ -4643,13 +4643,13 @@
         <v>0.1010451866933929</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.01214372176951727</v>
+        <v>0.01214372176951726</v>
       </c>
       <c r="DO8" t="n">
         <v>0.5569827412216705</v>
       </c>
       <c r="DP8" t="n">
-        <v>55.72667963150799</v>
+        <v>55.72667963150798</v>
       </c>
       <c r="DQ8" t="n">
         <v>0.003706840233057957</v>
@@ -4806,7 +4806,7 @@
         <v>0.3063499146037666</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3471933041993003</v>
+        <v>0.3471933041993001</v>
       </c>
       <c r="E9" t="n">
         <v>4.347833332192387</v>
@@ -4815,7 +4815,7 @@
         <v>105.0651197106895</v>
       </c>
       <c r="G9" t="n">
-        <v>232.3532486181905</v>
+        <v>232.3532486181906</v>
       </c>
       <c r="H9" t="n">
         <v>107.1485899417069</v>
@@ -4827,16 +4827,16 @@
         <v>10.46176393707282</v>
       </c>
       <c r="K9" t="n">
-        <v>42.47196063001724</v>
+        <v>42.47196063001723</v>
       </c>
       <c r="L9" t="n">
-        <v>14.11412453167334</v>
+        <v>14.11412453167333</v>
       </c>
       <c r="M9" t="n">
         <v>2.100707647950022</v>
       </c>
       <c r="N9" t="n">
-        <v>9.556682794319094</v>
+        <v>9.556682794319096</v>
       </c>
       <c r="O9" t="n">
         <v>2.266429528365788</v>
@@ -4845,7 +4845,7 @@
         <v>2.070685091602589</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.573699003903969</v>
+        <v>3.573699003903968</v>
       </c>
       <c r="R9" t="n">
         <v>2.827651824938837</v>
@@ -4854,16 +4854,16 @@
         <v>1.754853205190291</v>
       </c>
       <c r="T9" t="n">
-        <v>5.405688715368903</v>
+        <v>5.405688715368905</v>
       </c>
       <c r="U9" t="n">
         <v>0.01221880300543068</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6050064616045413</v>
+        <v>0.6050064616045414</v>
       </c>
       <c r="W9" t="n">
-        <v>23.30033193856781</v>
+        <v>23.3003319385678</v>
       </c>
       <c r="X9" t="n">
         <v>0.1536658684083485</v>
@@ -4878,34 +4878,34 @@
         <v>11.7009042275779</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.3325835564324551</v>
+        <v>0.332583556432455</v>
       </c>
       <c r="AC9" t="n">
-        <v>13.59756969944153</v>
+        <v>13.59756969944152</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.02296699809063352</v>
+        <v>0.02296699809063353</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.004464987007377502</v>
+        <v>0.004464987007377501</v>
       </c>
       <c r="AF9" t="n">
-        <v>21.48656101137114</v>
+        <v>21.48656101137113</v>
       </c>
       <c r="AG9" t="n">
-        <v>21.43984896650022</v>
+        <v>21.43984896650021</v>
       </c>
       <c r="AH9" t="n">
         <v>0.7702546375485593</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.6160614310605071</v>
+        <v>0.616061431060507</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.309335653968299</v>
       </c>
       <c r="AK9" t="n">
-        <v>7.821808437450235</v>
+        <v>7.821808437450236</v>
       </c>
       <c r="AL9" t="n">
         <v>0.3012688587454552</v>
@@ -4917,13 +4917,13 @@
         <v>0.1068655491495173</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.2227248899821783</v>
+        <v>0.2227248899821784</v>
       </c>
       <c r="AP9" t="n">
         <v>0.2313455560769902</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.5958331305680664</v>
+        <v>0.5958331305680666</v>
       </c>
       <c r="AR9" t="n">
         <v>3.47230724128306</v>
@@ -4950,28 +4950,28 @@
         <v>15.27050302327962</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.2838122522826748</v>
+        <v>0.2838122522826749</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.03741265908861736</v>
+        <v>0.03741265908861737</v>
       </c>
       <c r="BB9" t="n">
         <v>17.07160064407507</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.022402348416372</v>
+        <v>3.022402348416371</v>
       </c>
       <c r="BD9" t="n">
-        <v>13.5974141184299</v>
+        <v>13.59741411842991</v>
       </c>
       <c r="BE9" t="n">
         <v>0.2091212547368639</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.3114356260656577</v>
+        <v>0.3114356260656578</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.4742208117594476</v>
+        <v>0.4742208117594475</v>
       </c>
       <c r="BH9" t="n">
         <v>6.780125415666087</v>
@@ -4983,16 +4983,16 @@
         <v>0.07419645851843938</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.666940113751791</v>
+        <v>6.666940113751792</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.03374692911133307</v>
+        <v>0.03374692911133308</v>
       </c>
       <c r="BM9" t="n">
         <v>10.37326415855205</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.6956189370261474</v>
+        <v>0.6956189370261473</v>
       </c>
       <c r="BO9" t="n">
         <v>0.01936245314165293</v>
@@ -5016,7 +5016,7 @@
         <v>1.498706079619441</v>
       </c>
       <c r="BV9" t="n">
-        <v>1.52624738973323</v>
+        <v>1.526247389733231</v>
       </c>
       <c r="BW9" t="n">
         <v>0.003641222797075156</v>
@@ -5037,7 +5037,7 @@
         <v>0.1495194092891474</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.05164878148660472</v>
+        <v>0.05164878148660471</v>
       </c>
       <c r="CD9" t="n">
         <v>0.09843462988138479</v>
@@ -5052,22 +5052,22 @@
         <v>1.523997908334917</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.1927303369778627</v>
+        <v>0.1927303369778628</v>
       </c>
       <c r="CI9" t="n">
         <v>0.04268201319381001</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.841505409250778</v>
+        <v>2.841505409250779</v>
       </c>
       <c r="CK9" t="n">
         <v>0.002922508202888128</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.1982915449839802</v>
+        <v>0.1982915449839801</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.009981556220991632</v>
+        <v>0.00998155622099163</v>
       </c>
       <c r="CN9" t="n">
         <v>0.09697468775771055</v>
@@ -5085,13 +5085,13 @@
         <v>0.2342655673948319</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.04176296972431984</v>
+        <v>0.04176296972431983</v>
       </c>
       <c r="CT9" t="n">
         <v>0.08387857574106962</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.06733240946347598</v>
+        <v>0.067332409463476</v>
       </c>
       <c r="CV9" t="n">
         <v>0.1179505697788581</v>
@@ -5100,10 +5100,10 @@
         <v>0.1781750935030692</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.766057739127329</v>
+        <v>1.766057739127328</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.04176760800081346</v>
+        <v>0.04176760800081347</v>
       </c>
       <c r="CZ9" t="n">
         <v>0.09895297046330495</v>
@@ -5112,7 +5112,7 @@
         <v>0.1206008450221609</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.2348720174067935</v>
+        <v>0.2348720174067936</v>
       </c>
       <c r="DC9" t="n">
         <v>0.07030848800768888</v>
@@ -5154,7 +5154,7 @@
         <v>0.4755450367882136</v>
       </c>
       <c r="DP9" t="n">
-        <v>46.88073909451127</v>
+        <v>46.88073909451126</v>
       </c>
       <c r="DQ9" t="n">
         <v>0.003177745480090766</v>
@@ -5305,10 +5305,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>176.5021655182092</v>
+        <v>176.502165518209</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3400807864308382</v>
+        <v>0.3400807864308381</v>
       </c>
       <c r="D10" t="n">
         <v>0.3290448836663721</v>
@@ -5317,13 +5317,13 @@
         <v>4.435482614634006</v>
       </c>
       <c r="F10" t="n">
-        <v>103.9541102612538</v>
+        <v>103.954110261254</v>
       </c>
       <c r="G10" t="n">
-        <v>235.0706214611074</v>
+        <v>235.0706214611073</v>
       </c>
       <c r="H10" t="n">
-        <v>106.7000971377189</v>
+        <v>106.700097137719</v>
       </c>
       <c r="I10" t="n">
         <v>28.97186337142023</v>
@@ -5350,10 +5350,10 @@
         <v>2.301921450679949</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.825545655808233</v>
+        <v>2.825545655808234</v>
       </c>
       <c r="R10" t="n">
-        <v>3.247249273668731</v>
+        <v>3.247249273668732</v>
       </c>
       <c r="S10" t="n">
         <v>1.750947455166642</v>
@@ -5395,22 +5395,22 @@
         <v>0.00459043738696386</v>
       </c>
       <c r="AF10" t="n">
-        <v>21.86653457998643</v>
+        <v>21.86653457998644</v>
       </c>
       <c r="AG10" t="n">
         <v>19.98986465302142</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.7728840285905739</v>
+        <v>0.7728840285905738</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.6343336691637602</v>
+        <v>0.6343336691637605</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.323740422266948</v>
       </c>
       <c r="AK10" t="n">
-        <v>8.010174998157218</v>
+        <v>8.01017499815722</v>
       </c>
       <c r="AL10" t="n">
         <v>0.3067471673055576</v>
@@ -5449,7 +5449,7 @@
         <v>2.290763235957779</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.09771725670103719</v>
+        <v>0.09771725670103722</v>
       </c>
       <c r="AY10" t="n">
         <v>15.04962773666824</v>
@@ -5464,28 +5464,28 @@
         <v>17.05811283337796</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.114295236810141</v>
+        <v>3.114295236810142</v>
       </c>
       <c r="BD10" t="n">
-        <v>14.54418936305818</v>
+        <v>14.54418936305817</v>
       </c>
       <c r="BE10" t="n">
         <v>0.1961996114879743</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.3236855746377046</v>
+        <v>0.3236855746377045</v>
       </c>
       <c r="BG10" t="n">
         <v>0.4308885404772455</v>
       </c>
       <c r="BH10" t="n">
-        <v>6.767072585146674</v>
+        <v>6.767072585146675</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.203477773626796</v>
+        <v>0.2034777736267959</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.005398043655014138</v>
+        <v>0.005398043655014137</v>
       </c>
       <c r="BK10" t="n">
         <v>6.585760931303153</v>
@@ -5521,7 +5521,7 @@
         <v>1.634834905344694</v>
       </c>
       <c r="BV10" t="n">
-        <v>1.439845835266314</v>
+        <v>1.439845835266313</v>
       </c>
       <c r="BW10" t="n">
         <v>0.003714001496067616</v>
@@ -5572,7 +5572,7 @@
         <v>0.1844169951137988</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.01051261112679136</v>
+        <v>0.01051261112679135</v>
       </c>
       <c r="CN10" t="n">
         <v>0.100998206839551</v>
@@ -5581,7 +5581,7 @@
         <v>0.7292431431132188</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.3998182305580216</v>
+        <v>0.3998182305580217</v>
       </c>
       <c r="CQ10" t="n">
         <v>0.5207285228083589</v>
@@ -5593,7 +5593,7 @@
         <v>0.04237198931489834</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.08982486574616701</v>
+        <v>0.08982486574616702</v>
       </c>
       <c r="CU10" t="n">
         <v>0.06364515952936126</v>
@@ -5608,7 +5608,7 @@
         <v>1.728692986257528</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.04215617076575475</v>
+        <v>0.04215617076575474</v>
       </c>
       <c r="CZ10" t="n">
         <v>0.1038573560059444</v>
@@ -5623,7 +5623,7 @@
         <v>0.06896695079849764</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.6000502950882363</v>
+        <v>0.6000502950882362</v>
       </c>
       <c r="DE10" t="n">
         <v>0.003616053275144071</v>
@@ -5632,10 +5632,10 @@
         <v>0.173817803058287</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.608279296657932</v>
+        <v>2.608279296657934</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.1877492120083748</v>
+        <v>0.1877492120083749</v>
       </c>
       <c r="DI10" t="n">
         <v>0.04037746642106956</v>
@@ -5644,7 +5644,7 @@
         <v>0.02051908463940784</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.3580528216494314</v>
+        <v>0.3580528216494313</v>
       </c>
       <c r="DL10" t="n">
         <v>0.09876486462459264</v>
@@ -5653,19 +5653,19 @@
         <v>0.08741121325958065</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.009588173482431657</v>
+        <v>0.009588173482431659</v>
       </c>
       <c r="DO10" t="n">
         <v>0.4979740274220019</v>
       </c>
       <c r="DP10" t="n">
-        <v>46.06991967003137</v>
+        <v>46.0699196700314</v>
       </c>
       <c r="DQ10" t="n">
         <v>0.003262975951645978</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.03915343791191978</v>
+        <v>0.03915343791191977</v>
       </c>
       <c r="DS10" t="n">
         <v>1.065343571167971</v>
@@ -5695,7 +5695,7 @@
         <v>0.1674564070302692</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.09868430853697009</v>
+        <v>0.09868430853697011</v>
       </c>
       <c r="EC10" t="n">
         <v>1.704248274815274</v>
@@ -5810,10 +5810,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>188.392119752045</v>
+        <v>188.3921197520449</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3627065316307947</v>
+        <v>0.3627065316307945</v>
       </c>
       <c r="D11" t="n">
         <v>0.3745999273268713</v>
@@ -5822,13 +5822,13 @@
         <v>5.348680764520734</v>
       </c>
       <c r="F11" t="n">
-        <v>107.1511386458312</v>
+        <v>107.1511386458313</v>
       </c>
       <c r="G11" t="n">
-        <v>277.1407638493976</v>
+        <v>277.1407638493974</v>
       </c>
       <c r="H11" t="n">
-        <v>104.1523720523613</v>
+        <v>104.1523720523612</v>
       </c>
       <c r="I11" t="n">
         <v>25.98185544396454</v>
@@ -5837,10 +5837,10 @@
         <v>12.0207865326163</v>
       </c>
       <c r="K11" t="n">
-        <v>37.93758004013361</v>
+        <v>37.93758004013362</v>
       </c>
       <c r="L11" t="n">
-        <v>17.19123215896571</v>
+        <v>17.19123215896572</v>
       </c>
       <c r="M11" t="n">
         <v>2.733202960559168</v>
@@ -5855,25 +5855,25 @@
         <v>2.732038197793636</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.321007455276041</v>
+        <v>4.321007455276039</v>
       </c>
       <c r="R11" t="n">
-        <v>3.585612856636332</v>
+        <v>3.585612856636331</v>
       </c>
       <c r="S11" t="n">
-        <v>2.033171827422393</v>
+        <v>2.033171827422394</v>
       </c>
       <c r="T11" t="n">
-        <v>6.779577136475654</v>
+        <v>6.779577136475653</v>
       </c>
       <c r="U11" t="n">
         <v>0.0141786890133055</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7024153448399537</v>
+        <v>0.7024153448399538</v>
       </c>
       <c r="W11" t="n">
-        <v>19.80420939206326</v>
+        <v>19.80420939206327</v>
       </c>
       <c r="X11" t="n">
         <v>0.1716234046182999</v>
@@ -5891,7 +5891,7 @@
         <v>0.3818549328205632</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.56965801981577</v>
+        <v>16.56965801981578</v>
       </c>
       <c r="AD11" t="n">
         <v>0.02220517251655242</v>
@@ -5903,16 +5903,16 @@
         <v>26.1346226682076</v>
       </c>
       <c r="AG11" t="n">
-        <v>18.409012450934</v>
+        <v>18.40901245093401</v>
       </c>
       <c r="AH11" t="n">
         <v>0.8898760548571358</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.7061085205936739</v>
+        <v>0.706108520593674</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.498336159672434</v>
+        <v>1.498336159672435</v>
       </c>
       <c r="AK11" t="n">
         <v>9.004934032311967</v>
@@ -5933,10 +5933,10 @@
         <v>0.3337879722522906</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.775330741583978</v>
+        <v>0.7753307415839777</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.185554924020091</v>
+        <v>4.185554924020093</v>
       </c>
       <c r="AS11" t="n">
         <v>0.09633633359715214</v>
@@ -5966,7 +5966,7 @@
         <v>0.04477268194484697</v>
       </c>
       <c r="BB11" t="n">
-        <v>18.58251270403407</v>
+        <v>18.58251270403408</v>
       </c>
       <c r="BC11" t="n">
         <v>3.300267833329399</v>
@@ -5978,13 +5978,13 @@
         <v>0.2206493916154403</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.3804854728963059</v>
+        <v>0.3804854728963058</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.5075893048054004</v>
+        <v>0.5075893048054005</v>
       </c>
       <c r="BH11" t="n">
-        <v>7.603990588882166</v>
+        <v>7.603990588882167</v>
       </c>
       <c r="BI11" t="n">
         <v>0.246010848986166</v>
@@ -6002,7 +6002,7 @@
         <v>12.56411846965583</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.7551802154687061</v>
+        <v>0.7551802154687057</v>
       </c>
       <c r="BO11" t="n">
         <v>0.02271194402430413</v>
@@ -6047,7 +6047,7 @@
         <v>0.1608264319618944</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.05970994279377561</v>
+        <v>0.0597099427937756</v>
       </c>
       <c r="CD11" t="n">
         <v>0.1637941294357922</v>
@@ -6083,19 +6083,19 @@
         <v>0.1249070614196443</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.7961537520618309</v>
+        <v>0.796153752061831</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.4546009389174043</v>
+        <v>0.4546009389174042</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.5638320377990615</v>
+        <v>0.5638320377990617</v>
       </c>
       <c r="CR11" t="n">
         <v>0.2771967778569332</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.05996663682789351</v>
+        <v>0.05996663682789352</v>
       </c>
       <c r="CT11" t="n">
         <v>0.1141302357486455</v>
@@ -6128,7 +6128,7 @@
         <v>0.06449414900494278</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.6682684462619436</v>
+        <v>0.6682684462619435</v>
       </c>
       <c r="DE11" t="n">
         <v>0.004378530889456951</v>
@@ -6140,7 +6140,7 @@
         <v>2.885856698444893</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.2106602483431022</v>
+        <v>0.2106602483431021</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04963104701768073</v>
@@ -6161,10 +6161,10 @@
         <v>0.01187108661801902</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.5918819885997835</v>
+        <v>0.5918819885997836</v>
       </c>
       <c r="DP11" t="n">
-        <v>66.86606208878894</v>
+        <v>66.86606208878892</v>
       </c>
       <c r="DQ11" t="n">
         <v>0.003740307738466386</v>
@@ -6315,13 +6315,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>187.3070433279954</v>
+        <v>187.3070433279955</v>
       </c>
       <c r="C12" t="n">
         <v>0.3555703574112495</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4151547571207965</v>
+        <v>0.4151547571207964</v>
       </c>
       <c r="E12" t="n">
         <v>5.292774770321793</v>
@@ -6330,7 +6330,7 @@
         <v>108.7628022245244</v>
       </c>
       <c r="G12" t="n">
-        <v>268.7329213330884</v>
+        <v>268.7329213330883</v>
       </c>
       <c r="H12" t="n">
         <v>106.3532786148636</v>
@@ -6342,7 +6342,7 @@
         <v>11.30777484244006</v>
       </c>
       <c r="K12" t="n">
-        <v>39.8055979145052</v>
+        <v>39.80559791450519</v>
       </c>
       <c r="L12" t="n">
         <v>15.9791180294715</v>
@@ -6351,7 +6351,7 @@
         <v>2.394400220074553</v>
       </c>
       <c r="N12" t="n">
-        <v>9.736310523820672</v>
+        <v>9.736310523820675</v>
       </c>
       <c r="O12" t="n">
         <v>1.990417712685602</v>
@@ -6360,25 +6360,25 @@
         <v>2.626509281078438</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.886444447192756</v>
+        <v>3.886444447192755</v>
       </c>
       <c r="R12" t="n">
         <v>3.431604030995714</v>
       </c>
       <c r="S12" t="n">
-        <v>1.965292494422673</v>
+        <v>1.965292494422672</v>
       </c>
       <c r="T12" t="n">
-        <v>6.822938493470521</v>
+        <v>6.822938493470523</v>
       </c>
       <c r="U12" t="n">
         <v>0.01479850812310418</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6831327355708822</v>
+        <v>0.6831327355708823</v>
       </c>
       <c r="W12" t="n">
-        <v>21.91786035124965</v>
+        <v>21.91786035124966</v>
       </c>
       <c r="X12" t="n">
         <v>0.1812575561890338</v>
@@ -6387,31 +6387,31 @@
         <v>1.759118374594695</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.904726755139886</v>
+        <v>1.904726755139885</v>
       </c>
       <c r="AA12" t="n">
         <v>15.1735578247713</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.3916087622637228</v>
+        <v>0.3916087622637227</v>
       </c>
       <c r="AC12" t="n">
         <v>15.58310716611139</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.02516978813192495</v>
+        <v>0.02516978813192496</v>
       </c>
       <c r="AE12" t="n">
         <v>0.005088180246803167</v>
       </c>
       <c r="AF12" t="n">
-        <v>26.36321867281375</v>
+        <v>26.36321867281373</v>
       </c>
       <c r="AG12" t="n">
-        <v>19.19765185377348</v>
+        <v>19.19765185377346</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.8485600622825979</v>
+        <v>0.8485600622825978</v>
       </c>
       <c r="AI12" t="n">
         <v>0.67793136788177</v>
@@ -6426,7 +6426,7 @@
         <v>0.3521634432109499</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.1681905673975861</v>
+        <v>0.1681905673975862</v>
       </c>
       <c r="AN12" t="n">
         <v>0.1154911914492233</v>
@@ -6438,16 +6438,16 @@
         <v>0.2661535577246337</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.7358421863239855</v>
+        <v>0.7358421863239856</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.925163487466426</v>
+        <v>3.925163487466425</v>
       </c>
       <c r="AS12" t="n">
         <v>0.08268256667200101</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.03531369372634229</v>
+        <v>0.0353136937263423</v>
       </c>
       <c r="AU12" t="n">
         <v>0.161811391562324</v>
@@ -6471,10 +6471,10 @@
         <v>0.04494895685484368</v>
       </c>
       <c r="BB12" t="n">
-        <v>19.07413149796638</v>
+        <v>19.07413149796637</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.242387635362422</v>
+        <v>3.242387635362421</v>
       </c>
       <c r="BD12" t="n">
         <v>16.81914736292005</v>
@@ -6483,10 +6483,10 @@
         <v>0.2327865465708244</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.3587328305993009</v>
+        <v>0.3587328305993011</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.510434753019819</v>
+        <v>0.5104347530198191</v>
       </c>
       <c r="BH12" t="n">
         <v>7.347889275251529</v>
@@ -6498,7 +6498,7 @@
         <v>0.06141771527524521</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.168226399682598</v>
+        <v>6.1682263996826</v>
       </c>
       <c r="BL12" t="n">
         <v>0.04188725807252913</v>
@@ -6561,7 +6561,7 @@
         <v>3.152884702842632</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.582268809677139</v>
+        <v>0.5822688096771389</v>
       </c>
       <c r="CG12" t="n">
         <v>1.652165048163151</v>
@@ -6573,7 +6573,7 @@
         <v>0.05412814312805202</v>
       </c>
       <c r="CJ12" t="n">
-        <v>3.316017731220082</v>
+        <v>3.316017731220081</v>
       </c>
       <c r="CK12" t="n">
         <v>0.003580468490847631</v>
@@ -6594,7 +6594,7 @@
         <v>0.3934110076782731</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.5334785492231422</v>
+        <v>0.5334785492231423</v>
       </c>
       <c r="CR12" t="n">
         <v>0.2688384950185213</v>
@@ -6627,13 +6627,13 @@
         <v>0.130427145916406</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.2617282182589088</v>
+        <v>0.2617282182589089</v>
       </c>
       <c r="DC12" t="n">
         <v>0.07345723056398124</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.65904121619942</v>
+        <v>0.6590412161994199</v>
       </c>
       <c r="DE12" t="n">
         <v>0.004705290545009921</v>
@@ -6642,7 +6642,7 @@
         <v>0.1881385140493518</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.743713024582892</v>
+        <v>2.74371302458289</v>
       </c>
       <c r="DH12" t="n">
         <v>0.2223755308085498</v>
@@ -6660,16 +6660,16 @@
         <v>0.1050776726829563</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.08974562578912532</v>
+        <v>0.0897456257891253</v>
       </c>
       <c r="DN12" t="n">
         <v>0.01249759963997908</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.5435166559557555</v>
+        <v>0.5435166559557556</v>
       </c>
       <c r="DP12" t="n">
-        <v>64.62088792362664</v>
+        <v>64.62088792362663</v>
       </c>
       <c r="DQ12" t="n">
         <v>0.003583911960086808</v>
@@ -6711,7 +6711,7 @@
         <v>2.345461383379779</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.004425020456848928</v>
+        <v>0.004425020456848929</v>
       </c>
       <c r="EE12" t="n">
         <v>0.03928954644843916</v>
@@ -6820,25 +6820,25 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>191.0380320703822</v>
+        <v>191.0380320703824</v>
       </c>
       <c r="C13" t="n">
         <v>0.3924982775995451</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4111555903524835</v>
+        <v>0.4111555903524837</v>
       </c>
       <c r="E13" t="n">
         <v>5.213778626452774</v>
       </c>
       <c r="F13" t="n">
-        <v>110.3052217624947</v>
+        <v>110.3052217624946</v>
       </c>
       <c r="G13" t="n">
         <v>264.3676705543982</v>
       </c>
       <c r="H13" t="n">
-        <v>104.6966534357504</v>
+        <v>104.6966534357503</v>
       </c>
       <c r="I13" t="n">
         <v>22.34533065527027</v>
@@ -6850,7 +6850,7 @@
         <v>34.32068342049714</v>
       </c>
       <c r="L13" t="n">
-        <v>17.09755670687182</v>
+        <v>17.09755670687184</v>
       </c>
       <c r="M13" t="n">
         <v>2.737326259186796</v>
@@ -6862,25 +6862,25 @@
         <v>2.219151633555639</v>
       </c>
       <c r="P13" t="n">
-        <v>2.793978906999192</v>
+        <v>2.793978906999193</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.277978724909394</v>
+        <v>4.277978724909393</v>
       </c>
       <c r="R13" t="n">
-        <v>3.538331749640751</v>
+        <v>3.538331749640752</v>
       </c>
       <c r="S13" t="n">
         <v>2.0331648319044</v>
       </c>
       <c r="T13" t="n">
-        <v>6.110590743398348</v>
+        <v>6.110590743398344</v>
       </c>
       <c r="U13" t="n">
         <v>0.01386448343769085</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7426155281044446</v>
+        <v>0.7426155281044444</v>
       </c>
       <c r="W13" t="n">
         <v>19.95199690421991</v>
@@ -6889,7 +6889,7 @@
         <v>0.1718320453756577</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.780468192537125</v>
+        <v>1.780468192537126</v>
       </c>
       <c r="Z13" t="n">
         <v>2.004021483978576</v>
@@ -6898,10 +6898,10 @@
         <v>15.35778525360575</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.3851934035328792</v>
+        <v>0.3851934035328791</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.85428648851559</v>
+        <v>16.8542864885156</v>
       </c>
       <c r="AD13" t="n">
         <v>0.02413512281717073</v>
@@ -6913,7 +6913,7 @@
         <v>24.73088385068638</v>
       </c>
       <c r="AG13" t="n">
-        <v>22.81341672059989</v>
+        <v>22.81341672059988</v>
       </c>
       <c r="AH13" t="n">
         <v>0.8368804554497222</v>
@@ -6925,10 +6925,10 @@
         <v>1.477686988087022</v>
       </c>
       <c r="AK13" t="n">
-        <v>8.676850139866698</v>
+        <v>8.676850139866701</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.3672161387547306</v>
+        <v>0.3672161387547305</v>
       </c>
       <c r="AM13" t="n">
         <v>0.1786003732741557</v>
@@ -6943,16 +6943,16 @@
         <v>0.291072014145302</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.7576220320898086</v>
+        <v>0.7576220320898085</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.042892391814345</v>
+        <v>4.042892391814343</v>
       </c>
       <c r="AS13" t="n">
         <v>0.08467083455298798</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.03908874619543986</v>
+        <v>0.03908874619543987</v>
       </c>
       <c r="AU13" t="n">
         <v>0.1739873745788708</v>
@@ -6967,19 +6967,19 @@
         <v>0.120143993537056</v>
       </c>
       <c r="AY13" t="n">
-        <v>19.13479435591571</v>
+        <v>19.13479435591572</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.3465252200970448</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0470079201435409</v>
+        <v>0.04700792014354089</v>
       </c>
       <c r="BB13" t="n">
-        <v>19.87843876472925</v>
+        <v>19.87843876472924</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.222441603206716</v>
+        <v>3.222441603206717</v>
       </c>
       <c r="BD13" t="n">
         <v>17.98478547434986</v>
@@ -6988,7 +6988,7 @@
         <v>0.2263504382617427</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.3984779450632038</v>
+        <v>0.3984779450632039</v>
       </c>
       <c r="BG13" t="n">
         <v>0.4907193142019843</v>
@@ -7003,7 +7003,7 @@
         <v>0.08612387844326093</v>
       </c>
       <c r="BK13" t="n">
-        <v>7.023879547269579</v>
+        <v>7.02387954726958</v>
       </c>
       <c r="BL13" t="n">
         <v>0.04246970638124706</v>
@@ -7012,7 +7012,7 @@
         <v>12.28035276699541</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.7570082705146344</v>
+        <v>0.7570082705146346</v>
       </c>
       <c r="BO13" t="n">
         <v>0.02344663692084176</v>
@@ -7042,7 +7042,7 @@
         <v>0.004476151060149609</v>
       </c>
       <c r="BX13" t="n">
-        <v>1.256437534535655</v>
+        <v>1.256437534535654</v>
       </c>
       <c r="BY13" t="n">
         <v>0.05116264471375147</v>
@@ -7099,10 +7099,10 @@
         <v>0.4517372060521735</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.5569789107032853</v>
+        <v>0.5569789107032855</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.2828601122862184</v>
+        <v>0.2828601122862183</v>
       </c>
       <c r="CS13" t="n">
         <v>0.0567038137452178</v>
@@ -7120,7 +7120,7 @@
         <v>0.2119844465463632</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.820918577017731</v>
+        <v>1.82091857701773</v>
       </c>
       <c r="CY13" t="n">
         <v>0.0503209612435476</v>
@@ -7138,7 +7138,7 @@
         <v>0.06788730375416958</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.7035790012512176</v>
+        <v>0.7035790012512178</v>
       </c>
       <c r="DE13" t="n">
         <v>0.004865689545017192</v>
@@ -7147,13 +7147,13 @@
         <v>0.1932500887452609</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.783543866216574</v>
+        <v>2.783543866216575</v>
       </c>
       <c r="DH13" t="n">
         <v>0.2170466243168654</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05298630328692746</v>
+        <v>0.05298630328692745</v>
       </c>
       <c r="DJ13" t="n">
         <v>0.02037772726023158</v>
@@ -7174,7 +7174,7 @@
         <v>0.6030104600436827</v>
       </c>
       <c r="DP13" t="n">
-        <v>59.94315758148487</v>
+        <v>59.94315758148488</v>
       </c>
       <c r="DQ13" t="n">
         <v>0.003739565747016878</v>
@@ -7204,7 +7204,7 @@
         <v>0.1046447748266026</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.07751611637523577</v>
+        <v>0.07751611637523576</v>
       </c>
       <c r="EA13" t="n">
         <v>0.2132299028777321</v>
@@ -7231,7 +7231,7 @@
         <v>0.01751248503811286</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.0166060124047081</v>
+        <v>0.01660601240470809</v>
       </c>
       <c r="EJ13" t="n">
         <v>0.01436476716826299</v>
@@ -7328,7 +7328,7 @@
         <v>338.4823015571529</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5003321480743244</v>
+        <v>0.5003321480743245</v>
       </c>
       <c r="D14" t="n">
         <v>0.6506676470786706</v>
@@ -7337,10 +7337,10 @@
         <v>9.058890207885746</v>
       </c>
       <c r="F14" t="n">
-        <v>197.5002617175616</v>
+        <v>197.500261717562</v>
       </c>
       <c r="G14" t="n">
-        <v>550.9705103015147</v>
+        <v>550.970510301516</v>
       </c>
       <c r="H14" t="n">
         <v>202.7461011100775</v>
@@ -7352,13 +7352,13 @@
         <v>16.81970054946068</v>
       </c>
       <c r="K14" t="n">
-        <v>78.82347839509923</v>
+        <v>78.8234783950992</v>
       </c>
       <c r="L14" t="n">
-        <v>26.60739153097735</v>
+        <v>26.60739153097736</v>
       </c>
       <c r="M14" t="n">
-        <v>3.725108609580325</v>
+        <v>3.725108609580324</v>
       </c>
       <c r="N14" t="n">
         <v>14.5691849331249</v>
@@ -7367,19 +7367,19 @@
         <v>3.294903038112016</v>
       </c>
       <c r="P14" t="n">
-        <v>3.906260789134768</v>
+        <v>3.906260789134767</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.842754123659387</v>
+        <v>3.842754123659386</v>
       </c>
       <c r="R14" t="n">
-        <v>5.882607456598449</v>
+        <v>5.882607456598452</v>
       </c>
       <c r="S14" t="n">
         <v>3.169463582482697</v>
       </c>
       <c r="T14" t="n">
-        <v>13.27941177386085</v>
+        <v>13.27941177386086</v>
       </c>
       <c r="U14" t="n">
         <v>0.02296348693052435</v>
@@ -7394,13 +7394,13 @@
         <v>0.3246791236204478</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.103087807084308</v>
+        <v>3.103087807084307</v>
       </c>
       <c r="Z14" t="n">
         <v>2.872239639466172</v>
       </c>
       <c r="AA14" t="n">
-        <v>36.04669631674181</v>
+        <v>36.04669631674184</v>
       </c>
       <c r="AB14" t="n">
         <v>0.6566030779648063</v>
@@ -7415,16 +7415,16 @@
         <v>0.007651893511418113</v>
       </c>
       <c r="AF14" t="n">
-        <v>53.2915976146195</v>
+        <v>53.29159761461949</v>
       </c>
       <c r="AG14" t="n">
-        <v>34.28419660999059</v>
+        <v>34.2841966099906</v>
       </c>
       <c r="AH14" t="n">
         <v>1.573818366340089</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.334863705382981</v>
+        <v>1.33486370538298</v>
       </c>
       <c r="AJ14" t="n">
         <v>2.504438041799733</v>
@@ -7433,7 +7433,7 @@
         <v>13.35027819563612</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.5560605283839815</v>
+        <v>0.5560605283839812</v>
       </c>
       <c r="AM14" t="n">
         <v>0.2559435892229798</v>
@@ -7448,16 +7448,16 @@
         <v>0.3777150994936763</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.400432323002829</v>
+        <v>1.40043232300283</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.396388802691133</v>
+        <v>7.396388802691132</v>
       </c>
       <c r="AS14" t="n">
         <v>0.1652154569972128</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.05484461247834844</v>
+        <v>0.05484461247834845</v>
       </c>
       <c r="AU14" t="n">
         <v>0.2363514675839616</v>
@@ -7469,52 +7469,52 @@
         <v>4.67049283503858</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.2378016392687133</v>
+        <v>0.2378016392687132</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.21069115862191</v>
+        <v>50.21069115862192</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.5383586329485343</v>
+        <v>0.5383586329485341</v>
       </c>
       <c r="BA14" t="n">
         <v>0.06515883312020487</v>
       </c>
       <c r="BB14" t="n">
-        <v>46.85941209386324</v>
+        <v>46.85941209386325</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.323467152298638</v>
+        <v>5.323467152298637</v>
       </c>
       <c r="BD14" t="n">
-        <v>28.09770099886684</v>
+        <v>28.09770099886685</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.3739193495611519</v>
+        <v>0.3739193495611518</v>
       </c>
       <c r="BF14" t="n">
         <v>0.5733265193252318</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.7753968259582847</v>
+        <v>0.7753968259582849</v>
       </c>
       <c r="BH14" t="n">
         <v>11.23354743482509</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.3691221454281291</v>
+        <v>0.3691221454281292</v>
       </c>
       <c r="BJ14" t="n">
         <v>0.005737491980239817</v>
       </c>
       <c r="BK14" t="n">
-        <v>7.576125406056336</v>
+        <v>7.576125406056337</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.09660918369795228</v>
+        <v>0.09660918369795229</v>
       </c>
       <c r="BM14" t="n">
-        <v>21.96548053126048</v>
+        <v>21.96548053126049</v>
       </c>
       <c r="BN14" t="n">
         <v>1.334536763315314</v>
@@ -7526,7 +7526,7 @@
         <v>0.20967058173589</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.4065884659834504</v>
+        <v>0.4065884659834503</v>
       </c>
       <c r="BR14" t="n">
         <v>0.1151019298294808</v>
@@ -7535,7 +7535,7 @@
         <v>15.07977235414507</v>
       </c>
       <c r="BT14" t="n">
-        <v>5.147166574557632</v>
+        <v>5.147166574557633</v>
       </c>
       <c r="BU14" t="n">
         <v>2.703419228222107</v>
@@ -7550,7 +7550,7 @@
         <v>2.074779267803994</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.09563127485471259</v>
+        <v>0.09563127485471261</v>
       </c>
       <c r="BZ14" t="n">
         <v>4.012654404122346</v>
@@ -7574,7 +7574,7 @@
         <v>1.244031089143612</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.395896523025484</v>
+        <v>2.395896523025483</v>
       </c>
       <c r="CH14" t="n">
         <v>0.3224537586271389</v>
@@ -7592,7 +7592,7 @@
         <v>0.3511870505842729</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.01870451431533712</v>
+        <v>0.01870451431533713</v>
       </c>
       <c r="CN14" t="n">
         <v>0.221111651308962</v>
@@ -7601,13 +7601,13 @@
         <v>1.253943234206859</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.6649306411617704</v>
+        <v>0.6649306411617703</v>
       </c>
       <c r="CQ14" t="n">
         <v>0.6782095792201264</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.5207305060998288</v>
+        <v>0.5207305060998287</v>
       </c>
       <c r="CS14" t="n">
         <v>0.09357982263230565</v>
@@ -7628,7 +7628,7 @@
         <v>3.415825360980258</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.07507512349838728</v>
+        <v>0.07507512349838727</v>
       </c>
       <c r="CZ14" t="n">
         <v>0.1809315018351128</v>
@@ -7643,7 +7643,7 @@
         <v>0.1339083718702938</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.048874403837278</v>
+        <v>1.048874403837277</v>
       </c>
       <c r="DE14" t="n">
         <v>0.007017540010765875</v>
@@ -7661,10 +7661,10 @@
         <v>0.08287078400642736</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.03957516619987032</v>
+        <v>0.03957516619987031</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.755089749759567</v>
+        <v>0.7550897497595671</v>
       </c>
       <c r="DL14" t="n">
         <v>0.1643653690071008</v>
@@ -7673,13 +7673,13 @@
         <v>0.184134835247514</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.01981490243712676</v>
+        <v>0.01981490243712675</v>
       </c>
       <c r="DO14" t="n">
         <v>0.8847711651821888</v>
       </c>
       <c r="DP14" t="n">
-        <v>160.0510620993676</v>
+        <v>160.0510620993677</v>
       </c>
       <c r="DQ14" t="n">
         <v>0.005325984725393929</v>
@@ -7715,13 +7715,13 @@
         <v>0.3364997309286672</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.1784285836989163</v>
+        <v>0.1784285836989162</v>
       </c>
       <c r="EC14" t="n">
         <v>4.972578129277611</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.004000648607851965</v>
+        <v>0.004000648607851964</v>
       </c>
       <c r="EE14" t="n">
         <v>0.07073018304569616</v>
@@ -7733,7 +7733,7 @@
         <v>0.06116672976681157</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.02887553248198015</v>
+        <v>0.02887553248198016</v>
       </c>
       <c r="EI14" t="n">
         <v>0.02870513103385827</v>
@@ -7830,46 +7830,46 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>339.9679037431539</v>
+        <v>339.9679037431541</v>
       </c>
       <c r="C15" t="n">
         <v>0.5162502252648964</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6913160163047214</v>
+        <v>0.6913160163047213</v>
       </c>
       <c r="E15" t="n">
         <v>9.472006026950426</v>
       </c>
       <c r="F15" t="n">
-        <v>199.9282717881693</v>
+        <v>199.9282717881696</v>
       </c>
       <c r="G15" t="n">
         <v>550.8143144862206</v>
       </c>
       <c r="H15" t="n">
-        <v>201.4705166773789</v>
+        <v>201.4705166773788</v>
       </c>
       <c r="I15" t="n">
-        <v>49.64308423613164</v>
+        <v>49.64308423613162</v>
       </c>
       <c r="J15" t="n">
         <v>16.64573910606476</v>
       </c>
       <c r="K15" t="n">
-        <v>79.32295137278484</v>
+        <v>79.32295137278487</v>
       </c>
       <c r="L15" t="n">
-        <v>27.18642336678111</v>
+        <v>27.1864233667811</v>
       </c>
       <c r="M15" t="n">
-        <v>3.445901137445752</v>
+        <v>3.445901137445751</v>
       </c>
       <c r="N15" t="n">
         <v>14.97814149223479</v>
       </c>
       <c r="O15" t="n">
-        <v>3.877453199129756</v>
+        <v>3.877453199129755</v>
       </c>
       <c r="P15" t="n">
         <v>3.83433200290798</v>
@@ -7878,10 +7878,10 @@
         <v>6.023177172559853</v>
       </c>
       <c r="R15" t="n">
-        <v>5.949131763719676</v>
+        <v>5.949131763719677</v>
       </c>
       <c r="S15" t="n">
-        <v>3.224974770365973</v>
+        <v>3.224974770365974</v>
       </c>
       <c r="T15" t="n">
         <v>12.97248403445492</v>
@@ -7908,7 +7908,7 @@
         <v>38.36051604651183</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.618488506865019</v>
+        <v>0.6184885068650192</v>
       </c>
       <c r="AC15" t="n">
         <v>24.71870188120024</v>
@@ -7920,10 +7920,10 @@
         <v>0.008270629897851415</v>
       </c>
       <c r="AF15" t="n">
-        <v>50.55783057115721</v>
+        <v>50.55783057115723</v>
       </c>
       <c r="AG15" t="n">
-        <v>35.76583284950183</v>
+        <v>35.76583284950181</v>
       </c>
       <c r="AH15" t="n">
         <v>1.50826641993647</v>
@@ -7947,7 +7947,7 @@
         <v>0.1900537463111749</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.4496474792223005</v>
+        <v>0.4496474792223004</v>
       </c>
       <c r="AP15" t="n">
         <v>0.3996174953893472</v>
@@ -7956,7 +7956,7 @@
         <v>1.394145542172853</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.806862964356108</v>
+        <v>7.806862964356106</v>
       </c>
       <c r="AS15" t="n">
         <v>0.1660504141021948</v>
@@ -7968,7 +7968,7 @@
         <v>0.239473226394323</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.777795179031264</v>
+        <v>3.777795179031263</v>
       </c>
       <c r="AW15" t="n">
         <v>5.685296609868967</v>
@@ -7980,7 +7980,7 @@
         <v>50.22166455892092</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.5375528631004318</v>
+        <v>0.5375528631004317</v>
       </c>
       <c r="BA15" t="n">
         <v>0.0706783984784168</v>
@@ -7992,7 +7992,7 @@
         <v>5.164562010286512</v>
       </c>
       <c r="BD15" t="n">
-        <v>27.061580558701</v>
+        <v>27.06158055870101</v>
       </c>
       <c r="BE15" t="n">
         <v>0.3450973520570018</v>
@@ -8001,10 +8001,10 @@
         <v>0.5640821584039857</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.822912262522063</v>
+        <v>0.8229122625220627</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.97800730298769</v>
+        <v>10.97800730298768</v>
       </c>
       <c r="BI15" t="n">
         <v>0.4106936260497087</v>
@@ -8016,22 +8016,22 @@
         <v>7.583220679254564</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.09725104860782101</v>
+        <v>0.09725104860782102</v>
       </c>
       <c r="BM15" t="n">
-        <v>22.28538870430981</v>
+        <v>22.2853887043098</v>
       </c>
       <c r="BN15" t="n">
         <v>1.280089657097345</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.03244527416312854</v>
+        <v>0.03244527416312855</v>
       </c>
       <c r="BP15" t="n">
         <v>0.2030245335134443</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.4547050420758502</v>
+        <v>0.4547050420758503</v>
       </c>
       <c r="BR15" t="n">
         <v>0.1019380962360695</v>
@@ -8040,7 +8040,7 @@
         <v>14.66952582916914</v>
       </c>
       <c r="BT15" t="n">
-        <v>5.377060657092476</v>
+        <v>5.377060657092477</v>
       </c>
       <c r="BU15" t="n">
         <v>2.91052028118577</v>
@@ -8067,7 +8067,7 @@
         <v>0.3131226425413716</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.09981060038399732</v>
+        <v>0.09981060038399729</v>
       </c>
       <c r="CD15" t="n">
         <v>0.2965181102235944</v>
@@ -8082,13 +8082,13 @@
         <v>2.246875413497708</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.3560990120076208</v>
+        <v>0.3560990120076207</v>
       </c>
       <c r="CI15" t="n">
         <v>0.1202264550615719</v>
       </c>
       <c r="CJ15" t="n">
-        <v>4.685707881822317</v>
+        <v>4.685707881822316</v>
       </c>
       <c r="CK15" t="n">
         <v>0.00627177523991902</v>
@@ -8106,7 +8106,7 @@
         <v>1.116509428003112</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.6484568813828581</v>
+        <v>0.648456881382858</v>
       </c>
       <c r="CQ15" t="n">
         <v>0.7640684764955331</v>
@@ -8136,7 +8136,7 @@
         <v>0.07287907595229685</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.1805709191206047</v>
+        <v>0.1805709191206046</v>
       </c>
       <c r="DA15" t="n">
         <v>0.2218884171008656</v>
@@ -8157,10 +8157,10 @@
         <v>0.3451279815988144</v>
       </c>
       <c r="DG15" t="n">
-        <v>4.353706378088149</v>
+        <v>4.35370637808815</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.330090299681918</v>
+        <v>0.3300902996819181</v>
       </c>
       <c r="DI15" t="n">
         <v>0.08996835551590757</v>
@@ -8169,7 +8169,7 @@
         <v>0.0452821189075249</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.7370437127873852</v>
+        <v>0.7370437127873851</v>
       </c>
       <c r="DL15" t="n">
         <v>0.1650313945374654</v>
@@ -8184,7 +8184,7 @@
         <v>0.9358240422108777</v>
       </c>
       <c r="DP15" t="n">
-        <v>159.2556506418967</v>
+        <v>159.2556506418966</v>
       </c>
       <c r="DQ15" t="n">
         <v>0.004645682075760891</v>
@@ -8205,7 +8205,7 @@
         <v>0.04213054718216701</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.4379004654374032</v>
+        <v>0.4379004654374033</v>
       </c>
       <c r="DX15" t="n">
         <v>0.4512704674912991</v>
@@ -8220,7 +8220,7 @@
         <v>0.3315956427584689</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.1834864678085094</v>
+        <v>0.1834864678085093</v>
       </c>
       <c r="EC15" t="n">
         <v>4.696528261225937</v>
@@ -8335,25 +8335,25 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>316.4651507008169</v>
+        <v>316.4651507008165</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4992434495697613</v>
+        <v>0.4992434495697612</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6883910427175276</v>
+        <v>0.6883910427175275</v>
       </c>
       <c r="E16" t="n">
         <v>8.454021668257226</v>
       </c>
       <c r="F16" t="n">
-        <v>190.4890067392386</v>
+        <v>190.4890067392378</v>
       </c>
       <c r="G16" t="n">
-        <v>531.8284565095476</v>
+        <v>531.8284565095477</v>
       </c>
       <c r="H16" t="n">
-        <v>197.1847244190116</v>
+        <v>197.1847244190117</v>
       </c>
       <c r="I16" t="n">
         <v>55.17449330541861</v>
@@ -8362,10 +8362,10 @@
         <v>17.05904384213317</v>
       </c>
       <c r="K16" t="n">
-        <v>79.74836981076972</v>
+        <v>79.74836981076973</v>
       </c>
       <c r="L16" t="n">
-        <v>26.08149031429908</v>
+        <v>26.08149031429905</v>
       </c>
       <c r="M16" t="n">
         <v>3.65493199032628</v>
@@ -8380,10 +8380,10 @@
         <v>3.761919792796915</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.554566851162716</v>
+        <v>5.554566851162715</v>
       </c>
       <c r="R16" t="n">
-        <v>5.5952396878183</v>
+        <v>5.595239687818298</v>
       </c>
       <c r="S16" t="n">
         <v>3.067936579055761</v>
@@ -8395,7 +8395,7 @@
         <v>0.0241019265672788</v>
       </c>
       <c r="V16" t="n">
-        <v>1.053665962554217</v>
+        <v>1.053665962554218</v>
       </c>
       <c r="W16" t="n">
         <v>40.85438593492318</v>
@@ -8410,25 +8410,25 @@
         <v>2.76365308868008</v>
       </c>
       <c r="AA16" t="n">
-        <v>35.55832547782603</v>
+        <v>35.55832547782605</v>
       </c>
       <c r="AB16" t="n">
         <v>0.6013531913225519</v>
       </c>
       <c r="AC16" t="n">
-        <v>23.55321816763551</v>
+        <v>23.55321816763553</v>
       </c>
       <c r="AD16" t="n">
         <v>0.03549163257831871</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.007534851138386475</v>
+        <v>0.007534851138386476</v>
       </c>
       <c r="AF16" t="n">
-        <v>51.02369697691538</v>
+        <v>51.02369697691539</v>
       </c>
       <c r="AG16" t="n">
-        <v>30.94050442140451</v>
+        <v>30.9405044214045</v>
       </c>
       <c r="AH16" t="n">
         <v>1.369355104171192</v>
@@ -8452,7 +8452,7 @@
         <v>0.2080942140041126</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.3981511220443803</v>
+        <v>0.3981511220443804</v>
       </c>
       <c r="AP16" t="n">
         <v>0.4029380843034595</v>
@@ -8461,7 +8461,7 @@
         <v>1.441774165774629</v>
       </c>
       <c r="AR16" t="n">
-        <v>7.558398617417602</v>
+        <v>7.558398617417601</v>
       </c>
       <c r="AS16" t="n">
         <v>0.1710382159973853</v>
@@ -8473,7 +8473,7 @@
         <v>0.2383106961359086</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.240435673082851</v>
+        <v>3.24043567308285</v>
       </c>
       <c r="AW16" t="n">
         <v>4.757881288043024</v>
@@ -8485,7 +8485,7 @@
         <v>50.13837317396759</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.4778548293983885</v>
+        <v>0.4778548293983886</v>
       </c>
       <c r="BA16" t="n">
         <v>0.06363342134431832</v>
@@ -8500,10 +8500,10 @@
         <v>24.16732439168008</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.3871143697981334</v>
+        <v>0.3871143697981332</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.5843001414103957</v>
+        <v>0.5843001414103959</v>
       </c>
       <c r="BG16" t="n">
         <v>0.7637496637475516</v>
@@ -8518,10 +8518,10 @@
         <v>0.001975814628289631</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.525872006185973</v>
+        <v>6.525872006185974</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.07683679912447719</v>
+        <v>0.07683679912447718</v>
       </c>
       <c r="BM16" t="n">
         <v>19.0441899293089</v>
@@ -8536,13 +8536,13 @@
         <v>0.1926497405625261</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.4204724715982064</v>
+        <v>0.4204724715982063</v>
       </c>
       <c r="BR16" t="n">
         <v>0.1053617787462058</v>
       </c>
       <c r="BS16" t="n">
-        <v>14.61431866093425</v>
+        <v>14.61431866093424</v>
       </c>
       <c r="BT16" t="n">
         <v>4.473685519038743</v>
@@ -8569,7 +8569,7 @@
         <v>0.06520952053710402</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.325462257089227</v>
+        <v>0.3254622570892271</v>
       </c>
       <c r="CC16" t="n">
         <v>0.07475826716118832</v>
@@ -8581,10 +8581,10 @@
         <v>5.259860609033285</v>
       </c>
       <c r="CF16" t="n">
-        <v>1.067176372910878</v>
+        <v>1.067176372910877</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.289162291748106</v>
+        <v>2.289162291748105</v>
       </c>
       <c r="CH16" t="n">
         <v>0.3196776778397661</v>
@@ -8608,7 +8608,7 @@
         <v>0.2020668916630237</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.5997736627781288</v>
+        <v>0.5997736627781289</v>
       </c>
       <c r="CP16" t="n">
         <v>0.5562359673958449</v>
@@ -8623,10 +8623,10 @@
         <v>0.1071545452565853</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.1906983546248199</v>
+        <v>0.1906983546248198</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.1265788327576678</v>
+        <v>0.1265788327576677</v>
       </c>
       <c r="CV16" t="n">
         <v>0.2140383884757204</v>
@@ -8638,7 +8638,7 @@
         <v>2.438774334043478</v>
       </c>
       <c r="CY16" t="n">
-        <v>0.07541772980031555</v>
+        <v>0.07541772980031558</v>
       </c>
       <c r="CZ16" t="n">
         <v>0.1705255841763265</v>
@@ -8671,13 +8671,13 @@
         <v>0.0898961334915731</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.04274963930216525</v>
+        <v>0.04274963930216526</v>
       </c>
       <c r="DK16" t="n">
         <v>0.754051893186615</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.1583141723984232</v>
+        <v>0.1583141723984233</v>
       </c>
       <c r="DM16" t="n">
         <v>0.1806542599802746</v>
@@ -8686,10 +8686,10 @@
         <v>0.02248887581906394</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.8067208686977893</v>
+        <v>0.8067208686977895</v>
       </c>
       <c r="DP16" t="n">
-        <v>148.0693184042884</v>
+        <v>148.0693184042883</v>
       </c>
       <c r="DQ16" t="n">
         <v>0.00408496055828206</v>
@@ -8698,7 +8698,7 @@
         <v>0.04092794229738318</v>
       </c>
       <c r="DS16" t="n">
-        <v>2.386687071960739</v>
+        <v>2.38668707196074</v>
       </c>
       <c r="DT16" t="n">
         <v>1.00826734993306</v>
@@ -8725,13 +8725,13 @@
         <v>0.3342315392635242</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.184133170478274</v>
+        <v>0.1841331704782739</v>
       </c>
       <c r="EC16" t="n">
         <v>4.648363209790867</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.004415197859653697</v>
+        <v>0.004415197859653696</v>
       </c>
       <c r="EE16" t="n">
         <v>0.07529819277237361</v>
@@ -8840,25 +8840,25 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>424.97283683609</v>
+        <v>424.9728368360898</v>
       </c>
       <c r="C17" t="n">
         <v>0.578346559989949</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8026681630801572</v>
+        <v>0.8026681630801573</v>
       </c>
       <c r="E17" t="n">
         <v>10.25139762752197</v>
       </c>
       <c r="F17" t="n">
-        <v>263.174293165467</v>
+        <v>263.1742931654673</v>
       </c>
       <c r="G17" t="n">
-        <v>759.074433036407</v>
+        <v>759.0744330364075</v>
       </c>
       <c r="H17" t="n">
-        <v>277.9700000718029</v>
+        <v>277.970000071803</v>
       </c>
       <c r="I17" t="n">
         <v>78.52670899027697</v>
@@ -8870,28 +8870,28 @@
         <v>113.7499439550954</v>
       </c>
       <c r="L17" t="n">
-        <v>30.92416302141376</v>
+        <v>30.92416302141378</v>
       </c>
       <c r="M17" t="n">
-        <v>3.315162242105957</v>
+        <v>3.315162242105956</v>
       </c>
       <c r="N17" t="n">
-        <v>15.62250490095467</v>
+        <v>15.62250490095466</v>
       </c>
       <c r="O17" t="n">
         <v>3.97830927028128</v>
       </c>
       <c r="P17" t="n">
-        <v>4.253952706653429</v>
+        <v>4.253952706653428</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.169677931648652</v>
+        <v>6.169677931648655</v>
       </c>
       <c r="R17" t="n">
-        <v>7.203289999042919</v>
+        <v>7.203289999042917</v>
       </c>
       <c r="S17" t="n">
-        <v>4.038574819956987</v>
+        <v>4.038574819956989</v>
       </c>
       <c r="T17" t="n">
         <v>16.10289527677356</v>
@@ -8903,37 +8903,37 @@
         <v>1.370383244301234</v>
       </c>
       <c r="W17" t="n">
-        <v>57.45436274853692</v>
+        <v>57.45436274853693</v>
       </c>
       <c r="X17" t="n">
         <v>0.3621489062048468</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.470960661583678</v>
+        <v>3.470960661583677</v>
       </c>
       <c r="Z17" t="n">
         <v>3.238436963249196</v>
       </c>
       <c r="AA17" t="n">
-        <v>54.29853086694441</v>
+        <v>54.2985308669444</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.7095695368170816</v>
+        <v>0.7095695368170813</v>
       </c>
       <c r="AC17" t="n">
-        <v>27.30672319240505</v>
+        <v>27.30672319240508</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.05375065546140828</v>
+        <v>0.05375065546140827</v>
       </c>
       <c r="AE17" t="n">
         <v>0.009114815042309427</v>
       </c>
       <c r="AF17" t="n">
-        <v>75.07397051738786</v>
+        <v>75.07397051738788</v>
       </c>
       <c r="AG17" t="n">
-        <v>37.77008413281228</v>
+        <v>37.77008413281227</v>
       </c>
       <c r="AH17" t="n">
         <v>2.093817064582382</v>
@@ -8942,31 +8942,31 @@
         <v>1.419414465684149</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.054031011960829</v>
+        <v>3.05403101196083</v>
       </c>
       <c r="AK17" t="n">
         <v>15.07712930581885</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.7000854348229415</v>
+        <v>0.7000854348229416</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.322706471715766</v>
+        <v>0.3227064717157661</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.2625387612799135</v>
+        <v>0.2625387612799136</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.5190737316048599</v>
+        <v>0.5190737316048598</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.4685313158556249</v>
+        <v>0.4685313158556248</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.504180574800631</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.75743615301791</v>
+        <v>8.757436153017906</v>
       </c>
       <c r="AS17" t="n">
         <v>0.2056600914382004</v>
@@ -8975,7 +8975,7 @@
         <v>0.047343225860417</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.2607051141114113</v>
+        <v>0.2607051141114112</v>
       </c>
       <c r="AV17" t="n">
         <v>4.387061663915111</v>
@@ -8984,25 +8984,25 @@
         <v>5.653048057956342</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.3056180042771321</v>
+        <v>0.3056180042771322</v>
       </c>
       <c r="AY17" t="n">
-        <v>77.26122772373189</v>
+        <v>77.26122772373188</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.5592223663275285</v>
+        <v>0.5592223663275283</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.07107560786585659</v>
+        <v>0.07107560786585662</v>
       </c>
       <c r="BB17" t="n">
-        <v>62.33204504933176</v>
+        <v>62.33204504933175</v>
       </c>
       <c r="BC17" t="n">
         <v>6.287370154692155</v>
       </c>
       <c r="BD17" t="n">
-        <v>27.90142995101545</v>
+        <v>27.90142995101546</v>
       </c>
       <c r="BE17" t="n">
         <v>0.4228791122199831</v>
@@ -9050,10 +9050,10 @@
         <v>17.11880592520789</v>
       </c>
       <c r="BT17" t="n">
-        <v>6.379974186720847</v>
+        <v>6.379974186720848</v>
       </c>
       <c r="BU17" t="n">
-        <v>3.159059213605378</v>
+        <v>3.159059213605377</v>
       </c>
       <c r="BV17" t="n">
         <v>3.430566588778875</v>
@@ -9071,7 +9071,7 @@
         <v>4.028397708228863</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.07648818052484195</v>
+        <v>0.07648818052484196</v>
       </c>
       <c r="CB17" t="n">
         <v>0.4324860252312683</v>
@@ -9116,7 +9116,7 @@
         <v>1.491387534136776</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.7322264340903724</v>
+        <v>0.7322264340903725</v>
       </c>
       <c r="CQ17" t="n">
         <v>0.7455975000702633</v>
@@ -9143,16 +9143,16 @@
         <v>4.303492288392656</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.09691409456915476</v>
+        <v>0.09691409456915474</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.1910374347783412</v>
+        <v>0.1910374347783411</v>
       </c>
       <c r="DA17" t="n">
         <v>0.2550371984085896</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.4092292769400332</v>
+        <v>0.4092292769400333</v>
       </c>
       <c r="DC17" t="n">
         <v>0.1700319651189248</v>
@@ -9170,7 +9170,7 @@
         <v>4.926163053362602</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.3921391808218673</v>
+        <v>0.3921391808218672</v>
       </c>
       <c r="DI17" t="n">
         <v>0.1093438533910073</v>
@@ -9179,7 +9179,7 @@
         <v>0.054784359252892</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.9585364727435164</v>
+        <v>0.9585364727435163</v>
       </c>
       <c r="DL17" t="n">
         <v>0.1729668912227956</v>
@@ -9194,13 +9194,13 @@
         <v>1.013353858934098</v>
       </c>
       <c r="DP17" t="n">
-        <v>239.3649296795553</v>
+        <v>239.3649296795552</v>
       </c>
       <c r="DQ17" t="n">
         <v>0.004779376863406378</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.0512104812345633</v>
+        <v>0.05121048123456331</v>
       </c>
       <c r="DS17" t="n">
         <v>2.720748388672598</v>
@@ -9215,7 +9215,7 @@
         <v>0.06174103630174761</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.5758578171556976</v>
+        <v>0.5758578171556977</v>
       </c>
       <c r="DX17" t="n">
         <v>0.5419610516547005</v>
@@ -9236,7 +9236,7 @@
         <v>6.918524389962566</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.005707098546805792</v>
+        <v>0.005707098546805793</v>
       </c>
       <c r="EE17" t="n">
         <v>0.09120238656550907</v>
@@ -9345,28 +9345,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>452.7732087518454</v>
+        <v>452.7732087518451</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6028096168457832</v>
+        <v>0.602809616845783</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9624695034230455</v>
+        <v>0.9624695034230457</v>
       </c>
       <c r="E18" t="n">
         <v>10.70725105523885</v>
       </c>
       <c r="F18" t="n">
-        <v>283.6896214537359</v>
+        <v>283.6896214537362</v>
       </c>
       <c r="G18" t="n">
         <v>797.3983425768859</v>
       </c>
       <c r="H18" t="n">
-        <v>308.7744288208417</v>
+        <v>308.7744288208419</v>
       </c>
       <c r="I18" t="n">
-        <v>86.58033040432601</v>
+        <v>86.58033040432602</v>
       </c>
       <c r="J18" t="n">
         <v>19.27333480777068</v>
@@ -9375,28 +9375,28 @@
         <v>139.808191732281</v>
       </c>
       <c r="L18" t="n">
-        <v>33.67093013591804</v>
+        <v>33.670930135918</v>
       </c>
       <c r="M18" t="n">
         <v>3.635938154208346</v>
       </c>
       <c r="N18" t="n">
-        <v>16.78014764680845</v>
+        <v>16.78014764680844</v>
       </c>
       <c r="O18" t="n">
         <v>4.155985265138864</v>
       </c>
       <c r="P18" t="n">
-        <v>4.352405875048257</v>
+        <v>4.352405875048258</v>
       </c>
       <c r="Q18" t="n">
         <v>6.272894064982358</v>
       </c>
       <c r="R18" t="n">
-        <v>8.735446391515644</v>
+        <v>8.73544639151565</v>
       </c>
       <c r="S18" t="n">
-        <v>4.206550290138673</v>
+        <v>4.206550290138671</v>
       </c>
       <c r="T18" t="n">
         <v>14.95038329562327</v>
@@ -9405,10 +9405,10 @@
         <v>0.03303951752592633</v>
       </c>
       <c r="V18" t="n">
-        <v>1.378030835205638</v>
+        <v>1.378030835205639</v>
       </c>
       <c r="W18" t="n">
-        <v>74.60968757876508</v>
+        <v>74.60968757876509</v>
       </c>
       <c r="X18" t="n">
         <v>0.4067919635099077</v>
@@ -9438,7 +9438,7 @@
         <v>78.126363196377</v>
       </c>
       <c r="AG18" t="n">
-        <v>37.83058400153883</v>
+        <v>37.83058400153884</v>
       </c>
       <c r="AH18" t="n">
         <v>2.183655798046823</v>
@@ -9462,7 +9462,7 @@
         <v>0.2564671268979504</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.49266981765383</v>
+        <v>0.4926698176538301</v>
       </c>
       <c r="AP18" t="n">
         <v>0.4689794849502715</v>
@@ -9471,7 +9471,7 @@
         <v>1.750946287373406</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.836762725264924</v>
+        <v>9.836762725264926</v>
       </c>
       <c r="AS18" t="n">
         <v>0.2485624767400129</v>
@@ -9480,10 +9480,10 @@
         <v>0.04808156005787596</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.296278098906221</v>
+        <v>0.2962780989062211</v>
       </c>
       <c r="AV18" t="n">
-        <v>5.625264225328277</v>
+        <v>5.625264225328276</v>
       </c>
       <c r="AW18" t="n">
         <v>5.348696248413469</v>
@@ -9492,10 +9492,10 @@
         <v>0.3356938204301642</v>
       </c>
       <c r="AY18" t="n">
-        <v>83.51987220662355</v>
+        <v>83.51987220662352</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.5651631022033325</v>
+        <v>0.5651631022033323</v>
       </c>
       <c r="BA18" t="n">
         <v>0.07278457453362859</v>
@@ -9504,22 +9504,22 @@
         <v>68.0818331262815</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.671156152445691</v>
+        <v>6.67115615244569</v>
       </c>
       <c r="BD18" t="n">
-        <v>30.78461216488866</v>
+        <v>30.78461216488867</v>
       </c>
       <c r="BE18" t="n">
         <v>0.4854848696430998</v>
       </c>
       <c r="BF18" t="n">
-        <v>0.6905510298714844</v>
+        <v>0.6905510298714843</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.8358940932905663</v>
+        <v>0.8358940932905662</v>
       </c>
       <c r="BH18" t="n">
-        <v>13.97065214339741</v>
+        <v>13.9706521433974</v>
       </c>
       <c r="BI18" t="n">
         <v>0.5761061180904167</v>
@@ -9528,19 +9528,19 @@
         <v>0.00229708657276117</v>
       </c>
       <c r="BK18" t="n">
-        <v>8.831576217316705</v>
+        <v>8.831576217316702</v>
       </c>
       <c r="BL18" t="n">
         <v>0.1258254157547768</v>
       </c>
       <c r="BM18" t="n">
-        <v>24.82385990061704</v>
+        <v>24.82385990061705</v>
       </c>
       <c r="BN18" t="n">
         <v>1.558043731696295</v>
       </c>
       <c r="BO18" t="n">
-        <v>0.03304330346265144</v>
+        <v>0.03304330346265145</v>
       </c>
       <c r="BP18" t="n">
         <v>0.2340839958658352</v>
@@ -9552,13 +9552,13 @@
         <v>0.1111202260536448</v>
       </c>
       <c r="BS18" t="n">
-        <v>17.9386799591219</v>
+        <v>17.93867995912189</v>
       </c>
       <c r="BT18" t="n">
-        <v>5.431101620617826</v>
+        <v>5.431101620617825</v>
       </c>
       <c r="BU18" t="n">
-        <v>3.140371146369914</v>
+        <v>3.140371146369913</v>
       </c>
       <c r="BV18" t="n">
         <v>3.263613274909258</v>
@@ -9597,13 +9597,13 @@
         <v>1.941317000982244</v>
       </c>
       <c r="CH18" t="n">
-        <v>0.4207049694510192</v>
+        <v>0.4207049694510193</v>
       </c>
       <c r="CI18" t="n">
         <v>0.2227027841446452</v>
       </c>
       <c r="CJ18" t="n">
-        <v>3.739191187375785</v>
+        <v>3.739191187375784</v>
       </c>
       <c r="CK18" t="n">
         <v>0.006326157532838396</v>
@@ -9615,19 +9615,19 @@
         <v>0.02245709333566719</v>
       </c>
       <c r="CN18" t="n">
-        <v>0.2402360666983507</v>
+        <v>0.2402360666983506</v>
       </c>
       <c r="CO18" t="n">
         <v>2.548811120263291</v>
       </c>
       <c r="CP18" t="n">
-        <v>0.621781769647172</v>
+        <v>0.6217817696471721</v>
       </c>
       <c r="CQ18" t="n">
         <v>0.633685337909459</v>
       </c>
       <c r="CR18" t="n">
-        <v>0.6045335162258804</v>
+        <v>0.6045335162258805</v>
       </c>
       <c r="CS18" t="n">
         <v>0.1339617349782584</v>
@@ -9639,22 +9639,22 @@
         <v>0.1514051397906416</v>
       </c>
       <c r="CV18" t="n">
-        <v>0.2482454406371755</v>
+        <v>0.2482454406371754</v>
       </c>
       <c r="CW18" t="n">
         <v>0.4465436722764186</v>
       </c>
       <c r="CX18" t="n">
-        <v>4.156584988507411</v>
+        <v>4.156584988507412</v>
       </c>
       <c r="CY18" t="n">
-        <v>0.08907585487301588</v>
+        <v>0.08907585487301591</v>
       </c>
       <c r="CZ18" t="n">
         <v>0.1906562970796666</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.2435966559983966</v>
+        <v>0.2435966559983967</v>
       </c>
       <c r="DB18" t="n">
         <v>0.4236697570150296</v>
@@ -9675,16 +9675,16 @@
         <v>5.34815578678483</v>
       </c>
       <c r="DH18" t="n">
-        <v>0.4663618835657087</v>
+        <v>0.4663618835657086</v>
       </c>
       <c r="DI18" t="n">
         <v>0.1247185211256902</v>
       </c>
       <c r="DJ18" t="n">
-        <v>0.04887452673400481</v>
+        <v>0.04887452673400482</v>
       </c>
       <c r="DK18" t="n">
-        <v>0.980981670757517</v>
+        <v>0.9809816707575171</v>
       </c>
       <c r="DL18" t="n">
         <v>0.1760549860689678</v>
@@ -9714,13 +9714,13 @@
         <v>1.273681295473754</v>
       </c>
       <c r="DU18" t="n">
-        <v>3.666081720345591</v>
+        <v>3.666081720345592</v>
       </c>
       <c r="DV18" t="n">
         <v>0.0791418077117118</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.617149461815319</v>
+        <v>0.6171494618153192</v>
       </c>
       <c r="DX18" t="n">
         <v>0.5880162834958484</v>
@@ -9850,28 +9850,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>448.8247288819235</v>
+        <v>448.8247288819236</v>
       </c>
       <c r="C19" t="n">
         <v>0.5580478351504095</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9224246385322585</v>
+        <v>0.9224246385322588</v>
       </c>
       <c r="E19" t="n">
         <v>10.74934796496974</v>
       </c>
       <c r="F19" t="n">
-        <v>269.2484509264083</v>
+        <v>269.2484509264086</v>
       </c>
       <c r="G19" t="n">
-        <v>785.765087978192</v>
+        <v>785.7650879781914</v>
       </c>
       <c r="H19" t="n">
         <v>286.234307123676</v>
       </c>
       <c r="I19" t="n">
-        <v>77.0120479880252</v>
+        <v>77.01204798802522</v>
       </c>
       <c r="J19" t="n">
         <v>21.25938443433023</v>
@@ -9880,7 +9880,7 @@
         <v>117.9812102547329</v>
       </c>
       <c r="L19" t="n">
-        <v>34.87168598776994</v>
+        <v>34.87168598776992</v>
       </c>
       <c r="M19" t="n">
         <v>3.986433630032791</v>
@@ -9892,19 +9892,19 @@
         <v>4.254430363801599</v>
       </c>
       <c r="P19" t="n">
-        <v>5.006679935035801</v>
+        <v>5.006679935035802</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.704989322128009</v>
+        <v>6.704989322128011</v>
       </c>
       <c r="R19" t="n">
-        <v>9.028734150007697</v>
+        <v>9.028734150007693</v>
       </c>
       <c r="S19" t="n">
         <v>4.182635611530205</v>
       </c>
       <c r="T19" t="n">
-        <v>17.12089756026327</v>
+        <v>17.12089756026325</v>
       </c>
       <c r="U19" t="n">
         <v>0.02893467159938666</v>
@@ -9919,10 +9919,10 @@
         <v>0.4057598674094485</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.937660405606108</v>
+        <v>3.937660405606107</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.984225577084573</v>
+        <v>3.984225577084572</v>
       </c>
       <c r="AA19" t="n">
         <v>57.57534920434809</v>
@@ -9940,13 +9940,13 @@
         <v>0.009678379455482436</v>
       </c>
       <c r="AF19" t="n">
-        <v>74.25901315828332</v>
+        <v>74.25901315828337</v>
       </c>
       <c r="AG19" t="n">
-        <v>39.01559282927751</v>
+        <v>39.01559282927752</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.086229208040842</v>
+        <v>2.086229208040843</v>
       </c>
       <c r="AI19" t="n">
         <v>1.667507511373175</v>
@@ -9955,10 +9955,10 @@
         <v>3.490201020686051</v>
       </c>
       <c r="AK19" t="n">
-        <v>16.09873236260819</v>
+        <v>16.0987323626082</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.7224778093726278</v>
+        <v>0.7224778093726277</v>
       </c>
       <c r="AM19" t="n">
         <v>0.3385117436309611</v>
@@ -9967,10 +9967,10 @@
         <v>0.2597562821048839</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.5045882975581967</v>
+        <v>0.5045882975581968</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.4612020433625662</v>
+        <v>0.4612020433625661</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.871157889002289</v>
@@ -9988,19 +9988,19 @@
         <v>0.2941269442488873</v>
       </c>
       <c r="AV19" t="n">
-        <v>5.46888966580628</v>
+        <v>5.468889665806281</v>
       </c>
       <c r="AW19" t="n">
         <v>6.067849628342474</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.3253991120492345</v>
+        <v>0.3253991120492344</v>
       </c>
       <c r="AY19" t="n">
-        <v>79.43649960610364</v>
+        <v>79.43649960610365</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.6393289829530447</v>
+        <v>0.6393289829530449</v>
       </c>
       <c r="BA19" t="n">
         <v>0.0802778951032702</v>
@@ -10009,10 +10009,10 @@
         <v>67.54040679039808</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.586134288915915</v>
+        <v>6.586134288915917</v>
       </c>
       <c r="BD19" t="n">
-        <v>33.68994732335538</v>
+        <v>33.68994732335537</v>
       </c>
       <c r="BE19" t="n">
         <v>0.5083179191588839</v>
@@ -10033,16 +10033,16 @@
         <v>0.1281962205562935</v>
       </c>
       <c r="BK19" t="n">
-        <v>7.873375497297173</v>
+        <v>7.873375497297174</v>
       </c>
       <c r="BL19" t="n">
         <v>0.1212508408923788</v>
       </c>
       <c r="BM19" t="n">
-        <v>27.11831060220081</v>
+        <v>27.11831060220082</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.491737739410399</v>
+        <v>1.491737739410398</v>
       </c>
       <c r="BO19" t="n">
         <v>0.03374899302145457</v>
@@ -10057,7 +10057,7 @@
         <v>0.1273511982137756</v>
       </c>
       <c r="BS19" t="n">
-        <v>18.34885510296303</v>
+        <v>18.34885510296304</v>
       </c>
       <c r="BT19" t="n">
         <v>6.941913179724765</v>
@@ -10066,13 +10066,13 @@
         <v>3.199083838448154</v>
       </c>
       <c r="BV19" t="n">
-        <v>3.633930412665086</v>
+        <v>3.633930412665087</v>
       </c>
       <c r="BW19" t="n">
         <v>0.007991089357987537</v>
       </c>
       <c r="BX19" t="n">
-        <v>2.905019319809835</v>
+        <v>2.905019319809834</v>
       </c>
       <c r="BY19" t="n">
         <v>0.1281563934325669</v>
@@ -10102,7 +10102,7 @@
         <v>2.433263335331551</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.4153735254923928</v>
+        <v>0.4153735254923929</v>
       </c>
       <c r="CI19" t="n">
         <v>0.2332162826466168</v>
@@ -10126,25 +10126,25 @@
         <v>1.884495547139693</v>
       </c>
       <c r="CP19" t="n">
-        <v>0.6860214198591614</v>
+        <v>0.6860214198591617</v>
       </c>
       <c r="CQ19" t="n">
-        <v>0.6727509710144711</v>
+        <v>0.672750971014471</v>
       </c>
       <c r="CR19" t="n">
-        <v>0.5858840725609684</v>
+        <v>0.5858840725609685</v>
       </c>
       <c r="CS19" t="n">
         <v>0.1371763294525771</v>
       </c>
       <c r="CT19" t="n">
-        <v>0.2400608097112796</v>
+        <v>0.2400608097112797</v>
       </c>
       <c r="CU19" t="n">
         <v>0.154169627035524</v>
       </c>
       <c r="CV19" t="n">
-        <v>0.2777215853373122</v>
+        <v>0.2777215853373123</v>
       </c>
       <c r="CW19" t="n">
         <v>0.4796167721842459</v>
@@ -10153,7 +10153,7 @@
         <v>4.32355900024305</v>
       </c>
       <c r="CY19" t="n">
-        <v>0.08549185195936546</v>
+        <v>0.08549185195936547</v>
       </c>
       <c r="CZ19" t="n">
         <v>0.2195165997000265</v>
@@ -10168,7 +10168,7 @@
         <v>0.1974329715431272</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.271951823513564</v>
+        <v>1.271951823513563</v>
       </c>
       <c r="DE19" t="n">
         <v>0.007869031590050566</v>
@@ -10177,10 +10177,10 @@
         <v>0.3953490814184847</v>
       </c>
       <c r="DG19" t="n">
-        <v>5.343083739330379</v>
+        <v>5.34308373933038</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.487113246050039</v>
+        <v>0.4871132460500389</v>
       </c>
       <c r="DI19" t="n">
         <v>0.1095440100711572</v>
@@ -10255,7 +10255,7 @@
         <v>0.001777674644798384</v>
       </c>
       <c r="EG19" t="n">
-        <v>0.0579540795021263</v>
+        <v>0.05795407950212631</v>
       </c>
       <c r="EH19" t="n">
         <v>0.03133953716670834</v>
